--- a/财务与流水/馋唻买-听涛路店商品表.xlsx
+++ b/财务与流水/馋唻买-听涛路店商品表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github localpath\ChanWeiMai\财务与流水\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66068D6D-4933-4B5A-A96B-B0C09AD39E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD531C5-F4C4-499E-A046-49E3E203DD30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="915" yWindow="1575" windowWidth="35070" windowHeight="19335" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="成本管理" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="75">
   <si>
     <t>SKU名称</t>
   </si>
@@ -151,10 +151,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>金汤酸菜泡面+瘦肉丸</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>燕面</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -300,6 +296,18 @@
   </si>
   <si>
     <t>牛肉</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>合计成本</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>金汤酸菜泡面+瘦肉丸(特大份)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>/</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -311,7 +319,7 @@
     <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
     <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -357,20 +365,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <family val="3"/>
@@ -399,6 +393,11 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -459,7 +458,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -506,89 +505,109 @@
     <xf numFmtId="4" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="13">
     <dxf>
       <font>
-        <b/>
+        <b val="0"/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <name val="宋体"/>
-        <charset val="134"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
         <scheme val="none"/>
       </font>
-      <border outline="0">
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -835,6 +854,25 @@
         </right>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <border outline="0">
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -849,10 +887,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SKUTable" displayName="SKUTable" ref="A1:L36" totalsRowShown="0">
-  <autoFilter ref="A1:L36" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="SKU名称" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SKUTable" displayName="SKUTable" ref="A1:M36" totalsRowShown="0">
+  <autoFilter ref="A1:M36" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="SKU名称" dataDxfId="12"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="进货价格(元/500g)" dataDxfId="11"/>
     <tableColumn id="11" xr3:uid="{85AD201C-B605-4B3F-A35C-803E9EF62608}" name="运费(元/500g)" dataDxfId="10"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="每份重量(g)" dataDxfId="9"/>
@@ -860,6 +898,9 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="食材成本(元/份)" dataDxfId="7"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="打包成本(元/份)" dataDxfId="6"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="调味品成本(元/份)" dataDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{92F9A26C-6BB3-4CE8-9F14-DEF3C1B8B4F9}" name="合计成本" dataDxfId="0">
+      <calculatedColumnFormula>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="售价(元/份)" dataDxfId="4"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="毛利(元/份)" dataDxfId="3"/>
     <tableColumn id="13" xr3:uid="{550C8CA0-F351-4EDD-8624-328FC6B5B01D}" name="成本利润率(%)" dataDxfId="2">
@@ -1159,10 +1200,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:M42"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="30.5" style="20" customWidth="1"/>
+    <col min="1" max="1" width="30.5" style="18" customWidth="1"/>
     <col min="2" max="2" width="14" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" style="7" customWidth="1"/>
     <col min="4" max="4" width="13" style="5" bestFit="1" customWidth="1"/>
@@ -1170,14 +1211,15 @@
     <col min="6" max="6" width="14.25" style="4" customWidth="1"/>
     <col min="7" max="7" width="15.625" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.125" style="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.625" style="4" customWidth="1"/>
-    <col min="12" max="12" width="14.75" style="4" customWidth="1"/>
+    <col min="9" max="9" width="16.375" style="4" customWidth="1"/>
+    <col min="10" max="10" width="17.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.625" style="4" customWidth="1"/>
+    <col min="13" max="13" width="14.75" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:13" s="1" customFormat="1" ht="29.25" customHeight="1">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
@@ -1201,21 +1243,24 @@
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+    <row r="2" spans="1:13" ht="20.25" customHeight="1">
+      <c r="A2" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="10">
@@ -1238,32 +1283,32 @@
         <v>0.124</v>
       </c>
       <c r="H2" s="13"/>
-      <c r="I2" s="14">
+      <c r="I2" s="13">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>2.8360000000000003</v>
+      </c>
+      <c r="J2" s="14">
         <v>8</v>
       </c>
-      <c r="J2" s="15">
-        <f>I2-(F2+G2+H2)</f>
+      <c r="K2" s="15">
+        <f>J2-(F2+G2+H2)</f>
         <v>5.1639999999999997</v>
       </c>
-      <c r="K2" s="15">
+      <c r="L2" s="15">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
         <v>190.41297935103242</v>
       </c>
-      <c r="L2" s="15">
-        <f>(I2-(F2+G2+H2))/I2*100</f>
+      <c r="M2" s="15">
+        <f>(J2-(F2+G2+H2))/J2*100</f>
         <v>64.55</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+    <row r="3" spans="1:13" ht="20.25" customHeight="1">
+      <c r="A3" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="10">
-        <v>11.5</v>
-      </c>
-      <c r="C3" s="10">
-        <v>0.3</v>
-      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
       <c r="D3" s="11">
         <v>220</v>
       </c>
@@ -1271,31 +1316,34 @@
         <v>13</v>
       </c>
       <c r="F3" s="13">
-        <f>(B3+SKUTable[[#This Row],[运费(元/500g)]])*D3/500</f>
-        <v>5.1920000000000002</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="G3" s="13">
         <v>0.19600000000000001</v>
       </c>
       <c r="H3" s="13"/>
-      <c r="I3" s="14">
+      <c r="I3" s="13">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>2.6460000000000004</v>
+      </c>
+      <c r="J3" s="14">
         <v>8</v>
       </c>
-      <c r="J3" s="15">
-        <f>I3-(F3+G3+H3)</f>
-        <v>2.6120000000000001</v>
-      </c>
       <c r="K3" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>50.308166409861322</v>
+        <f>J3-(F3+G3+H3)</f>
+        <v>5.3539999999999992</v>
       </c>
       <c r="L3" s="15">
-        <f>(I3-(F3+G3+H3))/I3*100</f>
-        <v>32.65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
+        <v>218.53061224489792</v>
+      </c>
+      <c r="M3" s="15">
+        <f>(J3-(F3+G3+H3))/J3*100</f>
+        <v>66.924999999999983</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="20.25" customHeight="1">
+      <c r="A4" s="17" t="s">
         <v>16</v>
       </c>
       <c r="B4" s="10">
@@ -1320,24 +1368,28 @@
       <c r="H4" s="13">
         <v>0</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="13">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>1.282</v>
+      </c>
+      <c r="J4" s="14">
         <v>4</v>
       </c>
-      <c r="J4" s="15">
-        <f t="shared" ref="J4:J36" si="0">I4-(F4+G4+H4)</f>
+      <c r="K4" s="15">
+        <f t="shared" ref="K4:K36" si="0">J4-(F4+G4+H4)</f>
         <v>2.718</v>
       </c>
-      <c r="K4" s="15">
+      <c r="L4" s="15">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
         <v>220.61688311688309</v>
       </c>
-      <c r="L4" s="15">
-        <f t="shared" ref="L4:L36" si="1">(I4-(F4+G4+H4))/I4*100</f>
+      <c r="M4" s="15">
+        <f t="shared" ref="M4:M36" si="1">(J4-(F4+G4+H4))/J4*100</f>
         <v>67.95</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+    <row r="5" spans="1:13" ht="20.25" customHeight="1">
+      <c r="A5" s="17" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="10" t="s">
@@ -1361,24 +1413,28 @@
       <c r="H5" s="13">
         <v>0</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="13">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>2.02</v>
+      </c>
+      <c r="J5" s="14">
         <v>5</v>
       </c>
-      <c r="J5" s="15">
+      <c r="K5" s="15">
         <f t="shared" si="0"/>
         <v>2.98</v>
       </c>
-      <c r="K5" s="15">
+      <c r="L5" s="15">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
         <v>149</v>
       </c>
-      <c r="L5" s="15">
+      <c r="M5" s="15">
         <f t="shared" si="1"/>
         <v>59.599999999999994</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+    <row r="6" spans="1:13" ht="20.25" customHeight="1">
+      <c r="A6" s="17" t="s">
         <v>18</v>
       </c>
       <c r="B6" s="10" t="s">
@@ -1402,24 +1458,28 @@
       <c r="H6" s="13">
         <v>0</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="13">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="J6" s="14">
         <v>8</v>
       </c>
-      <c r="J6" s="15">
+      <c r="K6" s="15">
         <f t="shared" si="0"/>
         <v>2.9800000000000004</v>
       </c>
-      <c r="K6" s="15">
+      <c r="L6" s="15">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
         <v>59.600000000000009</v>
       </c>
-      <c r="L6" s="15">
+      <c r="M6" s="15">
         <f t="shared" si="1"/>
         <v>37.250000000000007</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+    <row r="7" spans="1:13" ht="20.25" customHeight="1">
+      <c r="A7" s="19" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="10" t="s">
@@ -1434,25 +1494,35 @@
       <c r="E7" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
+      <c r="F7" s="13">
+        <v>3.24</v>
+      </c>
+      <c r="G7" s="13">
+        <v>0.02</v>
+      </c>
       <c r="H7" s="13"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="15">
+      <c r="I7" s="13">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>3.2600000000000002</v>
+      </c>
+      <c r="J7" s="14">
+        <v>8</v>
+      </c>
+      <c r="K7" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K7" s="15" t="e">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L7" s="15" t="e">
+        <v>4.74</v>
+      </c>
+      <c r="L7" s="15">
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
+        <v>146.2962962962963</v>
+      </c>
+      <c r="M7" s="15">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+        <v>59.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="20.25" customHeight="1">
+      <c r="A8" s="19" t="s">
         <v>22</v>
       </c>
       <c r="B8" s="10" t="s">
@@ -1467,25 +1537,33 @@
       <c r="E8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="13"/>
+      <c r="F8" s="13">
+        <v>0.4</v>
+      </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K8" s="15" t="e">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L8" s="15" t="e">
+      <c r="I8" s="13">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>0.4</v>
+      </c>
+      <c r="J8" s="14">
+        <v>1.25</v>
+      </c>
+      <c r="K8" s="15">
+        <f>J8-(F8+G8+H8)</f>
+        <v>0.85</v>
+      </c>
+      <c r="L8" s="15">
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
+        <v>212.5</v>
+      </c>
+      <c r="M8" s="15">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="20.25" customHeight="1">
+      <c r="A9" s="17" t="s">
         <v>23</v>
       </c>
       <c r="B9" s="10" t="s">
@@ -1509,24 +1587,28 @@
       <c r="H9" s="13">
         <v>0</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="13">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>0.45</v>
+      </c>
+      <c r="J9" s="14">
         <v>1.25</v>
       </c>
-      <c r="J9" s="15">
+      <c r="K9" s="15">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="K9" s="15">
+      <c r="L9" s="15">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
         <v>177.7777777777778</v>
       </c>
-      <c r="L9" s="15">
+      <c r="M9" s="15">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+    <row r="10" spans="1:13" ht="20.25" customHeight="1">
+      <c r="A10" s="17" t="s">
         <v>20</v>
       </c>
       <c r="B10" s="10" t="s">
@@ -1550,24 +1632,28 @@
       <c r="H10" s="13">
         <v>0</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="13">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>1.37</v>
+      </c>
+      <c r="J10" s="14">
         <v>2</v>
       </c>
-      <c r="J10" s="15">
+      <c r="K10" s="15">
         <f t="shared" si="0"/>
         <v>0.62999999999999989</v>
       </c>
-      <c r="K10" s="15">
+      <c r="L10" s="15">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
         <v>45.985401459854003</v>
       </c>
-      <c r="L10" s="15">
+      <c r="M10" s="15">
         <f t="shared" si="1"/>
         <v>31.499999999999993</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+    <row r="11" spans="1:13" ht="20.25" customHeight="1">
+      <c r="A11" s="17" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="10" t="s">
@@ -1591,25 +1677,29 @@
       <c r="H11" s="13">
         <v>0</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="13">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>1.37</v>
+      </c>
+      <c r="J11" s="14">
         <v>2</v>
       </c>
-      <c r="J11" s="15">
+      <c r="K11" s="15">
         <f t="shared" si="0"/>
         <v>0.62999999999999989</v>
       </c>
-      <c r="K11" s="15">
+      <c r="L11" s="15">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
         <v>45.985401459854003</v>
       </c>
-      <c r="L11" s="15">
+      <c r="M11" s="15">
         <f t="shared" si="1"/>
         <v>31.499999999999993</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>55</v>
+    <row r="12" spans="1:13" ht="20.25" customHeight="1">
+      <c r="A12" s="17" t="s">
+        <v>54</v>
       </c>
       <c r="B12" s="10">
         <v>9.09</v>
@@ -1621,7 +1711,7 @@
         <v>200</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F12" s="13">
         <f>(B12+SKUTable[[#This Row],[运费(元/500g)]])*D12/500</f>
@@ -1633,25 +1723,29 @@
       <c r="H12" s="13">
         <v>0.2</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="13">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>4.3410000000000002</v>
+      </c>
+      <c r="J12" s="14">
         <v>12</v>
       </c>
-      <c r="J12" s="15">
+      <c r="K12" s="15">
         <f t="shared" si="0"/>
         <v>7.6589999999999998</v>
       </c>
-      <c r="K12" s="15">
+      <c r="L12" s="15">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
         <v>203.91373801916933</v>
       </c>
-      <c r="L12" s="15">
+      <c r="M12" s="15">
         <f t="shared" si="1"/>
         <v>63.824999999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>56</v>
+    <row r="13" spans="1:13" ht="20.25" customHeight="1">
+      <c r="A13" s="17" t="s">
+        <v>55</v>
       </c>
       <c r="B13" s="10">
         <v>9.09</v>
@@ -1663,7 +1757,7 @@
         <v>300</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F13" s="13">
         <f>(B13+SKUTable[[#This Row],[运费(元/500g)]])*D13/500</f>
@@ -1675,25 +1769,29 @@
       <c r="H13" s="13">
         <v>0.2</v>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="13">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>6.3540000000000001</v>
+      </c>
+      <c r="J13" s="14">
         <v>16</v>
       </c>
-      <c r="J13" s="15">
+      <c r="K13" s="15">
         <f t="shared" si="0"/>
         <v>9.6460000000000008</v>
       </c>
-      <c r="K13" s="15">
+      <c r="L13" s="15">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
         <v>171.21050763223286</v>
       </c>
-      <c r="L13" s="15">
+      <c r="M13" s="15">
         <f t="shared" si="1"/>
         <v>60.287500000000009</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>57</v>
+    <row r="14" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A14" s="17" t="s">
+        <v>56</v>
       </c>
       <c r="B14" s="10">
         <v>10</v>
@@ -1705,7 +1803,7 @@
         <v>200</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F14" s="13">
         <f>IF(B14&lt;&gt;"",B14*D14/500,"")</f>
@@ -1717,25 +1815,29 @@
       <c r="H14" s="13">
         <v>0.2</v>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="13">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>4.585</v>
+      </c>
+      <c r="J14" s="14">
         <v>14</v>
       </c>
-      <c r="J14" s="15">
+      <c r="K14" s="15">
         <f t="shared" si="0"/>
         <v>9.4149999999999991</v>
       </c>
-      <c r="K14" s="15">
+      <c r="L14" s="15">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
         <v>235.37499999999997</v>
       </c>
-      <c r="L14" s="15">
+      <c r="M14" s="15">
         <f t="shared" si="1"/>
         <v>67.25</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>58</v>
+    <row r="15" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A15" s="17" t="s">
+        <v>57</v>
       </c>
       <c r="B15" s="10">
         <v>10</v>
@@ -1747,7 +1849,7 @@
         <v>300</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F15" s="13">
         <f>IF(B15&lt;&gt;"",B15*D15/500,"")</f>
@@ -1759,25 +1861,29 @@
       <c r="H15" s="13">
         <v>0.2</v>
       </c>
-      <c r="I15" s="14">
+      <c r="I15" s="13">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>6.72</v>
+      </c>
+      <c r="J15" s="14">
         <v>18</v>
       </c>
-      <c r="J15" s="15">
+      <c r="K15" s="15">
         <f t="shared" si="0"/>
         <v>11.280000000000001</v>
       </c>
-      <c r="K15" s="15">
+      <c r="L15" s="15">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
         <v>188</v>
       </c>
-      <c r="L15" s="15">
+      <c r="M15" s="15">
         <f t="shared" si="1"/>
         <v>62.666666666666671</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>59</v>
+    <row r="16" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A16" s="17" t="s">
+        <v>58</v>
       </c>
       <c r="B16" s="10">
         <v>12.5</v>
@@ -1789,7 +1895,7 @@
         <v>200</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F16" s="13">
         <f>IF(B16&lt;&gt;"",B16*D16/500,"")</f>
@@ -1801,25 +1907,29 @@
       <c r="H16" s="13">
         <v>0.2</v>
       </c>
-      <c r="I16" s="14">
+      <c r="I16" s="13">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>5.585</v>
+      </c>
+      <c r="J16" s="14">
         <v>15</v>
       </c>
-      <c r="J16" s="15">
+      <c r="K16" s="15">
         <f t="shared" si="0"/>
         <v>9.4149999999999991</v>
       </c>
-      <c r="K16" s="15">
+      <c r="L16" s="15">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
         <v>188.29999999999998</v>
       </c>
-      <c r="L16" s="15">
+      <c r="M16" s="15">
         <f t="shared" si="1"/>
         <v>62.766666666666659</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>60</v>
+    <row r="17" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A17" s="17" t="s">
+        <v>59</v>
       </c>
       <c r="B17" s="10">
         <v>12.5</v>
@@ -1831,7 +1941,7 @@
         <v>300</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F17" s="13">
         <f>IF(B17&lt;&gt;"",B17*D17/500,"")</f>
@@ -1843,25 +1953,29 @@
       <c r="H17" s="13">
         <v>0.2</v>
       </c>
-      <c r="I17" s="14">
+      <c r="I17" s="13">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>8.2199999999999989</v>
+      </c>
+      <c r="J17" s="14">
         <v>20</v>
       </c>
-      <c r="J17" s="15">
+      <c r="K17" s="15">
         <f t="shared" si="0"/>
         <v>11.780000000000001</v>
       </c>
-      <c r="K17" s="15">
+      <c r="L17" s="15">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
         <v>157.06666666666669</v>
       </c>
-      <c r="L17" s="15">
+      <c r="M17" s="15">
         <f t="shared" si="1"/>
         <v>58.900000000000006</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
-        <v>49</v>
+    <row r="18" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A18" s="19" t="s">
+        <v>48</v>
       </c>
       <c r="B18" s="10">
         <v>17</v>
@@ -1870,14 +1984,14 @@
         <v>0.3</v>
       </c>
       <c r="D18" s="11">
-        <v>200</v>
+        <v>166</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F18" s="13">
         <f t="shared" ref="F18:F35" si="2">IF(B18&lt;&gt;"",B18*D18/500,"")</f>
-        <v>6.8</v>
+        <v>5.6440000000000001</v>
       </c>
       <c r="G18" s="13">
         <v>0.38500000000000001</v>
@@ -1885,25 +1999,29 @@
       <c r="H18" s="13">
         <v>0.2</v>
       </c>
-      <c r="I18" s="14">
+      <c r="I18" s="13">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>6.2290000000000001</v>
+      </c>
+      <c r="J18" s="14">
         <v>15</v>
       </c>
-      <c r="J18" s="15">
+      <c r="K18" s="15">
         <f t="shared" si="0"/>
-        <v>7.6150000000000002</v>
-      </c>
-      <c r="K18" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>111.98529411764706</v>
+        <v>8.7710000000000008</v>
       </c>
       <c r="L18" s="15">
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
+        <v>155.40396881644224</v>
+      </c>
+      <c r="M18" s="15">
         <f t="shared" si="1"/>
-        <v>50.766666666666673</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
-        <v>50</v>
+        <v>58.473333333333343</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A19" s="19" t="s">
+        <v>49</v>
       </c>
       <c r="B19" s="10">
         <v>17</v>
@@ -1912,14 +2030,14 @@
         <v>0.3</v>
       </c>
       <c r="D19" s="11">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F19" s="13">
         <f t="shared" si="2"/>
-        <v>10.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="G19" s="13">
         <v>0.52</v>
@@ -1927,25 +2045,29 @@
       <c r="H19" s="13">
         <v>0.2</v>
       </c>
-      <c r="I19" s="14">
+      <c r="I19" s="13">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>7.5200000000000005</v>
+      </c>
+      <c r="J19" s="14">
         <v>20</v>
       </c>
-      <c r="J19" s="15">
+      <c r="K19" s="15">
         <f t="shared" si="0"/>
-        <v>9.0800000000000018</v>
-      </c>
-      <c r="K19" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>89.01960784313728</v>
+        <v>12.48</v>
       </c>
       <c r="L19" s="15">
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
+        <v>183.52941176470588</v>
+      </c>
+      <c r="M19" s="15">
         <f t="shared" si="1"/>
-        <v>45.400000000000006</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="22" t="s">
-        <v>69</v>
+        <v>62.4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A20" s="19" t="s">
+        <v>68</v>
       </c>
       <c r="B20" s="10">
         <v>22.5</v>
@@ -1957,7 +2079,7 @@
         <v>180</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F20" s="13">
         <f t="shared" si="2"/>
@@ -1969,121 +2091,142 @@
       <c r="H20" s="13">
         <v>0.2</v>
       </c>
-      <c r="I20" s="14">
+      <c r="I20" s="13">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>8.6849999999999987</v>
+      </c>
+      <c r="J20" s="14">
         <v>18</v>
       </c>
-      <c r="J20" s="15">
+      <c r="K20" s="15">
         <f t="shared" si="0"/>
         <v>9.3150000000000013</v>
       </c>
-      <c r="K20" s="15">
+      <c r="L20" s="15">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
         <v>115.00000000000001</v>
       </c>
-      <c r="L20" s="15">
-        <f>(I20-(F20+G20+H20))/I20*100</f>
+      <c r="M20" s="15">
+        <f>(J20-(F20+G20+H20))/J20*100</f>
         <v>51.750000000000007</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="10"/>
+    <row r="21" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A21" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="10">
+        <v>19</v>
+      </c>
       <c r="C21" s="10">
         <v>0.3</v>
       </c>
-      <c r="D21" s="11"/>
+      <c r="D21" s="11" t="s">
+        <v>74</v>
+      </c>
       <c r="E21" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="F21" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="F21" s="13"/>
       <c r="G21" s="13"/>
       <c r="H21" s="13"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="15" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K21" s="15" t="e">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L21" s="15" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
+      <c r="I21" s="13"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+    </row>
+    <row r="22" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A22" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="10"/>
+      <c r="B22" s="10">
+        <v>19</v>
+      </c>
       <c r="C22" s="10">
         <v>0.3</v>
       </c>
-      <c r="D22" s="11"/>
+      <c r="D22" s="11">
+        <v>90</v>
+      </c>
       <c r="E22" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="F22" s="13" t="str">
+        <v>44</v>
+      </c>
+      <c r="F22" s="13">
         <f t="shared" si="2"/>
-        <v/>
+        <v>3.42</v>
       </c>
       <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="15" t="e">
+      <c r="H22" s="13">
+        <v>2.5</v>
+      </c>
+      <c r="I22" s="13">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>5.92</v>
+      </c>
+      <c r="J22" s="14">
+        <v>16</v>
+      </c>
+      <c r="K22" s="15">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K22" s="15" t="e">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L22" s="15" t="e">
+        <v>10.08</v>
+      </c>
+      <c r="L22" s="15">
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
+        <v>294.73684210526318</v>
+      </c>
+      <c r="M22" s="15">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A23" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="10"/>
+      <c r="B23" s="10">
+        <v>19</v>
+      </c>
       <c r="C23" s="10">
         <v>0.3</v>
       </c>
-      <c r="D23" s="11"/>
+      <c r="D23" s="11">
+        <v>70</v>
+      </c>
       <c r="E23" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="F23" s="13" t="str">
+        <v>44</v>
+      </c>
+      <c r="F23" s="13">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2.66</v>
       </c>
       <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="15" t="e">
+      <c r="H23" s="13">
+        <v>2.5</v>
+      </c>
+      <c r="I23" s="13">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>5.16</v>
+      </c>
+      <c r="J23" s="14">
+        <v>16</v>
+      </c>
+      <c r="K23" s="15">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K23" s="15" t="e">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L23" s="15" t="e">
+        <v>10.84</v>
+      </c>
+      <c r="L23" s="15">
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
+        <v>407.51879699248121</v>
+      </c>
+      <c r="M23" s="15">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
-        <v>52</v>
+        <v>67.75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A24" s="19" t="s">
+        <v>51</v>
       </c>
       <c r="B24" s="10">
         <v>9.09</v>
@@ -2095,7 +2238,7 @@
         <v>300</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F24" s="13">
         <f t="shared" si="2"/>
@@ -2104,28 +2247,32 @@
       <c r="G24" s="13">
         <v>0.52</v>
       </c>
-      <c r="H24" s="17">
+      <c r="H24" s="34">
         <v>0.5</v>
       </c>
-      <c r="I24" s="14">
+      <c r="I24" s="34">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>6.4740000000000002</v>
+      </c>
+      <c r="J24" s="14">
         <v>16</v>
       </c>
-      <c r="J24" s="15">
+      <c r="K24" s="15">
         <f t="shared" si="0"/>
         <v>9.5259999999999998</v>
       </c>
-      <c r="K24" s="15">
+      <c r="L24" s="15">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
         <v>174.66079941327465</v>
       </c>
-      <c r="L24" s="15">
+      <c r="M24" s="15">
         <f t="shared" si="1"/>
         <v>59.537500000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
-        <v>53</v>
+    <row r="25" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A25" s="17" t="s">
+        <v>52</v>
       </c>
       <c r="B25" s="10">
         <v>9.09</v>
@@ -2137,7 +2284,7 @@
         <v>200</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F25" s="13">
         <f t="shared" si="2"/>
@@ -2146,28 +2293,32 @@
       <c r="G25" s="13">
         <v>0.38500000000000001</v>
       </c>
-      <c r="H25" s="17">
+      <c r="H25" s="34">
         <v>1.5</v>
       </c>
-      <c r="I25" s="14">
+      <c r="I25" s="34">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>5.5209999999999999</v>
+      </c>
+      <c r="J25" s="14">
         <v>14</v>
       </c>
-      <c r="J25" s="15">
+      <c r="K25" s="15">
         <f t="shared" si="0"/>
         <v>8.4789999999999992</v>
       </c>
-      <c r="K25" s="15">
+      <c r="L25" s="15">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
         <v>233.19581958195818</v>
       </c>
-      <c r="L25" s="15">
+      <c r="M25" s="15">
         <f t="shared" si="1"/>
         <v>60.564285714285703</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
-        <v>54</v>
+    <row r="26" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A26" s="17" t="s">
+        <v>53</v>
       </c>
       <c r="B26" s="10">
         <v>9.09</v>
@@ -2179,7 +2330,7 @@
         <v>300</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F26" s="13">
         <f t="shared" si="2"/>
@@ -2188,28 +2339,32 @@
       <c r="G26" s="13">
         <v>0.52</v>
       </c>
-      <c r="H26" s="17">
+      <c r="H26" s="34">
         <v>1.5</v>
       </c>
-      <c r="I26" s="14">
+      <c r="I26" s="34">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>7.4740000000000002</v>
+      </c>
+      <c r="J26" s="14">
         <v>18</v>
       </c>
-      <c r="J26" s="15">
+      <c r="K26" s="15">
         <f t="shared" si="0"/>
         <v>10.526</v>
       </c>
-      <c r="K26" s="15">
+      <c r="L26" s="15">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
         <v>192.99596626329301</v>
       </c>
-      <c r="L26" s="15">
+      <c r="M26" s="15">
         <f t="shared" si="1"/>
         <v>58.477777777777774</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="19" t="s">
-        <v>64</v>
+    <row r="27" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A27" s="17" t="s">
+        <v>63</v>
       </c>
       <c r="B27" s="10">
         <v>11.75</v>
@@ -2228,13 +2383,14 @@
       <c r="G27" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H27" s="17" t="s">
+      <c r="H27" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="I27" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="J27" s="15" t="s">
+      <c r="I27" s="34">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>0.82250000000000001</v>
+      </c>
+      <c r="J27" s="14" t="s">
         <v>32</v>
       </c>
       <c r="K27" s="15" t="s">
@@ -2243,10 +2399,13 @@
       <c r="L27" s="15" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="19" t="s">
-        <v>62</v>
+      <c r="M27" s="15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A28" s="17" t="s">
+        <v>61</v>
       </c>
       <c r="B28" s="10">
         <v>9.09</v>
@@ -2258,7 +2417,7 @@
         <v>200</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F28" s="13">
         <f t="shared" si="2"/>
@@ -2267,28 +2426,32 @@
       <c r="G28" s="13">
         <v>0.38500000000000001</v>
       </c>
-      <c r="H28" s="17">
+      <c r="H28" s="34">
         <v>1.2</v>
       </c>
-      <c r="I28" s="14">
+      <c r="I28" s="34">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>5.2210000000000001</v>
+      </c>
+      <c r="J28" s="14">
         <v>14</v>
       </c>
-      <c r="J28" s="15">
+      <c r="K28" s="15">
         <f t="shared" si="0"/>
         <v>8.7789999999999999</v>
       </c>
-      <c r="K28" s="15">
+      <c r="L28" s="15">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
         <v>241.44664466446645</v>
       </c>
-      <c r="L28" s="15">
+      <c r="M28" s="15">
         <f t="shared" si="1"/>
         <v>62.707142857142863</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
-        <v>63</v>
+    <row r="29" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A29" s="17" t="s">
+        <v>62</v>
       </c>
       <c r="B29" s="10">
         <v>9.09</v>
@@ -2300,7 +2463,7 @@
         <v>300</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F29" s="13">
         <f t="shared" si="2"/>
@@ -2309,28 +2472,32 @@
       <c r="G29" s="13">
         <v>0.52</v>
       </c>
-      <c r="H29" s="17">
+      <c r="H29" s="34">
         <v>1.2</v>
       </c>
-      <c r="I29" s="14">
+      <c r="I29" s="34">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>7.1740000000000004</v>
+      </c>
+      <c r="J29" s="14">
         <v>18</v>
       </c>
-      <c r="J29" s="15">
+      <c r="K29" s="15">
         <f t="shared" si="0"/>
         <v>10.826000000000001</v>
       </c>
-      <c r="K29" s="15">
+      <c r="L29" s="15">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
         <v>198.49651631829852</v>
       </c>
-      <c r="L29" s="15">
+      <c r="M29" s="15">
         <f t="shared" si="1"/>
         <v>60.144444444444446</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
-        <v>35</v>
+    <row r="30" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A30" s="17" t="s">
+        <v>73</v>
       </c>
       <c r="B30" s="10">
         <v>2.875</v>
@@ -2338,11 +2505,11 @@
       <c r="C30" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="21">
+      <c r="D30" s="33">
         <v>140</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F30" s="13">
         <f>IF(B30&lt;&gt;"",B30*D30/500,"")</f>
@@ -2352,27 +2519,31 @@
         <v>0.52</v>
       </c>
       <c r="H30" s="13">
-        <v>2.5</v>
-      </c>
-      <c r="I30" s="14">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I30" s="13">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>5.4249999999999998</v>
+      </c>
+      <c r="J30" s="14">
         <v>16</v>
       </c>
-      <c r="J30" s="15">
+      <c r="K30" s="15">
         <f t="shared" si="0"/>
-        <v>12.175000000000001</v>
-      </c>
-      <c r="K30" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>1512.4223602484471</v>
+        <v>10.574999999999999</v>
       </c>
       <c r="L30" s="15">
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
+        <v>1313.6645962732916</v>
+      </c>
+      <c r="M30" s="15">
         <f t="shared" si="1"/>
-        <v>76.09375</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
-        <v>65</v>
+        <v>66.09375</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A31" s="17" t="s">
+        <v>64</v>
       </c>
       <c r="B31" s="10"/>
       <c r="C31" s="10">
@@ -2380,7 +2551,7 @@
       </c>
       <c r="D31" s="11"/>
       <c r="E31" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F31" s="13">
         <v>3.88</v>
@@ -2391,25 +2562,29 @@
       <c r="H31" s="13">
         <v>0.2</v>
       </c>
-      <c r="I31" s="14">
+      <c r="I31" s="13">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>4.4649999999999999</v>
+      </c>
+      <c r="J31" s="14">
         <v>14</v>
       </c>
-      <c r="J31" s="15">
+      <c r="K31" s="15">
         <f t="shared" si="0"/>
         <v>9.5350000000000001</v>
       </c>
-      <c r="K31" s="15">
+      <c r="L31" s="15">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
         <v>245.7474226804124</v>
       </c>
-      <c r="L31" s="15">
+      <c r="M31" s="15">
         <f t="shared" si="1"/>
         <v>68.107142857142861</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
-        <v>66</v>
+    <row r="32" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A32" s="17" t="s">
+        <v>65</v>
       </c>
       <c r="B32" s="10"/>
       <c r="C32" s="10">
@@ -2417,7 +2592,7 @@
       </c>
       <c r="D32" s="11"/>
       <c r="E32" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F32" s="13">
         <v>5.28</v>
@@ -2428,43 +2603,51 @@
       <c r="H32" s="13">
         <v>0.2</v>
       </c>
-      <c r="I32" s="14">
+      <c r="I32" s="13">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>5.8650000000000002</v>
+      </c>
+      <c r="J32" s="14">
         <v>15</v>
       </c>
-      <c r="J32" s="15">
+      <c r="K32" s="15">
         <f t="shared" si="0"/>
         <v>9.1349999999999998</v>
       </c>
-      <c r="K32" s="15">
+      <c r="L32" s="15">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
         <v>173.01136363636363</v>
       </c>
-      <c r="L32" s="15">
+      <c r="M32" s="15">
         <f t="shared" si="1"/>
         <v>60.9</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="B33" s="31"/>
-      <c r="C33" s="31">
+    <row r="33" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A33" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="B33" s="28"/>
+      <c r="C33" s="28">
         <v>0.3</v>
       </c>
-      <c r="D33" s="32"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="34"/>
-      <c r="J33" s="35"/>
-      <c r="K33" s="35"/>
-      <c r="L33" s="35"/>
-    </row>
-    <row r="34" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="19" t="s">
-        <v>67</v>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="31"/>
+      <c r="K33" s="32"/>
+      <c r="L33" s="32"/>
+      <c r="M33" s="32"/>
+    </row>
+    <row r="34" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A34" s="17" t="s">
+        <v>66</v>
       </c>
       <c r="B34" s="10"/>
       <c r="C34" s="10">
@@ -2474,7 +2657,7 @@
         <v>370</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F34" s="13">
         <v>8.9600000000000009</v>
@@ -2485,41 +2668,45 @@
       <c r="H34" s="13">
         <v>0.2</v>
       </c>
-      <c r="I34" s="14">
+      <c r="I34" s="13">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>9.68</v>
+      </c>
+      <c r="J34" s="14">
         <v>24</v>
       </c>
-      <c r="J34" s="15">
+      <c r="K34" s="15">
         <f t="shared" si="0"/>
         <v>14.32</v>
       </c>
-      <c r="K34" s="15">
+      <c r="L34" s="15">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
         <v>159.82142857142856</v>
       </c>
-      <c r="L34" s="15">
+      <c r="M34" s="15">
         <f t="shared" si="1"/>
         <v>59.666666666666671</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="B35" s="36">
-        <v>10</v>
+    <row r="35" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A35" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="35">
+        <v>4.5</v>
       </c>
       <c r="C35" s="10">
         <v>0.3</v>
       </c>
       <c r="D35" s="11">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F35" s="13">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>1.125</v>
       </c>
       <c r="G35" s="13">
         <v>0.52</v>
@@ -2527,24 +2714,28 @@
       <c r="H35" s="13">
         <v>2.5</v>
       </c>
-      <c r="I35" s="14">
+      <c r="I35" s="13">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>4.1449999999999996</v>
+      </c>
+      <c r="J35" s="14">
         <v>16</v>
       </c>
-      <c r="J35" s="15">
+      <c r="K35" s="15">
         <f t="shared" si="0"/>
-        <v>8.98</v>
-      </c>
-      <c r="K35" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>224.5</v>
+        <v>11.855</v>
       </c>
       <c r="L35" s="15">
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
+        <v>1053.7777777777778</v>
+      </c>
+      <c r="M35" s="15">
         <f t="shared" si="1"/>
-        <v>56.125</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
+        <v>74.09375</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A36" s="17" t="s">
         <v>24</v>
       </c>
       <c r="B36" s="10"/>
@@ -2553,7 +2744,7 @@
       </c>
       <c r="D36" s="11"/>
       <c r="E36" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F36" s="13">
         <v>2.84</v>
@@ -2564,61 +2755,67 @@
       <c r="H36" s="13">
         <v>2.5</v>
       </c>
-      <c r="I36" s="14">
+      <c r="I36" s="13">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
+        <v>5.7249999999999996</v>
+      </c>
+      <c r="J36" s="14">
         <v>15</v>
       </c>
-      <c r="J36" s="15">
+      <c r="K36" s="15">
         <f t="shared" si="0"/>
         <v>9.2750000000000004</v>
       </c>
-      <c r="K36" s="15">
+      <c r="L36" s="15">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
         <v>326.58450704225356</v>
       </c>
-      <c r="L36" s="15">
+      <c r="M36" s="15">
         <f t="shared" si="1"/>
         <v>61.833333333333343</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="23"/>
-      <c r="B37" s="24"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="29"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="29"/>
-    </row>
-    <row r="38" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="23"/>
-      <c r="B38" s="24"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="29"/>
-      <c r="K38" s="29"/>
-      <c r="L38" s="29"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A37" s="20"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="24"/>
+      <c r="I37" s="24"/>
+      <c r="J37" s="25"/>
+      <c r="K37" s="26"/>
+      <c r="L37" s="26"/>
+      <c r="M37" s="26"/>
+    </row>
+    <row r="38" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A38" s="20"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
+      <c r="H38" s="24"/>
+      <c r="I38" s="24"/>
+      <c r="J38" s="25"/>
+      <c r="K38" s="26"/>
+      <c r="L38" s="26"/>
+      <c r="M38" s="26"/>
+    </row>
+    <row r="39" spans="1:13">
       <c r="B39" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A40" s="20" t="s">
         <v>71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
+      <c r="A40" s="18" t="s">
+        <v>70</v>
       </c>
       <c r="B40" s="7">
         <v>200</v>
@@ -2630,7 +2827,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:13">
       <c r="B41" s="7">
         <v>160</v>
       </c>
@@ -2641,7 +2838,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:13">
       <c r="B42" s="7">
         <f>(B41/500)*(9.09+0.3)</f>
         <v>3.0048000000000004</v>
@@ -2661,7 +2858,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="L1:L1048576">
+  <conditionalFormatting sqref="M1:M1048576">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -2676,8 +2873,9 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -2693,7 +2891,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>L1:L1048576</xm:sqref>
+          <xm:sqref>M1:M1048576</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/财务与流水/馋唻买-听涛路店商品表.xlsx
+++ b/财务与流水/馋唻买-听涛路店商品表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github localpath\ChanWeiMai\财务与流水\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD531C5-F4C4-499E-A046-49E3E203DD30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F34F32E5-FDA9-4BA0-8851-BC68E1FEB2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -569,48 +569,6 @@
   </cellStyles>
   <dxfs count="13">
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -697,6 +655,48 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
@@ -898,15 +898,15 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="食材成本(元/份)" dataDxfId="7"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="打包成本(元/份)" dataDxfId="6"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="调味品成本(元/份)" dataDxfId="5"/>
-    <tableColumn id="12" xr3:uid="{92F9A26C-6BB3-4CE8-9F14-DEF3C1B8B4F9}" name="合计成本" dataDxfId="0">
+    <tableColumn id="12" xr3:uid="{92F9A26C-6BB3-4CE8-9F14-DEF3C1B8B4F9}" name="合计成本" dataDxfId="4">
       <calculatedColumnFormula>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="售价(元/份)" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="毛利(元/份)" dataDxfId="3"/>
-    <tableColumn id="13" xr3:uid="{550C8CA0-F351-4EDD-8624-328FC6B5B01D}" name="成本利润率(%)" dataDxfId="2">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="售价(元/份)" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="毛利(元/份)" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{550C8CA0-F351-4EDD-8624-328FC6B5B01D}" name="成本利润率(%)" dataDxfId="1">
       <calculatedColumnFormula>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="毛利率(%)" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="毛利率(%)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2712,26 +2712,26 @@
         <v>0.52</v>
       </c>
       <c r="H35" s="13">
-        <v>2.5</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I35" s="13">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
-        <v>4.1449999999999996</v>
+        <v>5.7449999999999992</v>
       </c>
       <c r="J35" s="14">
         <v>16</v>
       </c>
       <c r="K35" s="15">
         <f t="shared" si="0"/>
-        <v>11.855</v>
+        <v>10.255000000000001</v>
       </c>
       <c r="L35" s="15">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>1053.7777777777778</v>
+        <v>911.55555555555554</v>
       </c>
       <c r="M35" s="15">
         <f t="shared" si="1"/>
-        <v>74.09375</v>
+        <v>64.09375</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="18.75" customHeight="1">

--- a/财务与流水/馋唻买-听涛路店商品表.xlsx
+++ b/财务与流水/馋唻买-听涛路店商品表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github localpath\ChanWeiMai\财务与流水\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F34F32E5-FDA9-4BA0-8851-BC68E1FEB2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B6FD92-ED76-4CD1-8E9D-02837507AC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="75">
   <si>
     <t>SKU名称</t>
   </si>
@@ -904,7 +904,7 @@
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="售价(元/份)" dataDxfId="3"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="毛利(元/份)" dataDxfId="2"/>
     <tableColumn id="13" xr3:uid="{550C8CA0-F351-4EDD-8624-328FC6B5B01D}" name="成本利润率(%)" dataDxfId="1">
-      <calculatedColumnFormula>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</calculatedColumnFormula>
+      <calculatedColumnFormula>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="毛利率(%)" dataDxfId="0"/>
   </tableColumns>
@@ -1295,8 +1295,8 @@
         <v>5.1639999999999997</v>
       </c>
       <c r="L2" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>190.41297935103242</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>182.08744710860364</v>
       </c>
       <c r="M2" s="15">
         <f>(J2-(F2+G2+H2))/J2*100</f>
@@ -1334,8 +1334,8 @@
         <v>5.3539999999999992</v>
       </c>
       <c r="L3" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>218.53061224489792</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>202.34315948601656</v>
       </c>
       <c r="M3" s="15">
         <f>(J3-(F3+G3+H3))/J3*100</f>
@@ -1380,8 +1380,8 @@
         <v>2.718</v>
       </c>
       <c r="L4" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>220.61688311688309</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>212.01248049921998</v>
       </c>
       <c r="M4" s="15">
         <f t="shared" ref="M4:M36" si="1">(J4-(F4+G4+H4))/J4*100</f>
@@ -1425,8 +1425,8 @@
         <v>2.98</v>
       </c>
       <c r="L5" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>149</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>147.52475247524751</v>
       </c>
       <c r="M5" s="15">
         <f t="shared" si="1"/>
@@ -1470,8 +1470,8 @@
         <v>2.9800000000000004</v>
       </c>
       <c r="L6" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>59.600000000000009</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>59.362549800796828</v>
       </c>
       <c r="M6" s="15">
         <f t="shared" si="1"/>
@@ -1513,8 +1513,8 @@
         <v>4.74</v>
       </c>
       <c r="L7" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>146.2962962962963</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>145.39877300613497</v>
       </c>
       <c r="M7" s="15">
         <f t="shared" si="1"/>
@@ -1554,7 +1554,7 @@
         <v>0.85</v>
       </c>
       <c r="L8" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>212.5</v>
       </c>
       <c r="M8" s="15">
@@ -1599,7 +1599,7 @@
         <v>0.8</v>
       </c>
       <c r="L9" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>177.7777777777778</v>
       </c>
       <c r="M9" s="15">
@@ -1644,7 +1644,7 @@
         <v>0.62999999999999989</v>
       </c>
       <c r="L10" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>45.985401459854003</v>
       </c>
       <c r="M10" s="15">
@@ -1689,7 +1689,7 @@
         <v>0.62999999999999989</v>
       </c>
       <c r="L11" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>45.985401459854003</v>
       </c>
       <c r="M11" s="15">
@@ -1735,8 +1735,8 @@
         <v>7.6589999999999998</v>
       </c>
       <c r="L12" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>203.91373801916933</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>176.43400138217001</v>
       </c>
       <c r="M12" s="15">
         <f t="shared" si="1"/>
@@ -1781,8 +1781,8 @@
         <v>9.6460000000000008</v>
       </c>
       <c r="L13" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>171.21050763223286</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>151.80988353792887</v>
       </c>
       <c r="M13" s="15">
         <f t="shared" si="1"/>
@@ -1827,8 +1827,8 @@
         <v>9.4149999999999991</v>
       </c>
       <c r="L14" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>235.37499999999997</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>205.34351145038164</v>
       </c>
       <c r="M14" s="15">
         <f t="shared" si="1"/>
@@ -1873,8 +1873,8 @@
         <v>11.280000000000001</v>
       </c>
       <c r="L15" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>188</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>167.85714285714289</v>
       </c>
       <c r="M15" s="15">
         <f t="shared" si="1"/>
@@ -1919,8 +1919,8 @@
         <v>9.4149999999999991</v>
       </c>
       <c r="L16" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>188.29999999999998</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>168.57654431512981</v>
       </c>
       <c r="M16" s="15">
         <f t="shared" si="1"/>
@@ -1965,8 +1965,8 @@
         <v>11.780000000000001</v>
       </c>
       <c r="L17" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>157.06666666666669</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>143.30900243309006</v>
       </c>
       <c r="M17" s="15">
         <f t="shared" si="1"/>
@@ -2011,8 +2011,8 @@
         <v>8.7710000000000008</v>
       </c>
       <c r="L18" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>155.40396881644224</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>140.80911863862579</v>
       </c>
       <c r="M18" s="15">
         <f t="shared" si="1"/>
@@ -2057,8 +2057,8 @@
         <v>12.48</v>
       </c>
       <c r="L19" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>183.52941176470588</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>165.95744680851064</v>
       </c>
       <c r="M19" s="15">
         <f t="shared" si="1"/>
@@ -2103,8 +2103,8 @@
         <v>9.3150000000000013</v>
       </c>
       <c r="L20" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>115.00000000000001</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>107.25388601036272</v>
       </c>
       <c r="M20" s="15">
         <f>(J20-(F20+G20+H20))/J20*100</f>
@@ -2172,8 +2172,8 @@
         <v>10.08</v>
       </c>
       <c r="L22" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>294.73684210526318</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>170.27027027027026</v>
       </c>
       <c r="M22" s="15">
         <f t="shared" si="1"/>
@@ -2216,8 +2216,8 @@
         <v>10.84</v>
       </c>
       <c r="L23" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>407.51879699248121</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>210.07751937984494</v>
       </c>
       <c r="M23" s="15">
         <f t="shared" si="1"/>
@@ -2262,8 +2262,8 @@
         <v>9.5259999999999998</v>
       </c>
       <c r="L24" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>174.66079941327465</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>147.1424158171146</v>
       </c>
       <c r="M24" s="15">
         <f t="shared" si="1"/>
@@ -2308,8 +2308,8 @@
         <v>8.4789999999999992</v>
       </c>
       <c r="L25" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>233.19581958195818</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>153.57725049809815</v>
       </c>
       <c r="M25" s="15">
         <f t="shared" si="1"/>
@@ -2354,8 +2354,8 @@
         <v>10.526</v>
       </c>
       <c r="L26" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>192.99596626329301</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>140.83489430024082</v>
       </c>
       <c r="M26" s="15">
         <f t="shared" si="1"/>
@@ -2396,9 +2396,7 @@
       <c r="K27" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="L27" s="15" t="s">
-        <v>32</v>
-      </c>
+      <c r="L27" s="15"/>
       <c r="M27" s="15" t="s">
         <v>32</v>
       </c>
@@ -2441,8 +2439,8 @@
         <v>8.7789999999999999</v>
       </c>
       <c r="L28" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>241.44664466446645</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>168.14786439379426</v>
       </c>
       <c r="M28" s="15">
         <f t="shared" si="1"/>
@@ -2487,8 +2485,8 @@
         <v>10.826000000000001</v>
       </c>
       <c r="L29" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>198.49651631829852</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>150.90604962364091</v>
       </c>
       <c r="M29" s="15">
         <f t="shared" si="1"/>
@@ -2533,11 +2531,11 @@
         <v>10.574999999999999</v>
       </c>
       <c r="L30" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>1313.6645962732916</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>194.93087557603687</v>
       </c>
       <c r="M30" s="15">
-        <f t="shared" si="1"/>
+        <f>(J30-(F30+G30+H30))/J30*100</f>
         <v>66.09375</v>
       </c>
     </row>
@@ -2574,8 +2572,8 @@
         <v>9.5350000000000001</v>
       </c>
       <c r="L31" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>245.7474226804124</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>213.54983202687569</v>
       </c>
       <c r="M31" s="15">
         <f t="shared" si="1"/>
@@ -2615,8 +2613,8 @@
         <v>9.1349999999999998</v>
       </c>
       <c r="L32" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>173.01136363636363</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>155.7544757033248</v>
       </c>
       <c r="M32" s="15">
         <f t="shared" si="1"/>
@@ -2642,7 +2640,7 @@
       </c>
       <c r="J33" s="31"/>
       <c r="K33" s="32"/>
-      <c r="L33" s="32"/>
+      <c r="L33" s="15"/>
       <c r="M33" s="32"/>
     </row>
     <row r="34" spans="1:13" ht="18.75" customHeight="1">
@@ -2680,8 +2678,8 @@
         <v>14.32</v>
       </c>
       <c r="L34" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>159.82142857142856</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>147.93388429752068</v>
       </c>
       <c r="M34" s="15">
         <f t="shared" si="1"/>
@@ -2722,12 +2720,12 @@
         <v>16</v>
       </c>
       <c r="K35" s="15">
-        <f t="shared" si="0"/>
+        <f>J35-(F35+G35+H35)</f>
         <v>10.255000000000001</v>
       </c>
       <c r="L35" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>911.55555555555554</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>178.50304612706705</v>
       </c>
       <c r="M35" s="15">
         <f t="shared" si="1"/>
@@ -2763,12 +2761,12 @@
         <v>15</v>
       </c>
       <c r="K36" s="15">
-        <f t="shared" si="0"/>
+        <f>J36-(F36+G36+H36)</f>
         <v>9.2750000000000004</v>
       </c>
       <c r="L36" s="15">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[食材成本(元/份)]]*100</f>
-        <v>326.58450704225356</v>
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
+        <v>162.00873362445415</v>
       </c>
       <c r="M36" s="15">
         <f t="shared" si="1"/>

--- a/财务与流水/馋唻买-听涛路店商品表.xlsx
+++ b/财务与流水/馋唻买-听涛路店商品表.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="71">
   <si>
     <t>SKU名称</t>
   </si>
@@ -227,15 +227,6 @@
   </si>
   <si>
     <t>火鸡面、瘦肉丸、调味品</t>
-  </si>
-  <si>
-    <t>瘦肉丸</t>
-  </si>
-  <si>
-    <t>牛肉</t>
-  </si>
-  <si>
-    <t>三拼含量</t>
   </si>
 </sst>
 </file>
@@ -245,12 +236,12 @@
   <numFmts count="6">
     <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -262,13 +253,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -326,44 +310,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -377,9 +331,56 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -399,24 +400,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -430,6 +423,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -437,37 +445,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="37">
     <fill>
@@ -502,187 +479,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -724,15 +701,62 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -753,210 +777,163 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -977,88 +954,67 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1701,7 +1657,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="30.5" style="2" customWidth="1"/>
@@ -1734,28 +1690,28 @@
       <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="I1" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="29" t="s">
+      <c r="J1" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="K1" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="L1" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="22" t="s">
+      <c r="M1" s="19" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1772,33 +1728,33 @@
       <c r="D2" s="12">
         <v>120</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="21">
         <f>(B2+SKUTable[[#This Row],[运费(元/500g)]])*D2/500</f>
         <v>2.712</v>
       </c>
-      <c r="G2" s="24">
+      <c r="G2" s="21">
         <v>0.124</v>
       </c>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24">
+      <c r="H2" s="21"/>
+      <c r="I2" s="21">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>2.836</v>
       </c>
-      <c r="J2" s="30">
+      <c r="J2" s="25">
         <v>8</v>
       </c>
-      <c r="K2" s="31">
+      <c r="K2" s="26">
         <f>J2-(F2+G2+H2)</f>
         <v>5.164</v>
       </c>
-      <c r="L2" s="31">
+      <c r="L2" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>182.087447108604</v>
       </c>
-      <c r="M2" s="31">
+      <c r="M2" s="26">
         <f>(J2-(F2+G2+H2))/J2*100</f>
         <v>64.55</v>
       </c>
@@ -1812,32 +1768,32 @@
       <c r="D3" s="12">
         <v>220</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="21">
         <v>2.45</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="21">
         <v>0.196</v>
       </c>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24">
+      <c r="H3" s="21"/>
+      <c r="I3" s="21">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>2.646</v>
       </c>
-      <c r="J3" s="30">
+      <c r="J3" s="25">
         <v>8</v>
       </c>
-      <c r="K3" s="31">
+      <c r="K3" s="26">
         <f>J3-(F3+G3+H3)</f>
         <v>5.354</v>
       </c>
-      <c r="L3" s="31">
+      <c r="L3" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>202.343159486017</v>
       </c>
-      <c r="M3" s="31">
+      <c r="M3" s="26">
         <f>(J3-(F3+G3+H3))/J3*100</f>
         <v>66.925</v>
       </c>
@@ -1855,35 +1811,35 @@
       <c r="D4" s="12">
         <v>70</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="21">
         <f>(B4+SKUTable[[#This Row],[运费(元/500g)]])*D4/500</f>
         <v>1.232</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="21">
         <v>0.05</v>
       </c>
-      <c r="H4" s="24">
+      <c r="H4" s="21">
         <v>0</v>
       </c>
-      <c r="I4" s="24">
+      <c r="I4" s="21">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>1.282</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="25">
         <v>4</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="26">
         <f t="shared" ref="K4:K36" si="0">J4-(F4+G4+H4)</f>
         <v>2.718</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>212.01248049922</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M4" s="26">
         <f t="shared" ref="M4:M36" si="1">(J4-(F4+G4+H4))/J4*100</f>
         <v>67.95</v>
       </c>
@@ -1901,34 +1857,34 @@
       <c r="D5" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="21">
         <v>2</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="21">
         <v>0.02</v>
       </c>
-      <c r="H5" s="24">
+      <c r="H5" s="21">
         <v>0</v>
       </c>
-      <c r="I5" s="24">
+      <c r="I5" s="21">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>2.02</v>
       </c>
-      <c r="J5" s="30">
+      <c r="J5" s="25">
         <v>5</v>
       </c>
-      <c r="K5" s="31">
+      <c r="K5" s="26">
         <f t="shared" si="0"/>
         <v>2.98</v>
       </c>
-      <c r="L5" s="31">
+      <c r="L5" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>147.524752475248</v>
       </c>
-      <c r="M5" s="31">
+      <c r="M5" s="26">
         <f t="shared" si="1"/>
         <v>59.6</v>
       </c>
@@ -1946,34 +1902,34 @@
       <c r="D6" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="21">
         <v>5</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="21">
         <v>0.02</v>
       </c>
-      <c r="H6" s="24">
+      <c r="H6" s="21">
         <v>0</v>
       </c>
-      <c r="I6" s="24">
+      <c r="I6" s="21">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>5.02</v>
       </c>
-      <c r="J6" s="30">
+      <c r="J6" s="25">
         <v>8</v>
       </c>
-      <c r="K6" s="31">
+      <c r="K6" s="26">
         <f t="shared" si="0"/>
         <v>2.98</v>
       </c>
-      <c r="L6" s="31">
+      <c r="L6" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>59.3625498007968</v>
       </c>
-      <c r="M6" s="31">
+      <c r="M6" s="26">
         <f t="shared" si="1"/>
         <v>37.25</v>
       </c>
@@ -1991,32 +1947,32 @@
       <c r="D7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E7" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="21">
         <v>3.24</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="21">
         <v>0.02</v>
       </c>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24">
+      <c r="H7" s="21"/>
+      <c r="I7" s="21">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>3.26</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="25">
         <v>8</v>
       </c>
-      <c r="K7" s="31">
+      <c r="K7" s="26">
         <f t="shared" si="0"/>
         <v>4.74</v>
       </c>
-      <c r="L7" s="31">
+      <c r="L7" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>145.398773006135</v>
       </c>
-      <c r="M7" s="31">
+      <c r="M7" s="26">
         <f t="shared" si="1"/>
         <v>59.25</v>
       </c>
@@ -2034,30 +1990,30 @@
       <c r="D8" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="23" t="s">
+      <c r="E8" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="21">
         <v>0.4</v>
       </c>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="24">
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>0.4</v>
       </c>
-      <c r="J8" s="30">
+      <c r="J8" s="25">
         <v>1.25</v>
       </c>
-      <c r="K8" s="31">
+      <c r="K8" s="26">
         <f t="shared" si="0"/>
         <v>0.85</v>
       </c>
-      <c r="L8" s="31">
+      <c r="L8" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>212.5</v>
       </c>
-      <c r="M8" s="31">
+      <c r="M8" s="26">
         <f t="shared" si="1"/>
         <v>68</v>
       </c>
@@ -2075,34 +2031,34 @@
       <c r="D9" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="23" t="s">
+      <c r="E9" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="21">
         <v>0.45</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="21">
         <v>0</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="21">
         <v>0</v>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="21">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>0.45</v>
       </c>
-      <c r="J9" s="30">
+      <c r="J9" s="25">
         <v>1.25</v>
       </c>
-      <c r="K9" s="31">
+      <c r="K9" s="26">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="L9" s="31">
+      <c r="L9" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>177.777777777778</v>
       </c>
-      <c r="M9" s="31">
+      <c r="M9" s="26">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
@@ -2120,34 +2076,34 @@
       <c r="D10" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="23" t="s">
+      <c r="E10" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="21">
         <v>1.37</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="21">
         <v>0</v>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="21">
         <v>0</v>
       </c>
-      <c r="I10" s="24">
+      <c r="I10" s="21">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>1.37</v>
       </c>
-      <c r="J10" s="30">
+      <c r="J10" s="25">
         <v>2</v>
       </c>
-      <c r="K10" s="31">
+      <c r="K10" s="26">
         <f t="shared" si="0"/>
         <v>0.63</v>
       </c>
-      <c r="L10" s="31">
+      <c r="L10" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>45.985401459854</v>
       </c>
-      <c r="M10" s="31">
+      <c r="M10" s="26">
         <f t="shared" si="1"/>
         <v>31.5</v>
       </c>
@@ -2165,34 +2121,34 @@
       <c r="D11" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="23" t="s">
+      <c r="E11" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="21">
         <v>1.37</v>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="21">
         <v>0</v>
       </c>
-      <c r="H11" s="24">
+      <c r="H11" s="21">
         <v>0</v>
       </c>
-      <c r="I11" s="24">
+      <c r="I11" s="21">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>1.37</v>
       </c>
-      <c r="J11" s="30">
+      <c r="J11" s="25">
         <v>2</v>
       </c>
-      <c r="K11" s="31">
+      <c r="K11" s="26">
         <f t="shared" si="0"/>
         <v>0.63</v>
       </c>
-      <c r="L11" s="31">
+      <c r="L11" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>45.985401459854</v>
       </c>
-      <c r="M11" s="31">
+      <c r="M11" s="26">
         <f t="shared" si="1"/>
         <v>31.5</v>
       </c>
@@ -2210,35 +2166,35 @@
       <c r="D12" s="12">
         <v>200</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="21">
         <f>(B12+SKUTable[[#This Row],[运费(元/500g)]])*D12/500</f>
         <v>3.756</v>
       </c>
-      <c r="G12" s="24">
+      <c r="G12" s="21">
         <v>0.385</v>
       </c>
-      <c r="H12" s="24">
+      <c r="H12" s="21">
         <v>0.2</v>
       </c>
-      <c r="I12" s="24">
+      <c r="I12" s="21">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>4.341</v>
       </c>
-      <c r="J12" s="30">
+      <c r="J12" s="25">
         <v>12</v>
       </c>
-      <c r="K12" s="31">
+      <c r="K12" s="26">
         <f t="shared" si="0"/>
         <v>7.659</v>
       </c>
-      <c r="L12" s="31">
+      <c r="L12" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>176.43400138217</v>
       </c>
-      <c r="M12" s="31">
+      <c r="M12" s="26">
         <f t="shared" si="1"/>
         <v>63.825</v>
       </c>
@@ -2256,35 +2212,35 @@
       <c r="D13" s="12">
         <v>300</v>
       </c>
-      <c r="E13" s="23" t="s">
+      <c r="E13" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="21">
         <f>(B13+SKUTable[[#This Row],[运费(元/500g)]])*D13/500</f>
         <v>5.634</v>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="21">
         <v>0.52</v>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="21">
         <v>0.2</v>
       </c>
-      <c r="I13" s="24">
+      <c r="I13" s="21">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>6.354</v>
       </c>
-      <c r="J13" s="30">
+      <c r="J13" s="25">
         <v>16</v>
       </c>
-      <c r="K13" s="31">
+      <c r="K13" s="26">
         <f t="shared" si="0"/>
         <v>9.646</v>
       </c>
-      <c r="L13" s="31">
+      <c r="L13" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>151.809883537929</v>
       </c>
-      <c r="M13" s="31">
+      <c r="M13" s="26">
         <f t="shared" si="1"/>
         <v>60.2875</v>
       </c>
@@ -2302,35 +2258,35 @@
       <c r="D14" s="12">
         <v>200</v>
       </c>
-      <c r="E14" s="23" t="s">
+      <c r="E14" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="21">
         <f>IF(B14&lt;&gt;"",B14*D14/500,"")</f>
         <v>4</v>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="21">
         <v>0.385</v>
       </c>
-      <c r="H14" s="24">
+      <c r="H14" s="21">
         <v>0.2</v>
       </c>
-      <c r="I14" s="24">
+      <c r="I14" s="21">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>4.585</v>
       </c>
-      <c r="J14" s="30">
+      <c r="J14" s="25">
         <v>14</v>
       </c>
-      <c r="K14" s="31">
+      <c r="K14" s="26">
         <f t="shared" si="0"/>
         <v>9.415</v>
       </c>
-      <c r="L14" s="31">
+      <c r="L14" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>205.343511450382</v>
       </c>
-      <c r="M14" s="31">
+      <c r="M14" s="26">
         <f t="shared" si="1"/>
         <v>67.25</v>
       </c>
@@ -2348,35 +2304,35 @@
       <c r="D15" s="12">
         <v>300</v>
       </c>
-      <c r="E15" s="23" t="s">
+      <c r="E15" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="21">
         <f>IF(B15&lt;&gt;"",B15*D15/500,"")</f>
         <v>6</v>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="21">
         <v>0.52</v>
       </c>
-      <c r="H15" s="24">
+      <c r="H15" s="21">
         <v>0.2</v>
       </c>
-      <c r="I15" s="24">
+      <c r="I15" s="21">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>6.72</v>
       </c>
-      <c r="J15" s="30">
+      <c r="J15" s="25">
         <v>18</v>
       </c>
-      <c r="K15" s="31">
+      <c r="K15" s="26">
         <f t="shared" si="0"/>
         <v>11.28</v>
       </c>
-      <c r="L15" s="31">
+      <c r="L15" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>167.857142857143</v>
       </c>
-      <c r="M15" s="31">
+      <c r="M15" s="26">
         <f t="shared" si="1"/>
         <v>62.6666666666667</v>
       </c>
@@ -2394,35 +2350,35 @@
       <c r="D16" s="12">
         <v>200</v>
       </c>
-      <c r="E16" s="23" t="s">
+      <c r="E16" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="21">
         <f>IF(B16&lt;&gt;"",B16*D16/500,"")</f>
         <v>5</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="21">
         <v>0.385</v>
       </c>
-      <c r="H16" s="24">
+      <c r="H16" s="21">
         <v>0.2</v>
       </c>
-      <c r="I16" s="24">
+      <c r="I16" s="21">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>5.585</v>
       </c>
-      <c r="J16" s="30">
+      <c r="J16" s="25">
         <v>15</v>
       </c>
-      <c r="K16" s="31">
+      <c r="K16" s="26">
         <f t="shared" si="0"/>
         <v>9.415</v>
       </c>
-      <c r="L16" s="31">
+      <c r="L16" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>168.57654431513</v>
       </c>
-      <c r="M16" s="31">
+      <c r="M16" s="26">
         <f t="shared" si="1"/>
         <v>62.7666666666667</v>
       </c>
@@ -2440,35 +2396,35 @@
       <c r="D17" s="12">
         <v>300</v>
       </c>
-      <c r="E17" s="23" t="s">
+      <c r="E17" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="21">
         <f>IF(B17&lt;&gt;"",B17*D17/500,"")</f>
         <v>7.5</v>
       </c>
-      <c r="G17" s="24">
+      <c r="G17" s="21">
         <v>0.52</v>
       </c>
-      <c r="H17" s="24">
+      <c r="H17" s="21">
         <v>0.2</v>
       </c>
-      <c r="I17" s="24">
+      <c r="I17" s="21">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>8.22</v>
       </c>
-      <c r="J17" s="30">
+      <c r="J17" s="25">
         <v>20</v>
       </c>
-      <c r="K17" s="31">
+      <c r="K17" s="26">
         <f t="shared" si="0"/>
         <v>11.78</v>
       </c>
-      <c r="L17" s="31">
+      <c r="L17" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>143.30900243309</v>
       </c>
-      <c r="M17" s="31">
+      <c r="M17" s="26">
         <f t="shared" si="1"/>
         <v>58.9</v>
       </c>
@@ -2486,35 +2442,35 @@
       <c r="D18" s="12">
         <v>166</v>
       </c>
-      <c r="E18" s="23" t="s">
+      <c r="E18" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="21">
         <f t="shared" ref="F18:F35" si="2">IF(B18&lt;&gt;"",B18*D18/500,"")</f>
         <v>5.644</v>
       </c>
-      <c r="G18" s="24">
+      <c r="G18" s="21">
         <v>0.385</v>
       </c>
-      <c r="H18" s="24">
+      <c r="H18" s="21">
         <v>0.2</v>
       </c>
-      <c r="I18" s="24">
+      <c r="I18" s="21">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>6.229</v>
       </c>
-      <c r="J18" s="30">
+      <c r="J18" s="25">
         <v>15</v>
       </c>
-      <c r="K18" s="31">
+      <c r="K18" s="26">
         <f t="shared" si="0"/>
         <v>8.771</v>
       </c>
-      <c r="L18" s="31">
+      <c r="L18" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>140.809118638626</v>
       </c>
-      <c r="M18" s="31">
+      <c r="M18" s="26">
         <f t="shared" si="1"/>
         <v>58.4733333333333</v>
       </c>
@@ -2532,35 +2488,35 @@
       <c r="D19" s="12">
         <v>200</v>
       </c>
-      <c r="E19" s="23" t="s">
+      <c r="E19" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="21">
         <f t="shared" si="2"/>
         <v>6.8</v>
       </c>
-      <c r="G19" s="24">
+      <c r="G19" s="21">
         <v>0.52</v>
       </c>
-      <c r="H19" s="24">
+      <c r="H19" s="21">
         <v>0.2</v>
       </c>
-      <c r="I19" s="24">
+      <c r="I19" s="21">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>7.52</v>
       </c>
-      <c r="J19" s="30">
+      <c r="J19" s="25">
         <v>20</v>
       </c>
-      <c r="K19" s="31">
+      <c r="K19" s="26">
         <f t="shared" si="0"/>
         <v>12.48</v>
       </c>
-      <c r="L19" s="31">
+      <c r="L19" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>165.957446808511</v>
       </c>
-      <c r="M19" s="31">
+      <c r="M19" s="26">
         <f t="shared" si="1"/>
         <v>62.4</v>
       </c>
@@ -2578,35 +2534,35 @@
       <c r="D20" s="12">
         <v>100</v>
       </c>
-      <c r="E20" s="23" t="s">
+      <c r="E20" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="21">
         <f t="shared" si="2"/>
         <v>4.5</v>
       </c>
-      <c r="G20" s="24">
+      <c r="G20" s="21">
         <v>0.385</v>
       </c>
-      <c r="H20" s="24">
+      <c r="H20" s="21">
         <v>0.2</v>
       </c>
-      <c r="I20" s="24">
+      <c r="I20" s="21">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>5.085</v>
       </c>
-      <c r="J20" s="30">
+      <c r="J20" s="25">
         <v>18</v>
       </c>
-      <c r="K20" s="31">
+      <c r="K20" s="26">
         <f t="shared" si="0"/>
         <v>12.915</v>
       </c>
-      <c r="L20" s="31">
+      <c r="L20" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>253.982300884956</v>
       </c>
-      <c r="M20" s="31">
+      <c r="M20" s="26">
         <f t="shared" si="1"/>
         <v>71.75</v>
       </c>
@@ -2624,17 +2580,17 @@
       <c r="D21" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="23" t="s">
+      <c r="E21" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="31"/>
-      <c r="L21" s="31"/>
-      <c r="M21" s="31"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="26"/>
+      <c r="M21" s="26"/>
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:13">
       <c r="A22" s="13" t="s">
@@ -2649,33 +2605,33 @@
       <c r="D22" s="12">
         <v>90</v>
       </c>
-      <c r="E22" s="23" t="s">
+      <c r="E22" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="21">
         <f t="shared" si="2"/>
         <v>3.42</v>
       </c>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24">
+      <c r="G22" s="21"/>
+      <c r="H22" s="21">
         <v>2.5</v>
       </c>
-      <c r="I22" s="24">
+      <c r="I22" s="21">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>5.92</v>
       </c>
-      <c r="J22" s="30">
+      <c r="J22" s="25">
         <v>16</v>
       </c>
-      <c r="K22" s="31">
+      <c r="K22" s="26">
         <f t="shared" si="0"/>
         <v>10.08</v>
       </c>
-      <c r="L22" s="31">
+      <c r="L22" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>170.27027027027</v>
       </c>
-      <c r="M22" s="31">
+      <c r="M22" s="26">
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
@@ -2693,33 +2649,33 @@
       <c r="D23" s="12">
         <v>70</v>
       </c>
-      <c r="E23" s="23" t="s">
+      <c r="E23" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F23" s="24">
+      <c r="F23" s="21">
         <f t="shared" si="2"/>
         <v>2.66</v>
       </c>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24">
+      <c r="G23" s="21"/>
+      <c r="H23" s="21">
         <v>2.5</v>
       </c>
-      <c r="I23" s="24">
+      <c r="I23" s="21">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>5.16</v>
       </c>
-      <c r="J23" s="30">
+      <c r="J23" s="25">
         <v>16</v>
       </c>
-      <c r="K23" s="31">
+      <c r="K23" s="26">
         <f t="shared" si="0"/>
         <v>10.84</v>
       </c>
-      <c r="L23" s="31">
+      <c r="L23" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>210.077519379845</v>
       </c>
-      <c r="M23" s="31">
+      <c r="M23" s="26">
         <f t="shared" si="1"/>
         <v>67.75</v>
       </c>
@@ -2737,35 +2693,35 @@
       <c r="D24" s="12">
         <v>300</v>
       </c>
-      <c r="E24" s="23" t="s">
+      <c r="E24" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="F24" s="24">
+      <c r="F24" s="21">
         <f t="shared" si="2"/>
         <v>5.454</v>
       </c>
-      <c r="G24" s="24">
+      <c r="G24" s="21">
         <v>0.52</v>
       </c>
-      <c r="H24" s="25">
+      <c r="H24" s="22">
         <v>0.5</v>
       </c>
-      <c r="I24" s="25">
+      <c r="I24" s="22">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>6.474</v>
       </c>
-      <c r="J24" s="30">
+      <c r="J24" s="25">
         <v>16</v>
       </c>
-      <c r="K24" s="31">
+      <c r="K24" s="26">
         <f t="shared" si="0"/>
         <v>9.526</v>
       </c>
-      <c r="L24" s="31">
+      <c r="L24" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>147.142415817115</v>
       </c>
-      <c r="M24" s="31">
+      <c r="M24" s="26">
         <f t="shared" si="1"/>
         <v>59.5375</v>
       </c>
@@ -2783,35 +2739,35 @@
       <c r="D25" s="12">
         <v>200</v>
       </c>
-      <c r="E25" s="23" t="s">
+      <c r="E25" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="F25" s="24">
+      <c r="F25" s="21">
         <f t="shared" si="2"/>
         <v>3.636</v>
       </c>
-      <c r="G25" s="24">
+      <c r="G25" s="21">
         <v>0.385</v>
       </c>
-      <c r="H25" s="25">
+      <c r="H25" s="22">
         <v>1.5</v>
       </c>
-      <c r="I25" s="25">
+      <c r="I25" s="22">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>5.521</v>
       </c>
-      <c r="J25" s="30">
+      <c r="J25" s="25">
         <v>14</v>
       </c>
-      <c r="K25" s="31">
+      <c r="K25" s="26">
         <f t="shared" si="0"/>
         <v>8.479</v>
       </c>
-      <c r="L25" s="31">
+      <c r="L25" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>153.577250498098</v>
       </c>
-      <c r="M25" s="31">
+      <c r="M25" s="26">
         <f t="shared" si="1"/>
         <v>60.5642857142857</v>
       </c>
@@ -2829,35 +2785,35 @@
       <c r="D26" s="12">
         <v>300</v>
       </c>
-      <c r="E26" s="23" t="s">
+      <c r="E26" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="F26" s="24">
+      <c r="F26" s="21">
         <f t="shared" si="2"/>
         <v>5.454</v>
       </c>
-      <c r="G26" s="24">
+      <c r="G26" s="21">
         <v>0.52</v>
       </c>
-      <c r="H26" s="25">
+      <c r="H26" s="22">
         <v>1.5</v>
       </c>
-      <c r="I26" s="25">
+      <c r="I26" s="22">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>7.474</v>
       </c>
-      <c r="J26" s="30">
+      <c r="J26" s="25">
         <v>18</v>
       </c>
-      <c r="K26" s="31">
+      <c r="K26" s="26">
         <f t="shared" si="0"/>
         <v>10.526</v>
       </c>
-      <c r="L26" s="31">
+      <c r="L26" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>140.834894300241</v>
       </c>
-      <c r="M26" s="31">
+      <c r="M26" s="26">
         <f t="shared" si="1"/>
         <v>58.4777777777778</v>
       </c>
@@ -2876,28 +2832,28 @@
         <v>35</v>
       </c>
       <c r="E27" s="12"/>
-      <c r="F27" s="24">
+      <c r="F27" s="21">
         <f t="shared" si="2"/>
         <v>0.8225</v>
       </c>
-      <c r="G27" s="24" t="s">
+      <c r="G27" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="H27" s="25" t="s">
+      <c r="H27" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="I27" s="25">
+      <c r="I27" s="22">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>0.8225</v>
       </c>
-      <c r="J27" s="30" t="s">
+      <c r="J27" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="K27" s="31" t="s">
+      <c r="K27" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="L27" s="31"/>
-      <c r="M27" s="31" t="s">
+      <c r="L27" s="26"/>
+      <c r="M27" s="26" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2914,35 +2870,35 @@
       <c r="D28" s="12">
         <v>200</v>
       </c>
-      <c r="E28" s="23" t="s">
+      <c r="E28" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="F28" s="24">
+      <c r="F28" s="21">
         <f t="shared" si="2"/>
         <v>3.636</v>
       </c>
-      <c r="G28" s="24">
+      <c r="G28" s="21">
         <v>0.385</v>
       </c>
-      <c r="H28" s="25">
+      <c r="H28" s="22">
         <v>1.2</v>
       </c>
-      <c r="I28" s="25">
+      <c r="I28" s="22">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>5.221</v>
       </c>
-      <c r="J28" s="30">
+      <c r="J28" s="25">
         <v>14</v>
       </c>
-      <c r="K28" s="31">
+      <c r="K28" s="26">
         <f t="shared" si="0"/>
         <v>8.779</v>
       </c>
-      <c r="L28" s="31">
+      <c r="L28" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>168.147864393794</v>
       </c>
-      <c r="M28" s="31">
+      <c r="M28" s="26">
         <f t="shared" si="1"/>
         <v>62.7071428571429</v>
       </c>
@@ -2960,35 +2916,35 @@
       <c r="D29" s="12">
         <v>300</v>
       </c>
-      <c r="E29" s="23" t="s">
+      <c r="E29" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="F29" s="24">
+      <c r="F29" s="21">
         <f t="shared" si="2"/>
         <v>5.454</v>
       </c>
-      <c r="G29" s="24">
+      <c r="G29" s="21">
         <v>0.52</v>
       </c>
-      <c r="H29" s="25">
+      <c r="H29" s="22">
         <v>1.2</v>
       </c>
-      <c r="I29" s="25">
+      <c r="I29" s="22">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>7.174</v>
       </c>
-      <c r="J29" s="30">
+      <c r="J29" s="25">
         <v>18</v>
       </c>
-      <c r="K29" s="31">
+      <c r="K29" s="26">
         <f t="shared" si="0"/>
         <v>10.826</v>
       </c>
-      <c r="L29" s="31">
+      <c r="L29" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>150.906049623641</v>
       </c>
-      <c r="M29" s="31">
+      <c r="M29" s="26">
         <f t="shared" si="1"/>
         <v>60.1444444444444</v>
       </c>
@@ -3006,35 +2962,35 @@
       <c r="D30" s="14">
         <v>140</v>
       </c>
-      <c r="E30" s="23" t="s">
+      <c r="E30" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="F30" s="24">
+      <c r="F30" s="21">
         <f t="shared" si="2"/>
         <v>0.805</v>
       </c>
-      <c r="G30" s="24">
+      <c r="G30" s="21">
         <v>0.52</v>
       </c>
-      <c r="H30" s="24">
+      <c r="H30" s="21">
         <v>4.1</v>
       </c>
-      <c r="I30" s="24">
+      <c r="I30" s="21">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>5.425</v>
       </c>
-      <c r="J30" s="30">
+      <c r="J30" s="25">
         <v>16</v>
       </c>
-      <c r="K30" s="31">
+      <c r="K30" s="26">
         <f t="shared" si="0"/>
         <v>10.575</v>
       </c>
-      <c r="L30" s="31">
+      <c r="L30" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>194.930875576037</v>
       </c>
-      <c r="M30" s="31">
+      <c r="M30" s="26">
         <f t="shared" si="1"/>
         <v>66.09375</v>
       </c>
@@ -3048,34 +3004,34 @@
         <v>0.3</v>
       </c>
       <c r="D31" s="12"/>
-      <c r="E31" s="23" t="s">
+      <c r="E31" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="F31" s="24">
+      <c r="F31" s="21">
         <v>3.88</v>
       </c>
-      <c r="G31" s="24">
+      <c r="G31" s="21">
         <v>0.385</v>
       </c>
-      <c r="H31" s="24">
+      <c r="H31" s="21">
         <v>0.2</v>
       </c>
-      <c r="I31" s="24">
+      <c r="I31" s="21">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>4.465</v>
       </c>
-      <c r="J31" s="30">
+      <c r="J31" s="25">
         <v>14</v>
       </c>
-      <c r="K31" s="31">
+      <c r="K31" s="26">
         <f t="shared" si="0"/>
         <v>9.535</v>
       </c>
-      <c r="L31" s="31">
+      <c r="L31" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>213.549832026876</v>
       </c>
-      <c r="M31" s="31">
+      <c r="M31" s="26">
         <f t="shared" si="1"/>
         <v>68.1071428571429</v>
       </c>
@@ -3089,34 +3045,34 @@
         <v>0.3</v>
       </c>
       <c r="D32" s="12"/>
-      <c r="E32" s="23" t="s">
+      <c r="E32" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="F32" s="24">
+      <c r="F32" s="21">
         <v>5.28</v>
       </c>
-      <c r="G32" s="24">
+      <c r="G32" s="21">
         <v>0.385</v>
       </c>
-      <c r="H32" s="24">
+      <c r="H32" s="21">
         <v>0.2</v>
       </c>
-      <c r="I32" s="24">
+      <c r="I32" s="21">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>5.865</v>
       </c>
-      <c r="J32" s="30">
+      <c r="J32" s="25">
         <v>15</v>
       </c>
-      <c r="K32" s="31">
+      <c r="K32" s="26">
         <f t="shared" si="0"/>
         <v>9.135</v>
       </c>
-      <c r="L32" s="31">
+      <c r="L32" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>155.754475703325</v>
       </c>
-      <c r="M32" s="31">
+      <c r="M32" s="26">
         <f t="shared" si="1"/>
         <v>60.9</v>
       </c>
@@ -3131,17 +3087,17 @@
       </c>
       <c r="D33" s="17"/>
       <c r="E33" s="17"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26">
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="23">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>0</v>
       </c>
-      <c r="J33" s="32"/>
-      <c r="K33" s="33"/>
-      <c r="L33" s="31"/>
-      <c r="M33" s="33"/>
+      <c r="J33" s="27"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="26"/>
+      <c r="M33" s="28"/>
     </row>
     <row r="34" ht="18.75" customHeight="1" spans="1:13">
       <c r="A34" s="10" t="s">
@@ -3154,34 +3110,34 @@
       <c r="D34" s="12">
         <v>370</v>
       </c>
-      <c r="E34" s="23" t="s">
+      <c r="E34" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="F34" s="24">
+      <c r="F34" s="21">
         <v>8.96</v>
       </c>
-      <c r="G34" s="24">
+      <c r="G34" s="21">
         <v>0.52</v>
       </c>
-      <c r="H34" s="24">
+      <c r="H34" s="21">
         <v>0.2</v>
       </c>
-      <c r="I34" s="24">
+      <c r="I34" s="21">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>9.68</v>
       </c>
-      <c r="J34" s="30">
+      <c r="J34" s="25">
         <v>24</v>
       </c>
-      <c r="K34" s="31">
+      <c r="K34" s="26">
         <f t="shared" si="0"/>
         <v>14.32</v>
       </c>
-      <c r="L34" s="31">
+      <c r="L34" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>147.933884297521</v>
       </c>
-      <c r="M34" s="31">
+      <c r="M34" s="26">
         <f t="shared" si="1"/>
         <v>59.6666666666667</v>
       </c>
@@ -3199,35 +3155,35 @@
       <c r="D35" s="12">
         <v>125</v>
       </c>
-      <c r="E35" s="23" t="s">
+      <c r="E35" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="F35" s="24">
+      <c r="F35" s="21">
         <f t="shared" si="2"/>
         <v>1.125</v>
       </c>
-      <c r="G35" s="24">
+      <c r="G35" s="21">
         <v>0.52</v>
       </c>
-      <c r="H35" s="24">
+      <c r="H35" s="21">
         <v>4.1</v>
       </c>
-      <c r="I35" s="24">
+      <c r="I35" s="21">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>5.745</v>
       </c>
-      <c r="J35" s="30">
+      <c r="J35" s="25">
         <v>16</v>
       </c>
-      <c r="K35" s="31">
+      <c r="K35" s="26">
         <f t="shared" si="0"/>
         <v>10.255</v>
       </c>
-      <c r="L35" s="31">
+      <c r="L35" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>178.503046127067</v>
       </c>
-      <c r="M35" s="31">
+      <c r="M35" s="26">
         <f t="shared" si="1"/>
         <v>64.09375</v>
       </c>
@@ -3241,118 +3197,40 @@
         <v>0.3</v>
       </c>
       <c r="D36" s="12"/>
-      <c r="E36" s="23" t="s">
+      <c r="E36" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="F36" s="24">
+      <c r="F36" s="21">
         <v>2.84</v>
       </c>
-      <c r="G36" s="24">
+      <c r="G36" s="21">
         <v>0.385</v>
       </c>
-      <c r="H36" s="24">
+      <c r="H36" s="21">
         <v>2.5</v>
       </c>
-      <c r="I36" s="24">
+      <c r="I36" s="21">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味品成本(元/份)]])</f>
         <v>5.725</v>
       </c>
-      <c r="J36" s="30">
+      <c r="J36" s="25">
         <v>15</v>
       </c>
-      <c r="K36" s="31">
+      <c r="K36" s="26">
         <f t="shared" si="0"/>
         <v>9.275</v>
       </c>
-      <c r="L36" s="31">
+      <c r="L36" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[合计成本]]*100</f>
         <v>162.008733624454</v>
       </c>
-      <c r="M36" s="31">
+      <c r="M36" s="26">
         <f t="shared" si="1"/>
         <v>61.8333333333333</v>
       </c>
     </row>
-    <row r="37" ht="18.75" customHeight="1" spans="1:13">
-      <c r="A37" s="19"/>
-      <c r="B37" s="20"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="34"/>
-      <c r="K37" s="35"/>
-      <c r="L37" s="35"/>
-      <c r="M37" s="35"/>
-    </row>
-    <row r="38" ht="18.75" customHeight="1" spans="1:13">
-      <c r="A38" s="19"/>
-      <c r="B38" s="20"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="34"/>
-      <c r="K38" s="35"/>
-      <c r="L38" s="35"/>
-      <c r="M38" s="35"/>
-    </row>
-    <row r="39" ht="17" spans="2:3">
-      <c r="B39" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B40" s="3">
-        <v>200</v>
-      </c>
-      <c r="C40" s="3">
-        <v>100</v>
-      </c>
-      <c r="D40" s="4">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4">
-      <c r="B41" s="3">
-        <v>160</v>
-      </c>
-      <c r="C41" s="3">
-        <v>80</v>
-      </c>
-      <c r="D41" s="4">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5">
-      <c r="B42" s="3">
-        <f>(B41/500)*(9.09+0.3)</f>
-        <v>3.0048</v>
-      </c>
-      <c r="C42" s="3">
-        <f>(C41/500)*(17+0.3)</f>
-        <v>2.768</v>
-      </c>
-      <c r="D42" s="4">
-        <f>(D41/500)*(22.5+0.3)</f>
-        <v>3.192</v>
-      </c>
-      <c r="E42" s="6">
-        <f>SUM(B42:D42)</f>
-        <v>8.9648</v>
-      </c>
+    <row r="40" spans="5:5">
+      <c r="E40" s="6"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="M$1:M$1048576">
@@ -3364,7 +3242,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{94c0374d-8d4c-4be9-8b89-075d511dd53b}</x14:id>
+          <x14:id>{530355eb-ba37-47ed-9185-f077c56b7c68}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3379,7 +3257,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{94c0374d-8d4c-4be9-8b89-075d511dd53b}">
+          <x14:cfRule type="dataBar" id="{530355eb-ba37-47ed-9185-f077c56b7c68}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/财务与流水/馋唻买-听涛路店商品表.xlsx
+++ b/财务与流水/馋唻买-听涛路店商品表.xlsx
@@ -3242,7 +3242,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{530355eb-ba37-47ed-9185-f077c56b7c68}</x14:id>
+          <x14:id>{330aacf5-c321-4786-96b3-765b71cda135}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3257,7 +3257,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{530355eb-ba37-47ed-9185-f077c56b7c68}">
+          <x14:cfRule type="dataBar" id="{330aacf5-c321-4786-96b3-765b71cda135}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/财务与流水/馋唻买-听涛路店商品表.xlsx
+++ b/财务与流水/馋唻买-听涛路店商品表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15860"/>
+    <workbookView windowHeight="15820"/>
   </bookViews>
   <sheets>
     <sheet name="成本管理" sheetId="1" r:id="rId1"/>
@@ -3318,7 +3318,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fa753e9f-748f-4819-ac00-7584746b726b}</x14:id>
+          <x14:id>{9af3d531-55e9-4d94-bb4e-e3da00f601b7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3333,7 +3333,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fa753e9f-748f-4819-ac00-7584746b726b}">
+          <x14:cfRule type="dataBar" id="{9af3d531-55e9-4d94-bb4e-e3da00f601b7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/财务与流水/馋唻买-听涛路店商品表.xlsx
+++ b/财务与流水/馋唻买-听涛路店商品表.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github localpath\ChanWeiMai\财务与流水\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BED19CA-6A35-4152-A23E-E08287C036AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="15820"/>
+    <workbookView xWindow="1995" yWindow="1575" windowWidth="35070" windowHeight="19335" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="成本管理" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -232,17 +238,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0.000_);\(0.000\)"/>
     <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
     <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -276,7 +278,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -300,7 +302,7 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -320,160 +322,23 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="37">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -488,13 +353,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14996795556505"/>
+        <fgColor theme="0" tint="-0.14993743705557422"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.799951170384838"/>
+        <fgColor theme="3" tint="0.79992065187536243"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -504,194 +369,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -714,251 +393,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1054,268 +491,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
-    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
-    <cellStyle name="输入" xfId="4" builtinId="20"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
-    <cellStyle name="货币" xfId="7" builtinId="4"/>
-    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
-    <cellStyle name="百分比" xfId="9" builtinId="5"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
-    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
-    <cellStyle name="计算" xfId="15" builtinId="22"/>
-    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
-    <cellStyle name="适中" xfId="17" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
-    <cellStyle name="好" xfId="19" builtinId="26"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="差" xfId="22" builtinId="27"/>
-    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
-    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
-    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
-    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
-    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
-    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
-    <cellStyle name="标题" xfId="33" builtinId="15"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
-    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="注释" xfId="37" builtinId="10"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
-    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
-    <cellStyle name="超链接" xfId="41" builtinId="8"/>
-    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
-    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
-    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
   </cellStyles>
   <dxfs count="13">
-    <dxf>
-      <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="1"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="center" vertical="center"/>
-      <border>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-0.14996795556505"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center"/>
-      <border>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-0.14996795556505"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-0.14996795556505"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-0.14996795556505"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="3" tint="0.799951170384838"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="3" tint="0.799951170384838"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="3" tint="0.799951170384838"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="1"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="3" tint="0.799951170384838"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="3" tint="0.799951170384838"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center"/>
-      <border>
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-      </border>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1327,22 +506,19 @@
         <left style="thin">
           <color rgb="FF000000"/>
         </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
       </border>
     </dxf>
     <dxf>
       <font>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-        <family val="2"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
       <fill>
@@ -1377,6 +553,219 @@
         <left style="thin">
           <color rgb="FF000000"/>
         </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="3" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center"/>
+      <border>
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="3" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="3" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center"/>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="3" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center"/>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="3" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center"/>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0" tint="-0.14993743705557422"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0" tint="-0.14993743705557422"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center"/>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0" tint="-0.14993743705557422"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0" tint="-0.14993743705557422"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center"/>
+      <border>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+      <border>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
       </border>
     </dxf>
   </dxfs>
@@ -1385,27 +774,38 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SKUTable" displayName="SKUTable" ref="A1:M36" totalsRowShown="0">
-  <autoFilter ref="A1:M36"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SKUTable" displayName="SKUTable" ref="A1:M36" totalsRowShown="0">
+  <autoFilter ref="A1:M36" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="13">
-    <tableColumn id="1" name="SKU名称" dataDxfId="0"/>
-    <tableColumn id="2" name="进货价格(元/500g)" dataDxfId="1"/>
-    <tableColumn id="11" name="运费(元/500g)" dataDxfId="2"/>
-    <tableColumn id="3" name="每份重量(g)" dataDxfId="3"/>
-    <tableColumn id="10" name="成份说明" dataDxfId="4"/>
-    <tableColumn id="4" name="食材成本(元/份)" dataDxfId="5"/>
-    <tableColumn id="5" name="打包成本(元/份)" dataDxfId="6"/>
-    <tableColumn id="6" name="调味成本(元/份)" dataDxfId="7"/>
-    <tableColumn id="12" name="总成本(元/份)" dataDxfId="8"/>
-    <tableColumn id="7" name="堂食价(元/份)" dataDxfId="9"/>
-    <tableColumn id="8" name="毛利(元/份)" dataDxfId="10"/>
-    <tableColumn id="13" name="利润率(%)" dataDxfId="11"/>
-    <tableColumn id="9" name="毛利率(%)" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="SKU名称" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="进货价格(元/500g)" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="运费(元/500g)" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="每份重量(g)" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="成份说明" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="食材成本(元/份)" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="打包成本(元/份)" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="调味成本(元/份)" dataDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="总成本(元/份)" dataDxfId="4">
+      <calculatedColumnFormula>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="堂食价(元/份)" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="毛利(元/份)" dataDxfId="2">
+      <calculatedColumnFormula>J2-(F2+G2+H2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="利润率(%)" dataDxfId="1">
+      <calculatedColumnFormula>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="毛利率(%)" dataDxfId="0">
+      <calculatedColumnFormula>(J2-(F2+G2+H2))/J2*100</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1690,33 +1090,34 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:M40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="30.5" style="2" customWidth="1"/>
     <col min="2" max="2" width="14" style="3" customWidth="1"/>
     <col min="3" max="3" width="20.25" style="3" customWidth="1"/>
     <col min="4" max="4" width="23.875" style="4" customWidth="1"/>
     <col min="5" max="5" width="33.5" style="4" customWidth="1"/>
-    <col min="6" max="6" width="18.5865384615385" style="5" customWidth="1"/>
-    <col min="7" max="7" width="19.2307692307692" style="5" customWidth="1"/>
-    <col min="8" max="8" width="18.5865384615385" style="5" customWidth="1"/>
-    <col min="9" max="9" width="19.0673076923077" style="6" customWidth="1"/>
-    <col min="10" max="10" width="17.9519230769231" style="7" customWidth="1"/>
+    <col min="6" max="6" width="18.625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="19.25" style="5" customWidth="1"/>
+    <col min="8" max="8" width="18.625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="19.125" style="6" customWidth="1"/>
+    <col min="10" max="10" width="18" style="7" customWidth="1"/>
     <col min="11" max="11" width="16.75" style="5" customWidth="1"/>
     <col min="12" max="12" width="17.625" style="5" customWidth="1"/>
     <col min="13" max="13" width="14.75" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="29.25" customHeight="1" spans="1:13">
+    <row r="1" spans="1:13" s="1" customFormat="1" ht="29.25" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1757,7 +1158,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="20.25" customHeight="1" spans="1:13">
+    <row r="2" spans="1:13" ht="20.25" customHeight="1">
       <c r="A2" s="11" t="s">
         <v>13</v>
       </c>
@@ -1775,35 +1176,35 @@
       </c>
       <c r="F2" s="21">
         <f>(B2+SKUTable[[#This Row],[运费(元/500g)]])*D2/500</f>
-        <v>2.712</v>
+        <v>2.7120000000000002</v>
       </c>
       <c r="G2" s="21">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="H2" s="21">
         <v>0.15</v>
       </c>
       <c r="I2" s="26">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>2.882</v>
+        <v>3.0620000000000003</v>
       </c>
       <c r="J2" s="27">
         <v>8</v>
       </c>
       <c r="K2" s="28">
         <f>J2-(F2+G2+H2)</f>
-        <v>5.118</v>
+        <v>4.9379999999999997</v>
       </c>
       <c r="L2" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>177.585010409438</v>
+        <v>161.26714565643368</v>
       </c>
       <c r="M2" s="28">
         <f>(J2-(F2+G2+H2))/J2*100</f>
-        <v>63.975</v>
-      </c>
-    </row>
-    <row r="3" ht="20.25" customHeight="1" spans="1:13">
+        <v>61.724999999999994</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="20.25" customHeight="1">
       <c r="A3" s="11" t="s">
         <v>15</v>
       </c>
@@ -1816,40 +1217,40 @@
         <v>16</v>
       </c>
       <c r="F3" s="21">
-        <v>2.45</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="G3" s="21">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="H3" s="21">
         <v>0.15</v>
       </c>
       <c r="I3" s="26">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>2.62</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="J3" s="27">
         <v>8</v>
       </c>
       <c r="K3" s="28">
         <f>J3-(F3+G3+H3)</f>
-        <v>5.38</v>
+        <v>5.1999999999999993</v>
       </c>
       <c r="L3" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>205.343511450382</v>
+        <v>185.71428571428567</v>
       </c>
       <c r="M3" s="28">
         <f>(J3-(F3+G3+H3))/J3*100</f>
-        <v>67.25</v>
-      </c>
-    </row>
-    <row r="4" ht="20.25" customHeight="1" spans="1:13">
+        <v>64.999999999999986</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="20.25" customHeight="1">
       <c r="A4" s="11" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="12">
-        <v>8.8</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="C4" s="12">
         <v>0</v>
@@ -1883,14 +1284,14 @@
       </c>
       <c r="L4" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>212.01248049922</v>
+        <v>212.01248049921998</v>
       </c>
       <c r="M4" s="28">
         <f t="shared" ref="M4:M36" si="1">(J4-(F4+G4+H4))/J4*100</f>
         <v>67.95</v>
       </c>
     </row>
-    <row r="5" ht="20.25" customHeight="1" spans="1:13">
+    <row r="5" spans="1:13" ht="20.25" customHeight="1">
       <c r="A5" s="11" t="s">
         <v>19</v>
       </c>
@@ -1928,14 +1329,14 @@
       </c>
       <c r="L5" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>147.524752475248</v>
+        <v>147.52475247524751</v>
       </c>
       <c r="M5" s="28">
         <f t="shared" si="1"/>
-        <v>59.6</v>
-      </c>
-    </row>
-    <row r="6" ht="20.25" customHeight="1" spans="1:13">
+        <v>59.599999999999994</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="20.25" customHeight="1">
       <c r="A6" s="11" t="s">
         <v>22</v>
       </c>
@@ -1962,25 +1363,25 @@
       </c>
       <c r="I6" s="26">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>5.02</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="J6" s="27">
         <v>8</v>
       </c>
       <c r="K6" s="28">
         <f t="shared" si="0"/>
-        <v>2.98</v>
+        <v>2.9800000000000004</v>
       </c>
       <c r="L6" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>59.3625498007968</v>
+        <v>59.362549800796828</v>
       </c>
       <c r="M6" s="28">
         <f t="shared" si="1"/>
-        <v>37.25</v>
-      </c>
-    </row>
-    <row r="7" ht="20.25" customHeight="1" spans="1:13">
+        <v>37.250000000000007</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="20.25" customHeight="1">
       <c r="A7" s="14" t="s">
         <v>24</v>
       </c>
@@ -2000,32 +1401,32 @@
         <v>3.24</v>
       </c>
       <c r="G7" s="22">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H7" s="22">
         <v>0</v>
       </c>
       <c r="I7" s="29">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>3.24</v>
+        <v>3.4400000000000004</v>
       </c>
       <c r="J7" s="22">
         <v>8</v>
       </c>
       <c r="K7" s="30">
         <f t="shared" si="0"/>
-        <v>4.76</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="L7" s="30">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>146.913580246914</v>
+        <v>132.55813953488368</v>
       </c>
       <c r="M7" s="30">
         <f t="shared" si="1"/>
-        <v>59.5</v>
-      </c>
-    </row>
-    <row r="8" ht="20.25" customHeight="1" spans="1:13">
+        <v>56.999999999999993</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="20.25" customHeight="1">
       <c r="A8" s="14" t="s">
         <v>26</v>
       </c>
@@ -2070,7 +1471,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" ht="20.25" customHeight="1" spans="1:13">
+    <row r="9" spans="1:13" ht="20.25" customHeight="1">
       <c r="A9" s="11" t="s">
         <v>28</v>
       </c>
@@ -2108,14 +1509,14 @@
       </c>
       <c r="L9" s="30">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>177.777777777778</v>
+        <v>177.7777777777778</v>
       </c>
       <c r="M9" s="30">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
     </row>
-    <row r="10" ht="20.25" customHeight="1" spans="1:13">
+    <row r="10" spans="1:13" ht="20.25" customHeight="1">
       <c r="A10" s="11" t="s">
         <v>30</v>
       </c>
@@ -2149,18 +1550,18 @@
       </c>
       <c r="K10" s="30">
         <f t="shared" si="0"/>
-        <v>0.63</v>
+        <v>0.62999999999999989</v>
       </c>
       <c r="L10" s="30">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>45.985401459854</v>
+        <v>45.985401459854003</v>
       </c>
       <c r="M10" s="30">
         <f t="shared" si="1"/>
-        <v>31.5</v>
-      </c>
-    </row>
-    <row r="11" ht="20.25" customHeight="1" spans="1:13">
+        <v>31.499999999999993</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="20.25" customHeight="1">
       <c r="A11" s="11" t="s">
         <v>31</v>
       </c>
@@ -2194,23 +1595,23 @@
       </c>
       <c r="K11" s="30">
         <f t="shared" si="0"/>
-        <v>0.63</v>
+        <v>0.62999999999999989</v>
       </c>
       <c r="L11" s="30">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>45.985401459854</v>
+        <v>45.985401459854003</v>
       </c>
       <c r="M11" s="30">
         <f t="shared" si="1"/>
-        <v>31.5</v>
-      </c>
-    </row>
-    <row r="12" ht="20.25" customHeight="1" spans="1:13">
+        <v>31.499999999999993</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="20.25" customHeight="1">
       <c r="A12" s="15" t="s">
         <v>32</v>
       </c>
       <c r="B12" s="12">
-        <v>9.09</v>
+        <v>8</v>
       </c>
       <c r="C12" s="12">
         <v>0.3</v>
@@ -2223,40 +1624,40 @@
       </c>
       <c r="F12" s="22">
         <f>(B12+SKUTable[[#This Row],[运费(元/500g)]])*D12/500</f>
-        <v>3.0987</v>
+        <v>2.7390000000000003</v>
       </c>
       <c r="G12" s="22">
-        <v>0.685</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="H12" s="22">
         <v>0.2</v>
       </c>
       <c r="I12" s="29">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>3.9837</v>
+        <v>3.6240000000000006</v>
       </c>
       <c r="J12" s="22">
         <v>12</v>
       </c>
       <c r="K12" s="30">
         <f t="shared" si="0"/>
-        <v>8.0163</v>
+        <v>8.3759999999999994</v>
       </c>
       <c r="L12" s="30">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>201.227502070939</v>
+        <v>231.1258278145695</v>
       </c>
       <c r="M12" s="30">
         <f t="shared" si="1"/>
-        <v>66.8025</v>
-      </c>
-    </row>
-    <row r="13" ht="20.25" customHeight="1" spans="1:13">
+        <v>69.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="20.25" customHeight="1">
       <c r="A13" s="15" t="s">
         <v>34</v>
       </c>
       <c r="B13" s="12">
-        <v>9.09</v>
+        <v>8</v>
       </c>
       <c r="C13" s="12">
         <v>0.3</v>
@@ -2269,7 +1670,7 @@
       </c>
       <c r="F13" s="22">
         <f>(B13+SKUTable[[#This Row],[运费(元/500g)]])*D13/500</f>
-        <v>4.8828</v>
+        <v>4.3159999999999998</v>
       </c>
       <c r="G13" s="22">
         <v>0.82</v>
@@ -2279,25 +1680,25 @@
       </c>
       <c r="I13" s="29">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>5.9028</v>
+        <v>5.3360000000000003</v>
       </c>
       <c r="J13" s="22">
         <v>16</v>
       </c>
       <c r="K13" s="30">
         <f t="shared" si="0"/>
-        <v>10.0972</v>
+        <v>10.664</v>
       </c>
       <c r="L13" s="30">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>171.057803076506</v>
+        <v>199.85007496251873</v>
       </c>
       <c r="M13" s="30">
         <f t="shared" si="1"/>
-        <v>63.1075</v>
-      </c>
-    </row>
-    <row r="14" ht="18.75" customHeight="1" spans="1:13">
+        <v>66.649999999999991</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="18.75" customHeight="1">
       <c r="A14" s="15" t="s">
         <v>35</v>
       </c>
@@ -2318,32 +1719,32 @@
         <v>3.3</v>
       </c>
       <c r="G14" s="22">
-        <v>0.685</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="H14" s="22">
         <v>0.2</v>
       </c>
       <c r="I14" s="29">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>4.185</v>
+        <v>4.1849999999999996</v>
       </c>
       <c r="J14" s="22">
         <v>14</v>
       </c>
       <c r="K14" s="30">
         <f t="shared" si="0"/>
-        <v>9.815</v>
+        <v>9.8150000000000013</v>
       </c>
       <c r="L14" s="30">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>234.52807646356</v>
+        <v>234.52807646356041</v>
       </c>
       <c r="M14" s="30">
         <f t="shared" si="1"/>
-        <v>70.1071428571429</v>
-      </c>
-    </row>
-    <row r="15" ht="18.75" customHeight="1" spans="1:13">
+        <v>70.107142857142861</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="18.75" customHeight="1">
       <c r="A15" s="15" t="s">
         <v>37</v>
       </c>
@@ -2371,7 +1772,7 @@
       </c>
       <c r="I15" s="29">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>6.22</v>
+        <v>6.2200000000000006</v>
       </c>
       <c r="J15" s="22">
         <v>18</v>
@@ -2382,14 +1783,14 @@
       </c>
       <c r="L15" s="30">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>189.389067524116</v>
+        <v>189.38906752411572</v>
       </c>
       <c r="M15" s="30">
         <f t="shared" si="1"/>
-        <v>65.4444444444444</v>
-      </c>
-    </row>
-    <row r="16" ht="18.75" customHeight="1" spans="1:13">
+        <v>65.444444444444443</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="18.75" customHeight="1">
       <c r="A16" s="15" t="s">
         <v>38</v>
       </c>
@@ -2410,32 +1811,32 @@
         <v>4.125</v>
       </c>
       <c r="G16" s="22">
-        <v>0.685</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="H16" s="22">
         <v>0.2</v>
       </c>
       <c r="I16" s="29">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>5.01</v>
+        <v>5.0100000000000007</v>
       </c>
       <c r="J16" s="22">
         <v>15</v>
       </c>
       <c r="K16" s="30">
         <f t="shared" si="0"/>
-        <v>9.99</v>
+        <v>9.9899999999999984</v>
       </c>
       <c r="L16" s="30">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>199.40119760479</v>
+        <v>199.40119760479035</v>
       </c>
       <c r="M16" s="30">
         <f t="shared" si="1"/>
-        <v>66.6</v>
-      </c>
-    </row>
-    <row r="17" ht="18.75" customHeight="1" spans="1:13">
+        <v>66.599999999999994</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="18.75" customHeight="1">
       <c r="A17" s="15" t="s">
         <v>40</v>
       </c>
@@ -2463,7 +1864,7 @@
       </c>
       <c r="I17" s="29">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>7.52</v>
+        <v>7.5200000000000005</v>
       </c>
       <c r="J17" s="22">
         <v>20</v>
@@ -2474,14 +1875,14 @@
       </c>
       <c r="L17" s="30">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>165.957446808511</v>
+        <v>165.95744680851064</v>
       </c>
       <c r="M17" s="30">
         <f t="shared" si="1"/>
         <v>62.4</v>
       </c>
     </row>
-    <row r="18" ht="18.75" customHeight="1" spans="1:13">
+    <row r="18" spans="1:13" ht="18.75" customHeight="1">
       <c r="A18" s="16" t="s">
         <v>41</v>
       </c>
@@ -2502,21 +1903,21 @@
         <v>4.59</v>
       </c>
       <c r="G18" s="22">
-        <v>0.685</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="H18" s="22">
         <v>0.2</v>
       </c>
       <c r="I18" s="29">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>5.475</v>
+        <v>5.4750000000000005</v>
       </c>
       <c r="J18" s="22">
         <v>15</v>
       </c>
       <c r="K18" s="30">
         <f t="shared" ref="K18" si="3">J18-(F18+G18+H18)</f>
-        <v>9.525</v>
+        <v>9.5249999999999986</v>
       </c>
       <c r="L18" s="30">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
@@ -2524,10 +1925,10 @@
       </c>
       <c r="M18" s="30">
         <f t="shared" ref="M18" si="4">(J18-(F18+G18+H18))/J18*100</f>
-        <v>63.5</v>
-      </c>
-    </row>
-    <row r="19" ht="18.75" customHeight="1" spans="1:13">
+        <v>63.499999999999993</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="18.75" customHeight="1">
       <c r="A19" s="16" t="s">
         <v>43</v>
       </c>
@@ -2548,32 +1949,32 @@
         <v>5.61</v>
       </c>
       <c r="G19" s="22">
-        <v>0.685</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="H19" s="22">
         <v>0.2</v>
       </c>
       <c r="I19" s="29">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>6.495</v>
+        <v>6.4950000000000001</v>
       </c>
       <c r="J19" s="22">
         <v>20</v>
       </c>
       <c r="K19" s="30">
         <f t="shared" si="0"/>
-        <v>13.505</v>
+        <v>13.504999999999999</v>
       </c>
       <c r="L19" s="30">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>207.929176289453</v>
+        <v>207.92917628945341</v>
       </c>
       <c r="M19" s="30">
         <f t="shared" si="1"/>
-        <v>67.525</v>
-      </c>
-    </row>
-    <row r="20" ht="18.75" customHeight="1" spans="1:13">
+        <v>67.524999999999991</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="18.75" customHeight="1">
       <c r="A20" s="16" t="s">
         <v>44</v>
       </c>
@@ -2612,14 +2013,14 @@
       </c>
       <c r="L20" s="30">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>143.407707910751</v>
+        <v>143.40770791075053</v>
       </c>
       <c r="M20" s="30">
         <f t="shared" si="1"/>
-        <v>58.9166666666667</v>
-      </c>
-    </row>
-    <row r="21" ht="18.75" customHeight="1" spans="1:13">
+        <v>58.916666666666671</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="18.75" customHeight="1">
       <c r="A21" s="16" t="s">
         <v>45</v>
       </c>
@@ -2640,32 +2041,32 @@
         <v>4.5</v>
       </c>
       <c r="G21" s="22">
-        <v>0.685</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="H21" s="22">
         <v>0.2</v>
       </c>
       <c r="I21" s="29">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>5.385</v>
+        <v>5.3850000000000007</v>
       </c>
       <c r="J21" s="22">
         <v>18</v>
       </c>
       <c r="K21" s="30">
         <f t="shared" si="0"/>
-        <v>12.615</v>
+        <v>12.614999999999998</v>
       </c>
       <c r="L21" s="30">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>234.261838440111</v>
+        <v>234.26183844011135</v>
       </c>
       <c r="M21" s="30">
         <f t="shared" si="1"/>
-        <v>70.0833333333333</v>
-      </c>
-    </row>
-    <row r="22" ht="18.75" customHeight="1" spans="1:13">
+        <v>70.083333333333314</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="18.75" customHeight="1">
       <c r="A22" s="14" t="s">
         <v>47</v>
       </c>
@@ -2690,7 +2091,7 @@
       <c r="L22" s="30"/>
       <c r="M22" s="30"/>
     </row>
-    <row r="23" ht="18.75" customHeight="1" spans="1:13">
+    <row r="23" spans="1:13" ht="18.75" customHeight="1">
       <c r="A23" s="14" t="s">
         <v>48</v>
       </c>
@@ -2727,14 +2128,14 @@
       </c>
       <c r="L23" s="30">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>170.27027027027</v>
+        <v>170.27027027027026</v>
       </c>
       <c r="M23" s="30">
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
     </row>
-    <row r="24" ht="18.75" customHeight="1" spans="1:13">
+    <row r="24" spans="1:13" ht="18.75" customHeight="1">
       <c r="A24" s="14" t="s">
         <v>50</v>
       </c>
@@ -2771,14 +2172,14 @@
       </c>
       <c r="L24" s="30">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>210.077519379845</v>
+        <v>210.07751937984494</v>
       </c>
       <c r="M24" s="30">
         <f t="shared" si="1"/>
         <v>67.75</v>
       </c>
     </row>
-    <row r="25" ht="18.75" customHeight="1" spans="1:13">
+    <row r="25" spans="1:13" ht="18.75" customHeight="1">
       <c r="A25" s="16" t="s">
         <v>51</v>
       </c>
@@ -2796,7 +2197,7 @@
       </c>
       <c r="F25" s="22">
         <f t="shared" si="5"/>
-        <v>5.454</v>
+        <v>5.4539999999999997</v>
       </c>
       <c r="G25" s="22">
         <v>0.82</v>
@@ -2813,18 +2214,18 @@
       </c>
       <c r="K25" s="30">
         <f t="shared" si="0"/>
-        <v>9.226</v>
+        <v>9.2259999999999991</v>
       </c>
       <c r="L25" s="30">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>136.19722468261</v>
+        <v>136.19722468260997</v>
       </c>
       <c r="M25" s="30">
         <f t="shared" si="1"/>
-        <v>57.6625</v>
-      </c>
-    </row>
-    <row r="26" ht="18.75" customHeight="1" spans="1:13">
+        <v>57.662499999999994</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="18.75" customHeight="1">
       <c r="A26" s="15" t="s">
         <v>52</v>
       </c>
@@ -2842,35 +2243,35 @@
       </c>
       <c r="F26" s="22">
         <f t="shared" si="5"/>
-        <v>2.9997</v>
+        <v>2.9996999999999998</v>
       </c>
       <c r="G26" s="22">
-        <v>0.685</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="H26" s="23">
         <v>1.5</v>
       </c>
       <c r="I26" s="31">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>5.1847</v>
+        <v>5.1846999999999994</v>
       </c>
       <c r="J26" s="22">
         <v>14</v>
       </c>
       <c r="K26" s="30">
         <f t="shared" si="0"/>
-        <v>8.8153</v>
+        <v>8.8153000000000006</v>
       </c>
       <c r="L26" s="30">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>170.025266649951</v>
+        <v>170.02526664995085</v>
       </c>
       <c r="M26" s="30">
         <f t="shared" si="1"/>
-        <v>62.9664285714286</v>
-      </c>
-    </row>
-    <row r="27" ht="18.75" customHeight="1" spans="1:13">
+        <v>62.96642857142858</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="18.75" customHeight="1">
       <c r="A27" s="15" t="s">
         <v>54</v>
       </c>
@@ -2888,7 +2289,7 @@
       </c>
       <c r="F27" s="22">
         <f t="shared" si="5"/>
-        <v>4.7268</v>
+        <v>4.7267999999999999</v>
       </c>
       <c r="G27" s="22">
         <v>0.82</v>
@@ -2898,25 +2299,25 @@
       </c>
       <c r="I27" s="31">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>7.0468</v>
+        <v>7.0468000000000002</v>
       </c>
       <c r="J27" s="22">
         <v>18</v>
       </c>
       <c r="K27" s="30">
         <f t="shared" si="0"/>
-        <v>10.9532</v>
+        <v>10.953199999999999</v>
       </c>
       <c r="L27" s="30">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>155.435091105182</v>
+        <v>155.43509110518247</v>
       </c>
       <c r="M27" s="30">
         <f t="shared" si="1"/>
-        <v>60.8511111111111</v>
-      </c>
-    </row>
-    <row r="28" ht="18.75" customHeight="1" spans="1:13">
+        <v>60.851111111111102</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="18.75" customHeight="1">
       <c r="A28" s="11" t="s">
         <v>55</v>
       </c>
@@ -2932,7 +2333,7 @@
       <c r="E28" s="13"/>
       <c r="F28" s="22">
         <f t="shared" si="5"/>
-        <v>0.8225</v>
+        <v>0.82250000000000001</v>
       </c>
       <c r="G28" s="22" t="s">
         <v>20</v>
@@ -2942,7 +2343,7 @@
       </c>
       <c r="I28" s="31">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>0.8225</v>
+        <v>0.82250000000000001</v>
       </c>
       <c r="J28" s="22" t="s">
         <v>20</v>
@@ -2955,7 +2356,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" ht="18.75" customHeight="1" spans="1:13">
+    <row r="29" spans="1:13" ht="18.75" customHeight="1">
       <c r="A29" s="15" t="s">
         <v>56</v>
       </c>
@@ -2973,35 +2374,35 @@
       </c>
       <c r="F29" s="22">
         <f t="shared" si="5"/>
-        <v>2.9997</v>
+        <v>2.9996999999999998</v>
       </c>
       <c r="G29" s="22">
-        <v>0.685</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="H29" s="23">
         <v>1.2</v>
       </c>
       <c r="I29" s="31">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>4.8847</v>
+        <v>4.8846999999999996</v>
       </c>
       <c r="J29" s="22">
         <v>14</v>
       </c>
       <c r="K29" s="30">
         <f t="shared" si="0"/>
-        <v>9.1153</v>
+        <v>9.1153000000000013</v>
       </c>
       <c r="L29" s="30">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>186.609208344422</v>
+        <v>186.60920834442243</v>
       </c>
       <c r="M29" s="30">
         <f t="shared" si="1"/>
-        <v>65.1092857142857</v>
-      </c>
-    </row>
-    <row r="30" ht="18.75" customHeight="1" spans="1:13">
+        <v>65.109285714285718</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="18.75" customHeight="1">
       <c r="A30" s="15" t="s">
         <v>58</v>
       </c>
@@ -3019,7 +2420,7 @@
       </c>
       <c r="F30" s="22">
         <f t="shared" si="5"/>
-        <v>4.7268</v>
+        <v>4.7267999999999999</v>
       </c>
       <c r="G30" s="22">
         <v>0.82</v>
@@ -3029,7 +2430,7 @@
       </c>
       <c r="I30" s="31">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>6.7468</v>
+        <v>6.7468000000000004</v>
       </c>
       <c r="J30" s="22">
         <v>18</v>
@@ -3040,14 +2441,14 @@
       </c>
       <c r="L30" s="30">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>166.793146380506</v>
+        <v>166.7931463805063</v>
       </c>
       <c r="M30" s="30">
         <f t="shared" si="1"/>
-        <v>62.5177777777778</v>
-      </c>
-    </row>
-    <row r="31" ht="18.75" customHeight="1" spans="1:13">
+        <v>62.517777777777773</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="18.75" customHeight="1">
       <c r="A31" s="11" t="s">
         <v>59</v>
       </c>
@@ -3065,17 +2466,17 @@
       </c>
       <c r="F31" s="22">
         <f t="shared" si="5"/>
-        <v>0.805</v>
+        <v>0.80500000000000005</v>
       </c>
       <c r="G31" s="22">
         <v>0.82</v>
       </c>
       <c r="H31" s="22">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I31" s="29">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>5.725</v>
+        <v>5.7249999999999996</v>
       </c>
       <c r="J31" s="22">
         <v>16</v>
@@ -3086,14 +2487,14 @@
       </c>
       <c r="L31" s="30">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>179.475982532751</v>
+        <v>179.47598253275109</v>
       </c>
       <c r="M31" s="30">
         <f t="shared" si="1"/>
         <v>64.21875</v>
       </c>
     </row>
-    <row r="32" ht="18.75" customHeight="1" spans="1:13">
+    <row r="32" spans="1:13" ht="18.75" customHeight="1">
       <c r="A32" s="15" t="s">
         <v>61</v>
       </c>
@@ -3109,32 +2510,32 @@
         <v>3.88</v>
       </c>
       <c r="G32" s="22">
-        <v>0.685</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="H32" s="22">
         <v>0.2</v>
       </c>
       <c r="I32" s="29">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>4.765</v>
+        <v>4.7649999999999997</v>
       </c>
       <c r="J32" s="22">
         <v>14</v>
       </c>
       <c r="K32" s="30">
         <f t="shared" si="0"/>
-        <v>9.235</v>
+        <v>9.2349999999999994</v>
       </c>
       <c r="L32" s="30">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>193.809024134313</v>
+        <v>193.80902413431269</v>
       </c>
       <c r="M32" s="30">
         <f t="shared" si="1"/>
-        <v>65.9642857142857</v>
-      </c>
-    </row>
-    <row r="33" ht="18.75" customHeight="1" spans="1:13">
+        <v>65.964285714285708</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="18.75" customHeight="1">
       <c r="A33" s="15" t="s">
         <v>63</v>
       </c>
@@ -3150,7 +2551,7 @@
         <v>5.28</v>
       </c>
       <c r="G33" s="22">
-        <v>0.685</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="H33" s="22">
         <v>0.2</v>
@@ -3164,18 +2565,18 @@
       </c>
       <c r="K33" s="30">
         <f t="shared" si="0"/>
-        <v>8.835</v>
+        <v>8.8350000000000009</v>
       </c>
       <c r="L33" s="30">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>143.30900243309</v>
+        <v>143.30900243309003</v>
       </c>
       <c r="M33" s="30">
         <f t="shared" si="1"/>
-        <v>58.9</v>
-      </c>
-    </row>
-    <row r="34" ht="18.75" customHeight="1" spans="1:13">
+        <v>58.900000000000006</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="18.75" customHeight="1">
       <c r="A34" s="15" t="s">
         <v>65</v>
       </c>
@@ -3190,7 +2591,7 @@
         <v>66</v>
       </c>
       <c r="F34" s="22">
-        <v>6.94</v>
+        <v>6.64</v>
       </c>
       <c r="G34" s="22">
         <v>0.82</v>
@@ -3200,25 +2601,25 @@
       </c>
       <c r="I34" s="29">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>7.96</v>
+        <v>7.66</v>
       </c>
       <c r="J34" s="22">
         <v>24</v>
       </c>
       <c r="K34" s="30">
         <f t="shared" si="0"/>
-        <v>16.04</v>
+        <v>16.34</v>
       </c>
       <c r="L34" s="30">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>201.507537688442</v>
+        <v>213.31592689295042</v>
       </c>
       <c r="M34" s="30">
         <f t="shared" si="1"/>
-        <v>66.8333333333333</v>
-      </c>
-    </row>
-    <row r="35" ht="18.75" customHeight="1" spans="1:13">
+        <v>68.083333333333329</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="18.75" customHeight="1">
       <c r="A35" s="11" t="s">
         <v>67</v>
       </c>
@@ -3242,29 +2643,29 @@
         <v>0.82</v>
       </c>
       <c r="H35" s="22">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I35" s="29">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>6.045</v>
+        <v>6.0449999999999999</v>
       </c>
       <c r="J35" s="22">
         <v>16</v>
       </c>
       <c r="K35" s="30">
         <f t="shared" si="0"/>
-        <v>9.955</v>
+        <v>9.9550000000000001</v>
       </c>
       <c r="L35" s="30">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>164.681555004136</v>
+        <v>164.68155500413565</v>
       </c>
       <c r="M35" s="30">
         <f t="shared" si="1"/>
         <v>62.21875</v>
       </c>
     </row>
-    <row r="36" ht="18.75" customHeight="1" spans="1:13">
+    <row r="36" spans="1:13" ht="18.75" customHeight="1">
       <c r="A36" s="11" t="s">
         <v>69</v>
       </c>
@@ -3280,36 +2681,37 @@
         <v>2.84</v>
       </c>
       <c r="G36" s="22">
-        <v>0.685</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="H36" s="22">
         <v>2.5</v>
       </c>
       <c r="I36" s="29">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>6.025</v>
+        <v>6.0250000000000004</v>
       </c>
       <c r="J36" s="22">
         <v>15</v>
       </c>
       <c r="K36" s="30">
         <f t="shared" si="0"/>
-        <v>8.975</v>
+        <v>8.9749999999999996</v>
       </c>
       <c r="L36" s="30">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>148.96265560166</v>
+        <v>148.96265560165972</v>
       </c>
       <c r="M36" s="30">
         <f t="shared" si="1"/>
-        <v>59.8333333333333</v>
-      </c>
-    </row>
-    <row r="40" spans="5:5">
+        <v>59.833333333333329</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="E40" s="7"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="M$1:M$1048576">
+  <phoneticPr fontId="13" type="noConversion"/>
+  <conditionalFormatting sqref="M1:M1048576">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -3318,14 +2720,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9af3d531-55e9-4d94-bb4e-e3da00f601b7}</x14:id>
+          <x14:id>{9AF3D531-55E9-4D94-BB4E-E3DA00F601B7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -3333,7 +2734,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9af3d531-55e9-4d94-bb4e-e3da00f601b7}">
+          <x14:cfRule type="dataBar" id="{9AF3D531-55E9-4D94-BB4E-E3DA00F601B7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -3343,7 +2744,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>M$1:M$1048576</xm:sqref>
+          <xm:sqref>M1:M1048576</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/财务与流水/馋唻买-听涛路店商品表.xlsx
+++ b/财务与流水/馋唻买-听涛路店商品表.xlsx
@@ -1,39 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github localpath\ChanWeiMai\财务与流水\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Github\ChanWeiMai\财务与流水\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BED19CA-6A35-4152-A23E-E08287C036AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E69D4097-17BF-4F61-9257-0D2D743E9255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1995" yWindow="1575" windowWidth="35070" windowHeight="19335" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="成本管理" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="71">
   <si>
-    <t>SKU名称</t>
-  </si>
-  <si>
     <t>进货价格(元/500g)</t>
   </si>
   <si>
     <t>运费(元/500g)</t>
   </si>
   <si>
-    <t>每份重量(g)</t>
-  </si>
-  <si>
     <t>成份说明</t>
   </si>
   <si>
@@ -233,6 +240,14 @@
   </si>
   <si>
     <t>火鸡面、瘦肉丸、调味品</t>
+  </si>
+  <si>
+    <t>SKU</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>每份制作重量(g)</t>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -244,7 +259,7 @@
     <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
     <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -337,6 +352,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -397,7 +420,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -418,9 +441,6 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="178" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -489,6 +509,12 @@
     </xf>
     <xf numFmtId="176" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -785,10 +811,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SKUTable" displayName="SKUTable" ref="A1:M36" totalsRowShown="0">
   <autoFilter ref="A1:M36" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="SKU名称" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="SKU" dataDxfId="12"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="进货价格(元/500g)" dataDxfId="11"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="运费(元/500g)" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="每份重量(g)" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="每份制作重量(g)" dataDxfId="9"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="成份说明" dataDxfId="8"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="食材成本(元/份)" dataDxfId="7"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="打包成本(元/份)" dataDxfId="6"/>
@@ -1100,7 +1126,7 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:M40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="30.5" style="2" customWidth="1"/>
     <col min="2" max="2" width="14" style="3" customWidth="1"/>
@@ -1117,1596 +1143,1596 @@
     <col min="13" max="13" width="14.75" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:13" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="F1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="G1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="H1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="I1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="J1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="K1" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="L1" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="M1" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="19" t="s">
+    </row>
+    <row r="2" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="B2" s="11">
+        <v>11</v>
+      </c>
+      <c r="C2" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D2" s="12">
+        <v>120</v>
+      </c>
+      <c r="E2" s="19" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A2" s="11" t="s">
+      <c r="F2" s="20">
+        <f>(B2+SKUTable[[#This Row],[运费(元/500g)]])*D2/500</f>
+        <v>2.76</v>
+      </c>
+      <c r="G2" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="H2" s="20">
+        <v>0.15</v>
+      </c>
+      <c r="I2" s="25">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
+        <v>3.11</v>
+      </c>
+      <c r="J2" s="26">
+        <v>8</v>
+      </c>
+      <c r="K2" s="27">
+        <f>J2-(F2+G2+H2)</f>
+        <v>4.8900000000000006</v>
+      </c>
+      <c r="L2" s="27">
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
+        <v>157.23472668810291</v>
+      </c>
+      <c r="M2" s="27">
+        <f>(J2-(F2+G2+H2))/J2*100</f>
+        <v>61.125000000000007</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="12">
-        <v>11</v>
-      </c>
-      <c r="C2" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="D2" s="13">
-        <v>120</v>
-      </c>
-      <c r="E2" s="20" t="s">
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="12">
+        <v>220</v>
+      </c>
+      <c r="E3" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="21">
-        <f>(B2+SKUTable[[#This Row],[运费(元/500g)]])*D2/500</f>
-        <v>2.7120000000000002</v>
-      </c>
-      <c r="G2" s="21">
+      <c r="F3" s="20">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="G3" s="20">
         <v>0.2</v>
       </c>
-      <c r="H2" s="21">
+      <c r="H3" s="20">
         <v>0.15</v>
       </c>
-      <c r="I2" s="26">
-        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>3.0620000000000003</v>
-      </c>
-      <c r="J2" s="27">
+      <c r="I3" s="25">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
+        <v>2.8000000000000003</v>
+      </c>
+      <c r="J3" s="26">
         <v>8</v>
       </c>
-      <c r="K2" s="28">
-        <f>J2-(F2+G2+H2)</f>
-        <v>4.9379999999999997</v>
-      </c>
-      <c r="L2" s="28">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>161.26714565643368</v>
-      </c>
-      <c r="M2" s="28">
-        <f>(J2-(F2+G2+H2))/J2*100</f>
-        <v>61.724999999999994</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A3" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="13">
-        <v>220</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="21">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="G3" s="21">
-        <v>0.2</v>
-      </c>
-      <c r="H3" s="21">
-        <v>0.15</v>
-      </c>
-      <c r="I3" s="26">
-        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>2.8000000000000003</v>
-      </c>
-      <c r="J3" s="27">
-        <v>8</v>
-      </c>
-      <c r="K3" s="28">
+      <c r="K3" s="27">
         <f>J3-(F3+G3+H3)</f>
         <v>5.1999999999999993</v>
       </c>
-      <c r="L3" s="28">
+      <c r="L3" s="27">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>185.71428571428567</v>
       </c>
-      <c r="M3" s="28">
+      <c r="M3" s="27">
         <f>(J3-(F3+G3+H3))/J3*100</f>
         <v>64.999999999999986</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A4" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="12">
+    <row r="4" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="11">
         <v>8.8000000000000007</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="11">
         <v>0</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>70</v>
       </c>
-      <c r="E4" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="21">
+      <c r="E4" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="20">
         <f>(B4+SKUTable[[#This Row],[运费(元/500g)]])*D4/500</f>
         <v>1.232</v>
       </c>
-      <c r="G4" s="21">
+      <c r="G4" s="20">
         <v>0.05</v>
       </c>
-      <c r="H4" s="21">
+      <c r="H4" s="20">
         <v>0</v>
       </c>
-      <c r="I4" s="26">
+      <c r="I4" s="25">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>1.282</v>
       </c>
-      <c r="J4" s="27">
+      <c r="J4" s="26">
         <v>4</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="27">
         <f t="shared" ref="K4:K36" si="0">J4-(F4+G4+H4)</f>
         <v>2.718</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="27">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>212.01248049921998</v>
       </c>
-      <c r="M4" s="28">
+      <c r="M4" s="27">
         <f t="shared" ref="M4:M36" si="1">(J4-(F4+G4+H4))/J4*100</f>
         <v>67.95</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A5" s="11" t="s">
+    <row r="5" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="F5" s="20">
+        <v>2</v>
+      </c>
+      <c r="G5" s="20">
+        <v>0.02</v>
+      </c>
+      <c r="H5" s="20">
+        <v>0</v>
+      </c>
+      <c r="I5" s="25">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
+        <v>2.02</v>
+      </c>
+      <c r="J5" s="26">
+        <v>5</v>
+      </c>
+      <c r="K5" s="27">
+        <f t="shared" si="0"/>
+        <v>2.98</v>
+      </c>
+      <c r="L5" s="27">
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
+        <v>147.52475247524751</v>
+      </c>
+      <c r="M5" s="27">
+        <f t="shared" si="1"/>
+        <v>59.599999999999994</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="20" t="s">
+      <c r="B6" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F6" s="20">
+        <v>5</v>
+      </c>
+      <c r="G6" s="20">
+        <v>0.02</v>
+      </c>
+      <c r="H6" s="20">
+        <v>0</v>
+      </c>
+      <c r="I6" s="25">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="J6" s="26">
+        <v>8</v>
+      </c>
+      <c r="K6" s="27">
+        <f t="shared" si="0"/>
+        <v>2.9800000000000004</v>
+      </c>
+      <c r="L6" s="27">
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
+        <v>59.362549800796828</v>
+      </c>
+      <c r="M6" s="27">
+        <f t="shared" si="1"/>
+        <v>37.250000000000007</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="21">
+        <v>3.24</v>
+      </c>
+      <c r="G7" s="21">
+        <v>0.2</v>
+      </c>
+      <c r="H7" s="21">
+        <v>0</v>
+      </c>
+      <c r="I7" s="28">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
+        <v>3.4400000000000004</v>
+      </c>
+      <c r="J7" s="21">
+        <v>8</v>
+      </c>
+      <c r="K7" s="29">
+        <f t="shared" si="0"/>
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="L7" s="29">
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
+        <v>132.55813953488368</v>
+      </c>
+      <c r="M7" s="29">
+        <f t="shared" si="1"/>
+        <v>56.999999999999993</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="21">
+        <v>0.4</v>
+      </c>
+      <c r="G8" s="21">
+        <v>0</v>
+      </c>
+      <c r="H8" s="21">
+        <v>0</v>
+      </c>
+      <c r="I8" s="28">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
+        <v>0.4</v>
+      </c>
+      <c r="J8" s="21">
+        <v>1.25</v>
+      </c>
+      <c r="K8" s="29">
+        <f t="shared" si="0"/>
+        <v>0.85</v>
+      </c>
+      <c r="L8" s="29">
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
+        <v>212.5</v>
+      </c>
+      <c r="M8" s="29">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="21">
+        <v>0.45</v>
+      </c>
+      <c r="G9" s="21">
+        <v>0</v>
+      </c>
+      <c r="H9" s="21">
+        <v>0</v>
+      </c>
+      <c r="I9" s="28">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
+        <v>0.45</v>
+      </c>
+      <c r="J9" s="21">
+        <v>1.25</v>
+      </c>
+      <c r="K9" s="29">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="L9" s="29">
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
+        <v>177.7777777777778</v>
+      </c>
+      <c r="M9" s="29">
+        <f t="shared" si="1"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="21">
+        <v>1.37</v>
+      </c>
+      <c r="G10" s="21">
+        <v>0</v>
+      </c>
+      <c r="H10" s="21">
+        <v>0</v>
+      </c>
+      <c r="I10" s="28">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
+        <v>1.37</v>
+      </c>
+      <c r="J10" s="21">
         <v>2</v>
       </c>
-      <c r="G5" s="21">
-        <v>0.02</v>
-      </c>
-      <c r="H5" s="21">
+      <c r="K10" s="29">
+        <f t="shared" si="0"/>
+        <v>0.62999999999999989</v>
+      </c>
+      <c r="L10" s="29">
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
+        <v>45.985401459854003</v>
+      </c>
+      <c r="M10" s="29">
+        <f t="shared" si="1"/>
+        <v>31.499999999999993</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="21">
+        <v>1.37</v>
+      </c>
+      <c r="G11" s="21">
         <v>0</v>
       </c>
-      <c r="I5" s="26">
-        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>2.02</v>
-      </c>
-      <c r="J5" s="27">
-        <v>5</v>
-      </c>
-      <c r="K5" s="28">
-        <f t="shared" si="0"/>
-        <v>2.98</v>
-      </c>
-      <c r="L5" s="28">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>147.52475247524751</v>
-      </c>
-      <c r="M5" s="28">
-        <f t="shared" si="1"/>
-        <v>59.599999999999994</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A6" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="21">
-        <v>5</v>
-      </c>
-      <c r="G6" s="21">
-        <v>0.02</v>
-      </c>
-      <c r="H6" s="21">
+      <c r="H11" s="21">
         <v>0</v>
       </c>
-      <c r="I6" s="26">
-        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>5.0199999999999996</v>
-      </c>
-      <c r="J6" s="27">
+      <c r="I11" s="28">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
+        <v>1.37</v>
+      </c>
+      <c r="J11" s="21">
+        <v>2</v>
+      </c>
+      <c r="K11" s="29">
+        <f t="shared" si="0"/>
+        <v>0.62999999999999989</v>
+      </c>
+      <c r="L11" s="29">
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
+        <v>45.985401459854003</v>
+      </c>
+      <c r="M11" s="29">
+        <f t="shared" si="1"/>
+        <v>31.499999999999993</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="11">
         <v>8</v>
       </c>
-      <c r="K6" s="28">
-        <f t="shared" si="0"/>
-        <v>2.9800000000000004</v>
-      </c>
-      <c r="L6" s="28">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>59.362549800796828</v>
-      </c>
-      <c r="M6" s="28">
-        <f t="shared" si="1"/>
-        <v>37.250000000000007</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A7" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="22">
-        <v>3.24</v>
-      </c>
-      <c r="G7" s="22">
+      <c r="C12" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D12" s="12">
+        <v>165</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="21">
+        <f>(B12+SKUTable[[#This Row],[运费(元/500g)]])*D12/500</f>
+        <v>2.8050000000000002</v>
+      </c>
+      <c r="G12" s="21">
+        <v>0.68500000000000005</v>
+      </c>
+      <c r="H12" s="21">
         <v>0.2</v>
       </c>
-      <c r="H7" s="22">
-        <v>0</v>
-      </c>
-      <c r="I7" s="29">
-        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>3.4400000000000004</v>
-      </c>
-      <c r="J7" s="22">
+      <c r="I12" s="28">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
+        <v>3.6900000000000004</v>
+      </c>
+      <c r="J12" s="21">
+        <v>12</v>
+      </c>
+      <c r="K12" s="29">
+        <f t="shared" si="0"/>
+        <v>8.3099999999999987</v>
+      </c>
+      <c r="L12" s="29">
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
+        <v>225.20325203252028</v>
+      </c>
+      <c r="M12" s="29">
+        <f t="shared" si="1"/>
+        <v>69.249999999999986</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="11">
         <v>8</v>
       </c>
-      <c r="K7" s="30">
-        <f t="shared" si="0"/>
-        <v>4.5599999999999996</v>
-      </c>
-      <c r="L7" s="30">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>132.55813953488368</v>
-      </c>
-      <c r="M7" s="30">
-        <f t="shared" si="1"/>
-        <v>56.999999999999993</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A8" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="22">
-        <v>0.4</v>
-      </c>
-      <c r="G8" s="22">
-        <v>0</v>
-      </c>
-      <c r="H8" s="22">
-        <v>0</v>
-      </c>
-      <c r="I8" s="29">
-        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>0.4</v>
-      </c>
-      <c r="J8" s="22">
-        <v>1.25</v>
-      </c>
-      <c r="K8" s="30">
-        <f t="shared" si="0"/>
-        <v>0.85</v>
-      </c>
-      <c r="L8" s="30">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>212.5</v>
-      </c>
-      <c r="M8" s="30">
-        <f t="shared" si="1"/>
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A9" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="22">
-        <v>0.45</v>
-      </c>
-      <c r="G9" s="22">
-        <v>0</v>
-      </c>
-      <c r="H9" s="22">
-        <v>0</v>
-      </c>
-      <c r="I9" s="29">
-        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>0.45</v>
-      </c>
-      <c r="J9" s="22">
-        <v>1.25</v>
-      </c>
-      <c r="K9" s="30">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="L9" s="30">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>177.7777777777778</v>
-      </c>
-      <c r="M9" s="30">
-        <f t="shared" si="1"/>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A10" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="22">
-        <v>1.37</v>
-      </c>
-      <c r="G10" s="22">
-        <v>0</v>
-      </c>
-      <c r="H10" s="22">
-        <v>0</v>
-      </c>
-      <c r="I10" s="29">
-        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>1.37</v>
-      </c>
-      <c r="J10" s="22">
-        <v>2</v>
-      </c>
-      <c r="K10" s="30">
-        <f t="shared" si="0"/>
-        <v>0.62999999999999989</v>
-      </c>
-      <c r="L10" s="30">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>45.985401459854003</v>
-      </c>
-      <c r="M10" s="30">
-        <f t="shared" si="1"/>
-        <v>31.499999999999993</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A11" s="11" t="s">
+      <c r="C13" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D13" s="12">
+        <v>260</v>
+      </c>
+      <c r="E13" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" s="22">
-        <v>1.37</v>
-      </c>
-      <c r="G11" s="22">
-        <v>0</v>
-      </c>
-      <c r="H11" s="22">
-        <v>0</v>
-      </c>
-      <c r="I11" s="29">
-        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>1.37</v>
-      </c>
-      <c r="J11" s="22">
-        <v>2</v>
-      </c>
-      <c r="K11" s="30">
-        <f t="shared" si="0"/>
-        <v>0.62999999999999989</v>
-      </c>
-      <c r="L11" s="30">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>45.985401459854003</v>
-      </c>
-      <c r="M11" s="30">
-        <f t="shared" si="1"/>
-        <v>31.499999999999993</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A12" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="12">
-        <v>8</v>
-      </c>
-      <c r="C12" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="D12" s="13">
+      <c r="F13" s="21">
+        <f>(B13+SKUTable[[#This Row],[运费(元/500g)]])*D13/500</f>
+        <v>4.42</v>
+      </c>
+      <c r="G13" s="21">
+        <v>0.82</v>
+      </c>
+      <c r="H13" s="21">
+        <v>0.2</v>
+      </c>
+      <c r="I13" s="28">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
+        <v>5.44</v>
+      </c>
+      <c r="J13" s="21">
+        <v>16</v>
+      </c>
+      <c r="K13" s="29">
+        <f t="shared" si="0"/>
+        <v>10.559999999999999</v>
+      </c>
+      <c r="L13" s="29">
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
+        <v>194.11764705882348</v>
+      </c>
+      <c r="M13" s="29">
+        <f t="shared" si="1"/>
+        <v>65.999999999999986</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="11">
+        <v>10</v>
+      </c>
+      <c r="C14" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D14" s="12">
         <v>165</v>
       </c>
-      <c r="E12" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" s="22">
-        <f>(B12+SKUTable[[#This Row],[运费(元/500g)]])*D12/500</f>
-        <v>2.7390000000000003</v>
-      </c>
-      <c r="G12" s="22">
-        <v>0.68500000000000005</v>
-      </c>
-      <c r="H12" s="22">
-        <v>0.2</v>
-      </c>
-      <c r="I12" s="29">
-        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>3.6240000000000006</v>
-      </c>
-      <c r="J12" s="22">
-        <v>12</v>
-      </c>
-      <c r="K12" s="30">
-        <f t="shared" si="0"/>
-        <v>8.3759999999999994</v>
-      </c>
-      <c r="L12" s="30">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>231.1258278145695</v>
-      </c>
-      <c r="M12" s="30">
-        <f t="shared" si="1"/>
-        <v>69.8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A13" s="15" t="s">
+      <c r="E14" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="12">
-        <v>8</v>
-      </c>
-      <c r="C13" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="D13" s="13">
-        <v>260</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" s="22">
-        <f>(B13+SKUTable[[#This Row],[运费(元/500g)]])*D13/500</f>
-        <v>4.3159999999999998</v>
-      </c>
-      <c r="G13" s="22">
-        <v>0.82</v>
-      </c>
-      <c r="H13" s="22">
-        <v>0.2</v>
-      </c>
-      <c r="I13" s="29">
-        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>5.3360000000000003</v>
-      </c>
-      <c r="J13" s="22">
-        <v>16</v>
-      </c>
-      <c r="K13" s="30">
-        <f t="shared" si="0"/>
-        <v>10.664</v>
-      </c>
-      <c r="L13" s="30">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>199.85007496251873</v>
-      </c>
-      <c r="M13" s="30">
-        <f t="shared" si="1"/>
-        <v>66.649999999999991</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A14" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="12">
-        <v>10</v>
-      </c>
-      <c r="C14" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="D14" s="13">
-        <v>165</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="F14" s="22">
+      <c r="F14" s="21">
         <f>IF(B14&lt;&gt;"",B14*D14/500,"")</f>
         <v>3.3</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="21">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H14" s="22">
+      <c r="H14" s="21">
         <v>0.2</v>
       </c>
-      <c r="I14" s="29">
+      <c r="I14" s="28">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>4.1849999999999996</v>
       </c>
-      <c r="J14" s="22">
+      <c r="J14" s="21">
         <v>14</v>
       </c>
-      <c r="K14" s="30">
+      <c r="K14" s="29">
         <f t="shared" si="0"/>
         <v>9.8150000000000013</v>
       </c>
-      <c r="L14" s="30">
+      <c r="L14" s="29">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>234.52807646356041</v>
       </c>
-      <c r="M14" s="30">
+      <c r="M14" s="29">
         <f t="shared" si="1"/>
         <v>70.107142857142861</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A15" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="12">
+    <row r="15" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="11">
         <v>10</v>
       </c>
-      <c r="C15" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="D15" s="13">
+      <c r="C15" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D15" s="12">
         <v>260</v>
       </c>
-      <c r="E15" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="F15" s="22">
+      <c r="E15" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" s="21">
         <f>IF(B15&lt;&gt;"",B15*D15/500,"")</f>
         <v>5.2</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="21">
         <v>0.82</v>
       </c>
-      <c r="H15" s="22">
+      <c r="H15" s="21">
         <v>0.2</v>
       </c>
-      <c r="I15" s="29">
+      <c r="I15" s="28">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>6.2200000000000006</v>
       </c>
-      <c r="J15" s="22">
-        <v>18</v>
-      </c>
-      <c r="K15" s="30">
+      <c r="J15" s="21">
+        <v>18</v>
+      </c>
+      <c r="K15" s="29">
         <f t="shared" si="0"/>
         <v>11.78</v>
       </c>
-      <c r="L15" s="30">
+      <c r="L15" s="29">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>189.38906752411572</v>
       </c>
-      <c r="M15" s="30">
+      <c r="M15" s="29">
         <f t="shared" si="1"/>
         <v>65.444444444444443</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A16" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="12">
+    <row r="16" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="11">
         <v>12.5</v>
       </c>
-      <c r="C16" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="D16" s="13">
+      <c r="C16" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D16" s="12">
         <v>165</v>
       </c>
-      <c r="E16" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="22">
+      <c r="E16" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="21">
         <f>IF(B16&lt;&gt;"",B16*D16/500,"")</f>
         <v>4.125</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="21">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="21">
         <v>0.2</v>
       </c>
-      <c r="I16" s="29">
+      <c r="I16" s="28">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.0100000000000007</v>
       </c>
-      <c r="J16" s="22">
+      <c r="J16" s="21">
         <v>15</v>
       </c>
-      <c r="K16" s="30">
+      <c r="K16" s="29">
         <f t="shared" si="0"/>
         <v>9.9899999999999984</v>
       </c>
-      <c r="L16" s="30">
+      <c r="L16" s="29">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>199.40119760479035</v>
       </c>
-      <c r="M16" s="30">
+      <c r="M16" s="29">
         <f t="shared" si="1"/>
         <v>66.599999999999994</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A17" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="12">
+    <row r="17" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="11">
         <v>12.5</v>
       </c>
-      <c r="C17" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="D17" s="13">
+      <c r="C17" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D17" s="12">
         <v>260</v>
       </c>
-      <c r="E17" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="F17" s="22">
+      <c r="E17" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" s="21">
         <f>IF(B17&lt;&gt;"",B17*D17/500,"")</f>
         <v>6.5</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="21">
         <v>0.82</v>
       </c>
-      <c r="H17" s="22">
+      <c r="H17" s="21">
         <v>0.2</v>
       </c>
-      <c r="I17" s="29">
+      <c r="I17" s="28">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>7.5200000000000005</v>
       </c>
-      <c r="J17" s="22">
+      <c r="J17" s="21">
         <v>20</v>
       </c>
-      <c r="K17" s="30">
+      <c r="K17" s="29">
         <f t="shared" si="0"/>
         <v>12.48</v>
       </c>
-      <c r="L17" s="30">
+      <c r="L17" s="29">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>165.95744680851064</v>
       </c>
-      <c r="M17" s="30">
+      <c r="M17" s="29">
         <f t="shared" si="1"/>
         <v>62.4</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A18" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="12">
+    <row r="18" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="11">
         <v>17</v>
       </c>
-      <c r="C18" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="D18" s="13">
+      <c r="C18" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D18" s="12">
         <v>135</v>
       </c>
-      <c r="E18" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="F18" s="22">
+      <c r="E18" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="21">
         <f t="shared" ref="F18" si="2">IF(B18&lt;&gt;"",B18*D18/500,"")</f>
         <v>4.59</v>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="21">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H18" s="22">
+      <c r="H18" s="21">
         <v>0.2</v>
       </c>
-      <c r="I18" s="29">
+      <c r="I18" s="28">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.4750000000000005</v>
       </c>
-      <c r="J18" s="22">
+      <c r="J18" s="21">
         <v>15</v>
       </c>
-      <c r="K18" s="30">
+      <c r="K18" s="29">
         <f t="shared" ref="K18" si="3">J18-(F18+G18+H18)</f>
         <v>9.5249999999999986</v>
       </c>
-      <c r="L18" s="30">
+      <c r="L18" s="29">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>173.972602739726</v>
       </c>
-      <c r="M18" s="30">
+      <c r="M18" s="29">
         <f t="shared" ref="M18" si="4">(J18-(F18+G18+H18))/J18*100</f>
         <v>63.499999999999993</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A19" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19" s="12">
+    <row r="19" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="11">
         <v>17</v>
       </c>
-      <c r="C19" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="D19" s="13">
+      <c r="C19" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D19" s="12">
         <v>165</v>
       </c>
-      <c r="E19" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="F19" s="22">
+      <c r="E19" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" s="21">
         <f t="shared" ref="F19:F35" si="5">IF(B19&lt;&gt;"",B19*D19/500,"")</f>
         <v>5.61</v>
       </c>
-      <c r="G19" s="22">
+      <c r="G19" s="21">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H19" s="22">
+      <c r="H19" s="21">
         <v>0.2</v>
       </c>
-      <c r="I19" s="29">
+      <c r="I19" s="28">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>6.4950000000000001</v>
       </c>
-      <c r="J19" s="22">
+      <c r="J19" s="21">
         <v>20</v>
       </c>
-      <c r="K19" s="30">
+      <c r="K19" s="29">
         <f t="shared" si="0"/>
         <v>13.504999999999999</v>
       </c>
-      <c r="L19" s="30">
+      <c r="L19" s="29">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>207.92917628945341</v>
       </c>
-      <c r="M19" s="30">
+      <c r="M19" s="29">
         <f t="shared" si="1"/>
         <v>67.524999999999991</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A20" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" s="12">
+    <row r="20" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="11">
         <v>17</v>
       </c>
-      <c r="C20" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="D20" s="13">
+      <c r="C20" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D20" s="12">
         <v>260</v>
       </c>
-      <c r="E20" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="F20" s="22">
+      <c r="E20" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" s="21">
         <f t="shared" si="5"/>
         <v>8.84</v>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="21">
         <v>0.82</v>
       </c>
-      <c r="H20" s="22">
+      <c r="H20" s="21">
         <v>0.2</v>
       </c>
-      <c r="I20" s="29">
+      <c r="I20" s="28">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>9.86</v>
       </c>
-      <c r="J20" s="22">
+      <c r="J20" s="21">
         <v>24</v>
       </c>
-      <c r="K20" s="30">
+      <c r="K20" s="29">
         <f t="shared" si="0"/>
         <v>14.14</v>
       </c>
-      <c r="L20" s="30">
+      <c r="L20" s="29">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>143.40770791075053</v>
       </c>
-      <c r="M20" s="30">
+      <c r="M20" s="29">
         <f t="shared" si="1"/>
         <v>58.916666666666671</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A21" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="B21" s="12">
+    <row r="21" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="11">
         <v>22.5</v>
       </c>
-      <c r="C21" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="D21" s="13">
+      <c r="C21" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D21" s="12">
         <v>100</v>
       </c>
-      <c r="E21" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="F21" s="22">
+      <c r="E21" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="F21" s="21">
         <f t="shared" si="5"/>
         <v>4.5</v>
       </c>
-      <c r="G21" s="22">
+      <c r="G21" s="21">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H21" s="22">
+      <c r="H21" s="21">
         <v>0.2</v>
       </c>
-      <c r="I21" s="29">
+      <c r="I21" s="28">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.3850000000000007</v>
       </c>
-      <c r="J21" s="22">
-        <v>18</v>
-      </c>
-      <c r="K21" s="30">
+      <c r="J21" s="21">
+        <v>18</v>
+      </c>
+      <c r="K21" s="29">
         <f t="shared" si="0"/>
         <v>12.614999999999998</v>
       </c>
-      <c r="L21" s="30">
+      <c r="L21" s="29">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>234.26183844011135</v>
       </c>
-      <c r="M21" s="30">
+      <c r="M21" s="29">
         <f t="shared" si="1"/>
         <v>70.083333333333314</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A22" s="14" t="s">
+    <row r="22" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="11">
+        <v>19</v>
+      </c>
+      <c r="C22" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="29"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="29"/>
+    </row>
+    <row r="23" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="11">
+        <v>19</v>
+      </c>
+      <c r="C23" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D23" s="12">
+        <v>90</v>
+      </c>
+      <c r="E23" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="12">
-        <v>19</v>
-      </c>
-      <c r="C22" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="30"/>
-      <c r="L22" s="30"/>
-      <c r="M22" s="30"/>
-    </row>
-    <row r="23" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A23" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B23" s="12">
-        <v>19</v>
-      </c>
-      <c r="C23" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="D23" s="13">
-        <v>90</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="F23" s="22">
+      <c r="F23" s="21">
         <f t="shared" si="5"/>
         <v>3.42</v>
       </c>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22">
+      <c r="G23" s="21"/>
+      <c r="H23" s="21">
         <v>2.5</v>
       </c>
-      <c r="I23" s="29">
+      <c r="I23" s="28">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.92</v>
       </c>
-      <c r="J23" s="22">
+      <c r="J23" s="21">
         <v>16</v>
       </c>
-      <c r="K23" s="30">
+      <c r="K23" s="29">
         <f t="shared" si="0"/>
         <v>10.08</v>
       </c>
-      <c r="L23" s="30">
+      <c r="L23" s="29">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>170.27027027027026</v>
       </c>
-      <c r="M23" s="30">
+      <c r="M23" s="29">
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A24" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B24" s="12">
+    <row r="24" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="11">
         <v>19</v>
       </c>
-      <c r="C24" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="D24" s="13">
+      <c r="C24" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D24" s="12">
         <v>70</v>
       </c>
-      <c r="E24" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="F24" s="22">
+      <c r="E24" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24" s="21">
         <f t="shared" si="5"/>
         <v>2.66</v>
       </c>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22">
+      <c r="G24" s="21"/>
+      <c r="H24" s="21">
         <v>2.5</v>
       </c>
-      <c r="I24" s="29">
+      <c r="I24" s="28">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.16</v>
       </c>
-      <c r="J24" s="22">
+      <c r="J24" s="21">
         <v>16</v>
       </c>
-      <c r="K24" s="30">
+      <c r="K24" s="29">
         <f t="shared" si="0"/>
         <v>10.84</v>
       </c>
-      <c r="L24" s="30">
+      <c r="L24" s="29">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>210.07751937984494</v>
       </c>
-      <c r="M24" s="30">
+      <c r="M24" s="29">
         <f t="shared" si="1"/>
         <v>67.75</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A25" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="B25" s="12">
+    <row r="25" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="11">
         <v>9.09</v>
       </c>
-      <c r="C25" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="D25" s="13">
+      <c r="C25" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D25" s="12">
         <v>300</v>
       </c>
-      <c r="E25" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="F25" s="22">
+      <c r="E25" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F25" s="21">
         <f t="shared" si="5"/>
         <v>5.4539999999999997</v>
       </c>
-      <c r="G25" s="22">
+      <c r="G25" s="21">
         <v>0.82</v>
       </c>
-      <c r="H25" s="23">
+      <c r="H25" s="22">
         <v>0.5</v>
       </c>
-      <c r="I25" s="31">
+      <c r="I25" s="30">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>6.774</v>
       </c>
-      <c r="J25" s="22">
+      <c r="J25" s="21">
         <v>16</v>
       </c>
-      <c r="K25" s="30">
+      <c r="K25" s="29">
         <f t="shared" si="0"/>
         <v>9.2259999999999991</v>
       </c>
-      <c r="L25" s="30">
+      <c r="L25" s="29">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>136.19722468260997</v>
       </c>
-      <c r="M25" s="30">
+      <c r="M25" s="29">
         <f t="shared" si="1"/>
         <v>57.662499999999994</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A26" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="12">
+    <row r="26" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="11">
         <v>9.09</v>
       </c>
-      <c r="C26" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="D26" s="13">
+      <c r="C26" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D26" s="12">
         <v>165</v>
       </c>
-      <c r="E26" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="F26" s="22">
+      <c r="E26" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26" s="21">
         <f t="shared" si="5"/>
         <v>2.9996999999999998</v>
       </c>
-      <c r="G26" s="22">
+      <c r="G26" s="21">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H26" s="23">
+      <c r="H26" s="22">
         <v>1.5</v>
       </c>
-      <c r="I26" s="31">
+      <c r="I26" s="30">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.1846999999999994</v>
       </c>
-      <c r="J26" s="22">
+      <c r="J26" s="21">
         <v>14</v>
       </c>
-      <c r="K26" s="30">
+      <c r="K26" s="29">
         <f t="shared" si="0"/>
         <v>8.8153000000000006</v>
       </c>
-      <c r="L26" s="30">
+      <c r="L26" s="29">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>170.02526664995085</v>
       </c>
-      <c r="M26" s="30">
+      <c r="M26" s="29">
         <f t="shared" si="1"/>
         <v>62.96642857142858</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A27" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="B27" s="12">
+    <row r="27" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="11">
         <v>9.09</v>
       </c>
-      <c r="C27" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="D27" s="13">
+      <c r="C27" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D27" s="12">
         <v>260</v>
       </c>
-      <c r="E27" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="F27" s="22">
+      <c r="E27" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="F27" s="21">
         <f t="shared" si="5"/>
         <v>4.7267999999999999</v>
       </c>
-      <c r="G27" s="22">
+      <c r="G27" s="21">
         <v>0.82</v>
       </c>
-      <c r="H27" s="23">
+      <c r="H27" s="22">
         <v>1.5</v>
       </c>
-      <c r="I27" s="31">
+      <c r="I27" s="30">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>7.0468000000000002</v>
       </c>
-      <c r="J27" s="22">
-        <v>18</v>
-      </c>
-      <c r="K27" s="30">
+      <c r="J27" s="21">
+        <v>18</v>
+      </c>
+      <c r="K27" s="29">
         <f t="shared" si="0"/>
         <v>10.953199999999999</v>
       </c>
-      <c r="L27" s="30">
+      <c r="L27" s="29">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>155.43509110518247</v>
       </c>
-      <c r="M27" s="30">
+      <c r="M27" s="29">
         <f t="shared" si="1"/>
         <v>60.851111111111102</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A28" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B28" s="12">
+    <row r="28" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="11">
         <v>11.75</v>
       </c>
-      <c r="C28" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13">
+      <c r="C28" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="12">
         <v>35</v>
       </c>
-      <c r="E28" s="13"/>
-      <c r="F28" s="22">
+      <c r="E28" s="12"/>
+      <c r="F28" s="21">
         <f t="shared" si="5"/>
         <v>0.82250000000000001</v>
       </c>
-      <c r="G28" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="H28" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="I28" s="31">
+      <c r="G28" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" s="30">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>0.82250000000000001</v>
       </c>
-      <c r="J28" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="K28" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="L28" s="30"/>
-      <c r="M28" s="30" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A29" s="15" t="s">
+      <c r="J28" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="K28" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="L28" s="29"/>
+      <c r="M28" s="29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="11">
+        <v>8</v>
+      </c>
+      <c r="C29" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D29" s="12">
+        <v>165</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="F29" s="21">
+        <f t="shared" si="5"/>
+        <v>2.64</v>
+      </c>
+      <c r="G29" s="21">
+        <v>0.68500000000000005</v>
+      </c>
+      <c r="H29" s="22">
+        <v>1.2</v>
+      </c>
+      <c r="I29" s="30">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
+        <v>4.5250000000000004</v>
+      </c>
+      <c r="J29" s="21">
+        <v>14</v>
+      </c>
+      <c r="K29" s="29">
+        <f t="shared" si="0"/>
+        <v>9.4749999999999996</v>
+      </c>
+      <c r="L29" s="29">
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
+        <v>209.39226519337012</v>
+      </c>
+      <c r="M29" s="29">
+        <f t="shared" si="1"/>
+        <v>67.678571428571416</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="12">
-        <v>9.09</v>
-      </c>
-      <c r="C29" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="D29" s="13">
-        <v>165</v>
-      </c>
-      <c r="E29" s="20" t="s">
+      <c r="B30" s="11">
+        <v>8</v>
+      </c>
+      <c r="C30" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D30" s="12">
+        <v>260</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="F30" s="21">
+        <f t="shared" si="5"/>
+        <v>4.16</v>
+      </c>
+      <c r="G30" s="21">
+        <v>0.82</v>
+      </c>
+      <c r="H30" s="22">
+        <v>1.2</v>
+      </c>
+      <c r="I30" s="30">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
+        <v>6.1800000000000006</v>
+      </c>
+      <c r="J30" s="21">
+        <v>18</v>
+      </c>
+      <c r="K30" s="29">
+        <f t="shared" si="0"/>
+        <v>11.82</v>
+      </c>
+      <c r="L30" s="29">
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
+        <v>191.26213592233009</v>
+      </c>
+      <c r="M30" s="29">
+        <f t="shared" si="1"/>
+        <v>65.666666666666671</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="F29" s="22">
-        <f t="shared" si="5"/>
-        <v>2.9996999999999998</v>
-      </c>
-      <c r="G29" s="22">
-        <v>0.68500000000000005</v>
-      </c>
-      <c r="H29" s="23">
-        <v>1.2</v>
-      </c>
-      <c r="I29" s="31">
-        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>4.8846999999999996</v>
-      </c>
-      <c r="J29" s="22">
-        <v>14</v>
-      </c>
-      <c r="K29" s="30">
-        <f t="shared" si="0"/>
-        <v>9.1153000000000013</v>
-      </c>
-      <c r="L29" s="30">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>186.60920834442243</v>
-      </c>
-      <c r="M29" s="30">
-        <f t="shared" si="1"/>
-        <v>65.109285714285718</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A30" s="15" t="s">
+      <c r="B31" s="11">
+        <v>2.875</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="16">
+        <v>140</v>
+      </c>
+      <c r="E31" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="12">
-        <v>9.09</v>
-      </c>
-      <c r="C30" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="D30" s="13">
-        <v>260</v>
-      </c>
-      <c r="E30" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="F30" s="22">
-        <f t="shared" si="5"/>
-        <v>4.7267999999999999</v>
-      </c>
-      <c r="G30" s="22">
-        <v>0.82</v>
-      </c>
-      <c r="H30" s="23">
-        <v>1.2</v>
-      </c>
-      <c r="I30" s="31">
-        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>6.7468000000000004</v>
-      </c>
-      <c r="J30" s="22">
-        <v>18</v>
-      </c>
-      <c r="K30" s="30">
-        <f t="shared" si="0"/>
-        <v>11.2532</v>
-      </c>
-      <c r="L30" s="30">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>166.7931463805063</v>
-      </c>
-      <c r="M30" s="30">
-        <f t="shared" si="1"/>
-        <v>62.517777777777773</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A31" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="B31" s="12">
-        <v>2.875</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="17">
-        <v>140</v>
-      </c>
-      <c r="E31" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="F31" s="22">
+      <c r="F31" s="21">
         <f t="shared" si="5"/>
         <v>0.80500000000000005</v>
       </c>
-      <c r="G31" s="22">
+      <c r="G31" s="21">
         <v>0.82</v>
       </c>
-      <c r="H31" s="22">
+      <c r="H31" s="21">
         <v>4.0999999999999996</v>
       </c>
-      <c r="I31" s="29">
+      <c r="I31" s="28">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.7249999999999996</v>
       </c>
-      <c r="J31" s="22">
+      <c r="J31" s="21">
         <v>16</v>
       </c>
-      <c r="K31" s="30">
+      <c r="K31" s="29">
         <f t="shared" si="0"/>
         <v>10.275</v>
       </c>
-      <c r="L31" s="30">
+      <c r="L31" s="29">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>179.47598253275109</v>
       </c>
-      <c r="M31" s="30">
+      <c r="M31" s="29">
         <f t="shared" si="1"/>
         <v>64.21875</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A32" s="15" t="s">
+    <row r="32" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D32" s="12"/>
+      <c r="E32" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F32" s="21">
+        <v>3.88</v>
+      </c>
+      <c r="G32" s="21">
+        <v>0.68500000000000005</v>
+      </c>
+      <c r="H32" s="21">
+        <v>0.2</v>
+      </c>
+      <c r="I32" s="28">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
+        <v>4.7649999999999997</v>
+      </c>
+      <c r="J32" s="21">
+        <v>14</v>
+      </c>
+      <c r="K32" s="29">
+        <f t="shared" si="0"/>
+        <v>9.2349999999999994</v>
+      </c>
+      <c r="L32" s="29">
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
+        <v>193.80902413431269</v>
+      </c>
+      <c r="M32" s="29">
+        <f t="shared" si="1"/>
+        <v>65.964285714285708</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="D32" s="13"/>
-      <c r="E32" s="20" t="s">
+      <c r="B33" s="11"/>
+      <c r="C33" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D33" s="12"/>
+      <c r="E33" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="F32" s="22">
-        <v>3.88</v>
-      </c>
-      <c r="G32" s="22">
+      <c r="F33" s="21">
+        <v>5.28</v>
+      </c>
+      <c r="G33" s="21">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H32" s="22">
+      <c r="H33" s="21">
         <v>0.2</v>
       </c>
-      <c r="I32" s="29">
-        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>4.7649999999999997</v>
-      </c>
-      <c r="J32" s="22">
-        <v>14</v>
-      </c>
-      <c r="K32" s="30">
-        <f t="shared" si="0"/>
-        <v>9.2349999999999994</v>
-      </c>
-      <c r="L32" s="30">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>193.80902413431269</v>
-      </c>
-      <c r="M32" s="30">
-        <f t="shared" si="1"/>
-        <v>65.964285714285708</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A33" s="15" t="s">
+      <c r="I33" s="28">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
+        <v>6.165</v>
+      </c>
+      <c r="J33" s="21">
+        <v>15</v>
+      </c>
+      <c r="K33" s="29">
+        <f t="shared" si="0"/>
+        <v>8.8350000000000009</v>
+      </c>
+      <c r="L33" s="29">
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
+        <v>143.30900243309003</v>
+      </c>
+      <c r="M33" s="29">
+        <f t="shared" si="1"/>
+        <v>58.900000000000006</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="D33" s="13"/>
-      <c r="E33" s="20" t="s">
+      <c r="B34" s="11"/>
+      <c r="C34" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D34" s="12">
+        <v>370</v>
+      </c>
+      <c r="E34" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="F33" s="22">
-        <v>5.28</v>
-      </c>
-      <c r="G33" s="22">
-        <v>0.68500000000000005</v>
-      </c>
-      <c r="H33" s="22">
+      <c r="F34" s="21">
+        <v>6.64</v>
+      </c>
+      <c r="G34" s="21">
+        <v>0.82</v>
+      </c>
+      <c r="H34" s="21">
         <v>0.2</v>
       </c>
-      <c r="I33" s="29">
-        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>6.165</v>
-      </c>
-      <c r="J33" s="22">
-        <v>15</v>
-      </c>
-      <c r="K33" s="30">
-        <f t="shared" si="0"/>
-        <v>8.8350000000000009</v>
-      </c>
-      <c r="L33" s="30">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>143.30900243309003</v>
-      </c>
-      <c r="M33" s="30">
-        <f t="shared" si="1"/>
-        <v>58.900000000000006</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A34" s="15" t="s">
+      <c r="I34" s="28">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
+        <v>7.66</v>
+      </c>
+      <c r="J34" s="21">
+        <v>24</v>
+      </c>
+      <c r="K34" s="29">
+        <f t="shared" si="0"/>
+        <v>16.34</v>
+      </c>
+      <c r="L34" s="29">
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
+        <v>213.31592689295042</v>
+      </c>
+      <c r="M34" s="29">
+        <f t="shared" si="1"/>
+        <v>68.083333333333329</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="D34" s="13">
-        <v>370</v>
-      </c>
-      <c r="E34" s="20" t="s">
+      <c r="B35" s="17">
+        <v>4.5</v>
+      </c>
+      <c r="C35" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D35" s="12">
+        <v>125</v>
+      </c>
+      <c r="E35" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="F34" s="22">
-        <v>6.64</v>
-      </c>
-      <c r="G34" s="22">
-        <v>0.82</v>
-      </c>
-      <c r="H34" s="22">
-        <v>0.2</v>
-      </c>
-      <c r="I34" s="29">
-        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>7.66</v>
-      </c>
-      <c r="J34" s="22">
-        <v>24</v>
-      </c>
-      <c r="K34" s="30">
-        <f t="shared" si="0"/>
-        <v>16.34</v>
-      </c>
-      <c r="L34" s="30">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>213.31592689295042</v>
-      </c>
-      <c r="M34" s="30">
-        <f t="shared" si="1"/>
-        <v>68.083333333333329</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A35" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B35" s="18">
-        <v>4.5</v>
-      </c>
-      <c r="C35" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="D35" s="13">
-        <v>125</v>
-      </c>
-      <c r="E35" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="F35" s="22">
+      <c r="F35" s="21">
         <f t="shared" si="5"/>
         <v>1.125</v>
       </c>
-      <c r="G35" s="22">
+      <c r="G35" s="21">
         <v>0.82</v>
       </c>
-      <c r="H35" s="22">
+      <c r="H35" s="21">
         <v>4.0999999999999996</v>
       </c>
-      <c r="I35" s="29">
+      <c r="I35" s="28">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>6.0449999999999999</v>
       </c>
-      <c r="J35" s="22">
+      <c r="J35" s="21">
         <v>16</v>
       </c>
-      <c r="K35" s="30">
+      <c r="K35" s="29">
         <f t="shared" si="0"/>
         <v>9.9550000000000001</v>
       </c>
-      <c r="L35" s="30">
+      <c r="L35" s="29">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>164.68155500413565</v>
       </c>
-      <c r="M35" s="30">
+      <c r="M35" s="29">
         <f t="shared" si="1"/>
         <v>62.21875</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A36" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="D36" s="13"/>
-      <c r="E36" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F36" s="22">
-        <v>2.84</v>
-      </c>
-      <c r="G36" s="22">
+    <row r="36" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D36" s="12"/>
+      <c r="E36" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="F36" s="21">
+        <v>2.1</v>
+      </c>
+      <c r="G36" s="21">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H36" s="22">
+      <c r="H36" s="21">
         <v>2.5</v>
       </c>
-      <c r="I36" s="29">
-        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>6.0250000000000004</v>
-      </c>
-      <c r="J36" s="22">
+      <c r="I36" s="28">
+        <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
+        <v>5.2850000000000001</v>
+      </c>
+      <c r="J36" s="21">
         <v>15</v>
       </c>
-      <c r="K36" s="30">
-        <f t="shared" si="0"/>
-        <v>8.9749999999999996</v>
-      </c>
-      <c r="L36" s="30">
-        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>148.96265560165972</v>
-      </c>
-      <c r="M36" s="30">
-        <f t="shared" si="1"/>
-        <v>59.833333333333329</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
+      <c r="K36" s="29">
+        <f t="shared" si="0"/>
+        <v>9.7149999999999999</v>
+      </c>
+      <c r="L36" s="29">
+        <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
+        <v>183.82213812677389</v>
+      </c>
+      <c r="M36" s="29">
+        <f t="shared" si="1"/>
+        <v>64.766666666666666</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.15">
       <c r="E40" s="7"/>
     </row>
   </sheetData>

--- a/财务与流水/馋唻买-听涛路店商品表.xlsx
+++ b/财务与流水/馋唻买-听涛路店商品表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Github\ChanWeiMai\财务与流水\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E69D4097-17BF-4F61-9257-0D2D743E9255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0687CCF5-656C-42DA-A50D-02F12182150A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -206,9 +206,6 @@
     <t>金汤酸菜瘦肉丸(370g)</t>
   </si>
   <si>
-    <t>金汤酸菜泡面+瘦肉丸(特大份)</t>
-  </si>
-  <si>
     <t>金汤、酸菜、瘦肉丸、泡面、调味品</t>
   </si>
   <si>
@@ -230,13 +227,7 @@
     <t>瘦肉丸、肉燕、肉牛瘦肉丸、调味品</t>
   </si>
   <si>
-    <t>金汤酸菜弹粉+瘦肉丸(特大份)</t>
-  </si>
-  <si>
     <t>金汤、酸菜、弹粉、瘦肉丸、调味品</t>
-  </si>
-  <si>
-    <t>火鸡面拌瘦肉丸</t>
   </si>
   <si>
     <t>火鸡面、瘦肉丸、调味品</t>
@@ -247,6 +238,18 @@
   </si>
   <si>
     <t>每份制作重量(g)</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>火鸡面拌瘦肉丸(119+90)</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>金汤酸菜泡面+瘦肉丸(370g)</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>金汤酸菜弹粉+瘦肉丸(特大碗)</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
@@ -259,7 +262,7 @@
     <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
     <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -360,6 +363,14 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -420,7 +431,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -515,6 +526,9 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1145,7 +1159,7 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="32" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -1154,7 +1168,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="31" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>2</v>
@@ -1337,29 +1351,29 @@
         <v>2</v>
       </c>
       <c r="G5" s="20">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="H5" s="20">
         <v>0</v>
       </c>
       <c r="I5" s="25">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>2.02</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="J5" s="26">
         <v>5</v>
       </c>
       <c r="K5" s="27">
         <f t="shared" si="0"/>
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="L5" s="27">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>147.52475247524751</v>
+        <v>143.90243902439025</v>
       </c>
       <c r="M5" s="27">
         <f t="shared" si="1"/>
-        <v>59.599999999999994</v>
+        <v>59.000000000000007</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -1379,32 +1393,32 @@
         <v>21</v>
       </c>
       <c r="F6" s="20">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="G6" s="20">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="H6" s="20">
         <v>0</v>
       </c>
       <c r="I6" s="25">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>5.0199999999999996</v>
+        <v>2.8499999999999996</v>
       </c>
       <c r="J6" s="26">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K6" s="27">
         <f t="shared" si="0"/>
-        <v>2.9800000000000004</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="L6" s="27">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>59.362549800796828</v>
+        <v>110.52631578947371</v>
       </c>
       <c r="M6" s="27">
         <f t="shared" si="1"/>
-        <v>37.250000000000007</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -1572,19 +1586,19 @@
         <v>1.37</v>
       </c>
       <c r="J10" s="21">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="K10" s="29">
         <f t="shared" si="0"/>
-        <v>0.62999999999999989</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="L10" s="29">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>45.985401459854003</v>
+        <v>82.481751824817508</v>
       </c>
       <c r="M10" s="29">
         <f t="shared" si="1"/>
-        <v>31.499999999999993</v>
+        <v>45.199999999999996</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -1617,19 +1631,19 @@
         <v>1.37</v>
       </c>
       <c r="J11" s="21">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="K11" s="29">
         <f t="shared" si="0"/>
-        <v>0.62999999999999989</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="L11" s="29">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>45.985401459854003</v>
+        <v>82.481751824817508</v>
       </c>
       <c r="M11" s="29">
         <f t="shared" si="1"/>
-        <v>31.499999999999993</v>
+        <v>45.199999999999996</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -2475,8 +2489,8 @@
       </c>
     </row>
     <row r="31" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="10" t="s">
-        <v>57</v>
+      <c r="A31" s="33" t="s">
+        <v>69</v>
       </c>
       <c r="B31" s="11">
         <v>2.875</v>
@@ -2488,7 +2502,7 @@
         <v>140</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F31" s="21">
         <f t="shared" si="5"/>
@@ -2522,7 +2536,7 @@
     </row>
     <row r="32" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11">
@@ -2530,7 +2544,7 @@
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F32" s="21">
         <v>3.88</v>
@@ -2563,7 +2577,7 @@
     </row>
     <row r="33" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11">
@@ -2571,7 +2585,7 @@
       </c>
       <c r="D33" s="12"/>
       <c r="E33" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F33" s="21">
         <v>5.28</v>
@@ -2604,7 +2618,7 @@
     </row>
     <row r="34" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11">
@@ -2614,7 +2628,7 @@
         <v>370</v>
       </c>
       <c r="E34" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F34" s="21">
         <v>6.64</v>
@@ -2646,8 +2660,8 @@
       </c>
     </row>
     <row r="35" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="10" t="s">
-        <v>65</v>
+      <c r="A35" s="33" t="s">
+        <v>70</v>
       </c>
       <c r="B35" s="17">
         <v>4.5</v>
@@ -2656,80 +2670,82 @@
         <v>0.5</v>
       </c>
       <c r="D35" s="12">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F35" s="21">
         <f t="shared" si="5"/>
-        <v>1.125</v>
+        <v>1.8</v>
       </c>
       <c r="G35" s="21">
         <v>0.82</v>
       </c>
       <c r="H35" s="21">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="I35" s="28">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>6.0449999999999999</v>
+        <v>6.62</v>
       </c>
       <c r="J35" s="21">
         <v>16</v>
       </c>
       <c r="K35" s="29">
         <f t="shared" si="0"/>
-        <v>9.9550000000000001</v>
+        <v>9.379999999999999</v>
       </c>
       <c r="L35" s="29">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>164.68155500413565</v>
+        <v>141.69184290030211</v>
       </c>
       <c r="M35" s="29">
         <f t="shared" si="1"/>
-        <v>62.21875</v>
+        <v>58.624999999999993</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="10" t="s">
-        <v>67</v>
+      <c r="A36" s="33" t="s">
+        <v>68</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11">
         <v>0.5</v>
       </c>
-      <c r="D36" s="12"/>
+      <c r="D36" s="12">
+        <v>185</v>
+      </c>
       <c r="E36" s="19" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F36" s="21">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="G36" s="21">
         <v>0.68500000000000005</v>
       </c>
       <c r="H36" s="21">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="I36" s="28">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>5.2850000000000001</v>
+        <v>4.585</v>
       </c>
       <c r="J36" s="21">
         <v>15</v>
       </c>
       <c r="K36" s="29">
         <f t="shared" si="0"/>
-        <v>9.7149999999999999</v>
+        <v>10.414999999999999</v>
       </c>
       <c r="L36" s="29">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>183.82213812677389</v>
+        <v>227.15376226826604</v>
       </c>
       <c r="M36" s="29">
         <f t="shared" si="1"/>
-        <v>64.766666666666666</v>
+        <v>69.433333333333323</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.15">

--- a/财务与流水/馋唻买-听涛路店商品表.xlsx
+++ b/财务与流水/馋唻买-听涛路店商品表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="15820" activeTab="1"/>
+    <workbookView windowHeight="15860" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="堂食利润" sheetId="1" r:id="rId1"/>
@@ -3448,7 +3448,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7daa8060-6165-449c-a58f-5ac634e1bb04}</x14:id>
+          <x14:id>{79fe3af2-6cac-487e-88f3-e045e147a1c6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3463,7 +3463,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7daa8060-6165-449c-a58f-5ac634e1bb04}">
+          <x14:cfRule type="dataBar" id="{79fe3af2-6cac-487e-88f3-e045e147a1c6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -3664,7 +3664,7 @@
         <v>91</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
         <v>85</v>
@@ -3692,7 +3692,7 @@
         <v>93</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
         <v>85</v>

--- a/财务与流水/馋唻买-听涛路店商品表.xlsx
+++ b/财务与流水/馋唻买-听涛路店商品表.xlsx
@@ -272,7 +272,7 @@
     <t>牛肉羹瘦肉丸</t>
   </si>
   <si>
-    <t>24元</t>
+    <t>20元</t>
   </si>
   <si>
     <t>剁椒干拌瘦肉丸</t>
@@ -302,7 +302,7 @@
     <t>火鸡面拌瘦肉丸</t>
   </si>
   <si>
-    <t>200克</t>
+    <t>约240克</t>
   </si>
   <si>
     <t>特色口味</t>
@@ -3448,7 +3448,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{79fe3af2-6cac-487e-88f3-e045e147a1c6}</x14:id>
+          <x14:id>{ec170b43-6ed5-48d1-89d8-1875d0c16cd8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3463,7 +3463,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{79fe3af2-6cac-487e-88f3-e045e147a1c6}">
+          <x14:cfRule type="dataBar" id="{ec170b43-6ed5-48d1-89d8-1875d0c16cd8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -3569,7 +3569,7 @@
         <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
         <v>78</v>
@@ -3597,7 +3597,7 @@
         <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
         <v>78</v>
@@ -3611,7 +3611,7 @@
         <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
         <v>78</v>
@@ -3653,7 +3653,7 @@
         <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
         <v>92</v>
@@ -3681,7 +3681,7 @@
         <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D16" t="s">
         <v>92</v>
@@ -3807,7 +3807,7 @@
         <v>104</v>
       </c>
       <c r="C28" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="D28" t="s">
         <v>102</v>

--- a/财务与流水/馋唻买-听涛路店商品表.xlsx
+++ b/财务与流水/馋唻买-听涛路店商品表.xlsx
@@ -3448,7 +3448,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ec170b43-6ed5-48d1-89d8-1875d0c16cd8}</x14:id>
+          <x14:id>{7e516038-da46-4e69-93a5-b3125136e3da}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3463,7 +3463,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ec170b43-6ed5-48d1-89d8-1875d0c16cd8}">
+          <x14:cfRule type="dataBar" id="{7e516038-da46-4e69-93a5-b3125136e3da}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -3807,7 +3807,7 @@
         <v>104</v>
       </c>
       <c r="C28" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="D28" t="s">
         <v>102</v>

--- a/财务与流水/馋唻买-听涛路店商品表.xlsx
+++ b/财务与流水/馋唻买-听涛路店商品表.xlsx
@@ -1527,8 +1527,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="表3" displayName="表3" ref="A1:D44" totalsRowShown="0">
-  <autoFilter ref="A1:D44"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="表3" displayName="表3" ref="A1:D45" totalsRowShown="0">
+  <autoFilter ref="A1:D45"/>
   <tableColumns count="4">
     <tableColumn id="1" name="菜品名"/>
     <tableColumn id="2" name="规格"/>
@@ -3448,7 +3448,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7e516038-da46-4e69-93a5-b3125136e3da}</x14:id>
+          <x14:id>{a810df6f-8cec-4f7d-8525-51eb8ad54209}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3463,7 +3463,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7e516038-da46-4e69-93a5-b3125136e3da}">
+          <x14:cfRule type="dataBar" id="{a810df6f-8cec-4f7d-8525-51eb8ad54209}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -3484,7 +3484,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultColWidth="20.6923076923077" defaultRowHeight="20" customHeight="1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="31.8942307692308" customWidth="1"/>
@@ -3785,29 +3785,15 @@
         <v>96</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="1:4">
-      <c r="A27" t="s">
+    <row r="28" customHeight="1" spans="1:4">
+      <c r="A28" t="s">
         <v>15</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>101</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C28" t="s">
         <v>100</v>
-      </c>
-      <c r="D27" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="28" customFormat="1" customHeight="1" spans="1:4">
-      <c r="A28" t="s">
-        <v>103</v>
-      </c>
-      <c r="B28" t="s">
-        <v>104</v>
-      </c>
-      <c r="C28" t="s">
-        <v>77</v>
       </c>
       <c r="D28" t="s">
         <v>102</v>
@@ -3815,7 +3801,7 @@
     </row>
     <row r="29" customFormat="1" customHeight="1" spans="1:4">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="B29" t="s">
         <v>104</v>
@@ -3829,13 +3815,13 @@
     </row>
     <row r="30" customFormat="1" customHeight="1" spans="1:4">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C30" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="D30" t="s">
         <v>102</v>
@@ -3843,10 +3829,10 @@
     </row>
     <row r="31" customFormat="1" customHeight="1" spans="1:4">
       <c r="A31" t="s">
-        <v>105</v>
+        <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C31" t="s">
         <v>100</v>
@@ -3855,15 +3841,15 @@
         <v>102</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="1:4">
+    <row r="32" customFormat="1" customHeight="1" spans="1:4">
       <c r="A32" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
       <c r="B32" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D32" t="s">
         <v>102</v>
@@ -3871,13 +3857,13 @@
     </row>
     <row r="33" customHeight="1" spans="1:4">
       <c r="A33" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B33" t="s">
         <v>107</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D33" t="s">
         <v>102</v>
@@ -3885,15 +3871,29 @@
     </row>
     <row r="34" customHeight="1" spans="1:4">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B34" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C34" t="s">
         <v>109</v>
       </c>
       <c r="D34" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:4">
+      <c r="A35" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" t="s">
+        <v>110</v>
+      </c>
+      <c r="C35" t="s">
+        <v>109</v>
+      </c>
+      <c r="D35" t="s">
         <v>102</v>
       </c>
     </row>

--- a/财务与流水/馋唻买-听涛路店商品表.xlsx
+++ b/财务与流水/馋唻买-听涛路店商品表.xlsx
@@ -3448,7 +3448,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a810df6f-8cec-4f7d-8525-51eb8ad54209}</x14:id>
+          <x14:id>{419032ec-fb80-43c0-9c6b-7e01a062ea6d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3463,7 +3463,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a810df6f-8cec-4f7d-8525-51eb8ad54209}">
+          <x14:cfRule type="dataBar" id="{419032ec-fb80-43c0-9c6b-7e01a062ea6d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/财务与流水/馋唻买-听涛路店商品表.xlsx
+++ b/财务与流水/馋唻买-听涛路店商品表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15860" activeTab="1"/>
+    <workbookView windowHeight="15820" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="堂食利润" sheetId="1" r:id="rId1"/>
@@ -355,15 +355,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
-    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="177" formatCode="0.000_);\(0.000\)"/>
+    <numFmt numFmtId="176" formatCode="0.000_);\(0.000\)"/>
+    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
     <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -394,13 +394,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -409,13 +402,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -482,7 +468,53 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -496,17 +528,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -521,46 +545,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -569,13 +562,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -627,7 +613,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -639,7 +625,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -651,19 +679,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -675,13 +721,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -699,25 +751,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -729,13 +763,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -747,55 +781,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -848,51 +834,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -914,6 +859,47 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -930,152 +916,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1096,13 +1082,13 @@
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1111,61 +1097,55 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1417,7 +1397,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="3" tint="0.799920651875362"/>
@@ -1857,31 +1837,31 @@
       <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="I1" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="20" t="s">
+      <c r="K1" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="20" t="s">
+      <c r="L1" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="M1" s="18" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1898,35 +1878,35 @@
       <c r="D2" s="14">
         <v>120</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="20">
         <f>(B2+SKUTable[[#This Row],[运费(元/500g)]])*D2/500</f>
         <v>2.76</v>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="20">
         <v>0.2</v>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="20">
         <v>0.15</v>
       </c>
-      <c r="I2" s="26">
+      <c r="I2" s="24">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>3.11</v>
       </c>
-      <c r="J2" s="27">
+      <c r="J2" s="25">
         <v>8</v>
       </c>
-      <c r="K2" s="28">
+      <c r="K2" s="26">
         <f>J2-(F2+G2+H2)</f>
         <v>4.89</v>
       </c>
-      <c r="L2" s="28">
+      <c r="L2" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>157.234726688103</v>
       </c>
-      <c r="M2" s="28">
+      <c r="M2" s="26">
         <f>(J2-(F2+G2+H2))/J2*100</f>
         <v>61.125</v>
       </c>
@@ -1940,34 +1920,34 @@
       <c r="D3" s="14">
         <v>220</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="20">
         <v>2.45</v>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="20">
         <v>0.2</v>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="20">
         <v>0.15</v>
       </c>
-      <c r="I3" s="26">
+      <c r="I3" s="24">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>2.8</v>
       </c>
-      <c r="J3" s="27">
+      <c r="J3" s="25">
         <v>8</v>
       </c>
-      <c r="K3" s="28">
+      <c r="K3" s="26">
         <f>J3-(F3+G3+H3)</f>
         <v>5.2</v>
       </c>
-      <c r="L3" s="28">
+      <c r="L3" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>185.714285714286</v>
       </c>
-      <c r="M3" s="28">
+      <c r="M3" s="26">
         <f>(J3-(F3+G3+H3))/J3*100</f>
         <v>65</v>
       </c>
@@ -1985,35 +1965,35 @@
       <c r="D4" s="14">
         <v>70</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="20">
         <f>(B4+SKUTable[[#This Row],[运费(元/500g)]])*D4/500</f>
         <v>1.232</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="20">
         <v>0.05</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="20">
         <v>0</v>
       </c>
-      <c r="I4" s="26">
+      <c r="I4" s="24">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>1.282</v>
       </c>
-      <c r="J4" s="27">
+      <c r="J4" s="25">
         <v>4</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="26">
         <f t="shared" ref="K4:K36" si="0">J4-(F4+G4+H4)</f>
         <v>2.718</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>212.01248049922</v>
       </c>
-      <c r="M4" s="28">
+      <c r="M4" s="26">
         <f t="shared" ref="M4:M36" si="1">(J4-(F4+G4+H4))/J4*100</f>
         <v>67.95</v>
       </c>
@@ -2031,34 +2011,34 @@
       <c r="D5" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="20">
         <v>2</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="20">
         <v>0.05</v>
       </c>
-      <c r="H5" s="22">
+      <c r="H5" s="20">
         <v>0</v>
       </c>
-      <c r="I5" s="26">
+      <c r="I5" s="24">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>2.05</v>
       </c>
-      <c r="J5" s="27">
+      <c r="J5" s="25">
         <v>5</v>
       </c>
-      <c r="K5" s="28">
+      <c r="K5" s="26">
         <f t="shared" si="0"/>
         <v>2.95</v>
       </c>
-      <c r="L5" s="28">
+      <c r="L5" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>143.90243902439</v>
       </c>
-      <c r="M5" s="28">
+      <c r="M5" s="26">
         <f t="shared" si="1"/>
         <v>59</v>
       </c>
@@ -2076,34 +2056,34 @@
       <c r="D6" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="20">
         <v>2.8</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="20">
         <v>0.05</v>
       </c>
-      <c r="H6" s="22">
+      <c r="H6" s="20">
         <v>0</v>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="24">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>2.85</v>
       </c>
-      <c r="J6" s="27">
+      <c r="J6" s="25">
         <v>6</v>
       </c>
-      <c r="K6" s="28">
+      <c r="K6" s="26">
         <f t="shared" si="0"/>
         <v>3.15</v>
       </c>
-      <c r="L6" s="28">
+      <c r="L6" s="26">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>110.526315789474</v>
       </c>
-      <c r="M6" s="28">
+      <c r="M6" s="26">
         <f t="shared" si="1"/>
         <v>52.5</v>
       </c>
@@ -2121,34 +2101,34 @@
       <c r="D7" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="21">
         <v>3.24</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="21">
         <v>0.2</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="21">
         <v>0</v>
       </c>
-      <c r="I7" s="29">
+      <c r="I7" s="27">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>3.44</v>
       </c>
-      <c r="J7" s="23">
+      <c r="J7" s="21">
         <v>8</v>
       </c>
-      <c r="K7" s="30">
+      <c r="K7" s="28">
         <f t="shared" si="0"/>
         <v>4.56</v>
       </c>
-      <c r="L7" s="30">
+      <c r="L7" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>132.558139534884</v>
       </c>
-      <c r="M7" s="30">
+      <c r="M7" s="28">
         <f t="shared" si="1"/>
         <v>57</v>
       </c>
@@ -2166,34 +2146,34 @@
       <c r="D8" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="21">
         <v>0.4</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="21">
         <v>0</v>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="21">
         <v>0</v>
       </c>
-      <c r="I8" s="29">
+      <c r="I8" s="27">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>0.4</v>
       </c>
-      <c r="J8" s="23">
+      <c r="J8" s="21">
         <v>1.25</v>
       </c>
-      <c r="K8" s="30">
+      <c r="K8" s="28">
         <f t="shared" si="0"/>
         <v>0.85</v>
       </c>
-      <c r="L8" s="30">
+      <c r="L8" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>212.5</v>
       </c>
-      <c r="M8" s="30">
+      <c r="M8" s="28">
         <f t="shared" si="1"/>
         <v>68</v>
       </c>
@@ -2211,34 +2191,34 @@
       <c r="D9" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="21">
         <v>0.45</v>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="21">
         <v>0</v>
       </c>
-      <c r="H9" s="23">
+      <c r="H9" s="21">
         <v>0</v>
       </c>
-      <c r="I9" s="29">
+      <c r="I9" s="27">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>0.45</v>
       </c>
-      <c r="J9" s="23">
+      <c r="J9" s="21">
         <v>1.25</v>
       </c>
-      <c r="K9" s="30">
+      <c r="K9" s="28">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="L9" s="30">
+      <c r="L9" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>177.777777777778</v>
       </c>
-      <c r="M9" s="30">
+      <c r="M9" s="28">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
@@ -2256,34 +2236,34 @@
       <c r="D10" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="21">
         <v>1.37</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="21">
         <v>0</v>
       </c>
-      <c r="H10" s="23">
+      <c r="H10" s="21">
         <v>0</v>
       </c>
-      <c r="I10" s="29">
+      <c r="I10" s="27">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>1.37</v>
       </c>
-      <c r="J10" s="23">
+      <c r="J10" s="21">
         <v>2.5</v>
       </c>
-      <c r="K10" s="30">
+      <c r="K10" s="28">
         <f t="shared" si="0"/>
         <v>1.13</v>
       </c>
-      <c r="L10" s="30">
+      <c r="L10" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>82.4817518248175</v>
       </c>
-      <c r="M10" s="30">
+      <c r="M10" s="28">
         <f t="shared" si="1"/>
         <v>45.2</v>
       </c>
@@ -2301,34 +2281,34 @@
       <c r="D11" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="21">
         <v>1.37</v>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="21">
         <v>0</v>
       </c>
-      <c r="H11" s="23">
+      <c r="H11" s="21">
         <v>0</v>
       </c>
-      <c r="I11" s="29">
+      <c r="I11" s="27">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>1.37</v>
       </c>
-      <c r="J11" s="23">
+      <c r="J11" s="21">
         <v>2.5</v>
       </c>
-      <c r="K11" s="30">
+      <c r="K11" s="28">
         <f t="shared" si="0"/>
         <v>1.13</v>
       </c>
-      <c r="L11" s="30">
+      <c r="L11" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>82.4817518248175</v>
       </c>
-      <c r="M11" s="30">
+      <c r="M11" s="28">
         <f t="shared" si="1"/>
         <v>45.2</v>
       </c>
@@ -2346,35 +2326,35 @@
       <c r="D12" s="14">
         <v>165</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="E12" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="21">
         <f>(B12+SKUTable[[#This Row],[运费(元/500g)]])*D12/500</f>
         <v>2.805</v>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="21">
         <v>0.685</v>
       </c>
-      <c r="H12" s="23">
+      <c r="H12" s="21">
         <v>0.2</v>
       </c>
-      <c r="I12" s="29">
+      <c r="I12" s="27">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>3.69</v>
       </c>
-      <c r="J12" s="23">
+      <c r="J12" s="21">
         <v>12</v>
       </c>
-      <c r="K12" s="30">
+      <c r="K12" s="28">
         <f t="shared" si="0"/>
         <v>8.31</v>
       </c>
-      <c r="L12" s="30">
+      <c r="L12" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>225.20325203252</v>
       </c>
-      <c r="M12" s="30">
+      <c r="M12" s="28">
         <f t="shared" si="1"/>
         <v>69.25</v>
       </c>
@@ -2392,35 +2372,35 @@
       <c r="D13" s="14">
         <v>260</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="21">
         <f>(B13+SKUTable[[#This Row],[运费(元/500g)]])*D13/500</f>
         <v>4.42</v>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="21">
         <v>0.82</v>
       </c>
-      <c r="H13" s="23">
+      <c r="H13" s="21">
         <v>0.2</v>
       </c>
-      <c r="I13" s="29">
+      <c r="I13" s="27">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.44</v>
       </c>
-      <c r="J13" s="23">
+      <c r="J13" s="21">
         <v>16</v>
       </c>
-      <c r="K13" s="30">
+      <c r="K13" s="28">
         <f t="shared" si="0"/>
         <v>10.56</v>
       </c>
-      <c r="L13" s="30">
+      <c r="L13" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>194.117647058823</v>
       </c>
-      <c r="M13" s="30">
+      <c r="M13" s="28">
         <f t="shared" si="1"/>
         <v>66</v>
       </c>
@@ -2438,35 +2418,35 @@
       <c r="D14" s="14">
         <v>165</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="E14" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="21">
         <f>IF(B14&lt;&gt;"",B14*D14/500,"")</f>
         <v>3.3</v>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="21">
         <v>0.685</v>
       </c>
-      <c r="H14" s="23">
+      <c r="H14" s="21">
         <v>0.2</v>
       </c>
-      <c r="I14" s="29">
+      <c r="I14" s="27">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>4.185</v>
       </c>
-      <c r="J14" s="23">
+      <c r="J14" s="21">
         <v>14</v>
       </c>
-      <c r="K14" s="30">
+      <c r="K14" s="28">
         <f t="shared" si="0"/>
         <v>9.815</v>
       </c>
-      <c r="L14" s="30">
+      <c r="L14" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>234.52807646356</v>
       </c>
-      <c r="M14" s="30">
+      <c r="M14" s="28">
         <f t="shared" si="1"/>
         <v>70.1071428571429</v>
       </c>
@@ -2484,35 +2464,35 @@
       <c r="D15" s="14">
         <v>260</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="23">
+      <c r="F15" s="21">
         <f>IF(B15&lt;&gt;"",B15*D15/500,"")</f>
         <v>5.2</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="21">
         <v>0.82</v>
       </c>
-      <c r="H15" s="23">
+      <c r="H15" s="21">
         <v>0.2</v>
       </c>
-      <c r="I15" s="29">
+      <c r="I15" s="27">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>6.22</v>
       </c>
-      <c r="J15" s="23">
+      <c r="J15" s="21">
         <v>18</v>
       </c>
-      <c r="K15" s="30">
+      <c r="K15" s="28">
         <f t="shared" si="0"/>
         <v>11.78</v>
       </c>
-      <c r="L15" s="30">
+      <c r="L15" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>189.389067524116</v>
       </c>
-      <c r="M15" s="30">
+      <c r="M15" s="28">
         <f t="shared" si="1"/>
         <v>65.4444444444444</v>
       </c>
@@ -2530,35 +2510,35 @@
       <c r="D16" s="14">
         <v>165</v>
       </c>
-      <c r="E16" s="21" t="s">
+      <c r="E16" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="23">
+      <c r="F16" s="21">
         <f>IF(B16&lt;&gt;"",B16*D16/500,"")</f>
         <v>4.125</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="21">
         <v>0.685</v>
       </c>
-      <c r="H16" s="23">
+      <c r="H16" s="21">
         <v>0.2</v>
       </c>
-      <c r="I16" s="29">
+      <c r="I16" s="27">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.01</v>
       </c>
-      <c r="J16" s="23">
+      <c r="J16" s="21">
         <v>15</v>
       </c>
-      <c r="K16" s="30">
+      <c r="K16" s="28">
         <f t="shared" si="0"/>
         <v>9.99</v>
       </c>
-      <c r="L16" s="30">
+      <c r="L16" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>199.40119760479</v>
       </c>
-      <c r="M16" s="30">
+      <c r="M16" s="28">
         <f t="shared" si="1"/>
         <v>66.6</v>
       </c>
@@ -2576,35 +2556,35 @@
       <c r="D17" s="14">
         <v>260</v>
       </c>
-      <c r="E17" s="21" t="s">
+      <c r="E17" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="23">
+      <c r="F17" s="21">
         <f>IF(B17&lt;&gt;"",B17*D17/500,"")</f>
         <v>6.5</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="21">
         <v>0.82</v>
       </c>
-      <c r="H17" s="23">
+      <c r="H17" s="21">
         <v>0.2</v>
       </c>
-      <c r="I17" s="29">
+      <c r="I17" s="27">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>7.52</v>
       </c>
-      <c r="J17" s="23">
+      <c r="J17" s="21">
         <v>20</v>
       </c>
-      <c r="K17" s="30">
+      <c r="K17" s="28">
         <f t="shared" si="0"/>
         <v>12.48</v>
       </c>
-      <c r="L17" s="30">
+      <c r="L17" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>165.957446808511</v>
       </c>
-      <c r="M17" s="30">
+      <c r="M17" s="28">
         <f t="shared" si="1"/>
         <v>62.4</v>
       </c>
@@ -2622,35 +2602,35 @@
       <c r="D18" s="14">
         <v>135</v>
       </c>
-      <c r="E18" s="21" t="s">
+      <c r="E18" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="F18" s="23">
+      <c r="F18" s="21">
         <f t="shared" ref="F18" si="2">IF(B18&lt;&gt;"",B18*D18/500,"")</f>
         <v>4.59</v>
       </c>
-      <c r="G18" s="23">
+      <c r="G18" s="21">
         <v>0.685</v>
       </c>
-      <c r="H18" s="23">
+      <c r="H18" s="21">
         <v>0.2</v>
       </c>
-      <c r="I18" s="29">
+      <c r="I18" s="27">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.475</v>
       </c>
-      <c r="J18" s="23">
+      <c r="J18" s="21">
         <v>15</v>
       </c>
-      <c r="K18" s="30">
+      <c r="K18" s="28">
         <f t="shared" ref="K18" si="3">J18-(F18+G18+H18)</f>
         <v>9.525</v>
       </c>
-      <c r="L18" s="30">
+      <c r="L18" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>173.972602739726</v>
       </c>
-      <c r="M18" s="30">
+      <c r="M18" s="28">
         <f t="shared" ref="M18" si="4">(J18-(F18+G18+H18))/J18*100</f>
         <v>63.5</v>
       </c>
@@ -2668,35 +2648,35 @@
       <c r="D19" s="14">
         <v>165</v>
       </c>
-      <c r="E19" s="21" t="s">
+      <c r="E19" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="21">
         <f t="shared" ref="F19:F35" si="5">IF(B19&lt;&gt;"",B19*D19/500,"")</f>
         <v>5.61</v>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="21">
         <v>0.685</v>
       </c>
-      <c r="H19" s="23">
+      <c r="H19" s="21">
         <v>0.2</v>
       </c>
-      <c r="I19" s="29">
+      <c r="I19" s="27">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>6.495</v>
       </c>
-      <c r="J19" s="23">
+      <c r="J19" s="21">
         <v>20</v>
       </c>
-      <c r="K19" s="30">
+      <c r="K19" s="28">
         <f t="shared" si="0"/>
         <v>13.505</v>
       </c>
-      <c r="L19" s="30">
+      <c r="L19" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>207.929176289453</v>
       </c>
-      <c r="M19" s="30">
+      <c r="M19" s="28">
         <f t="shared" si="1"/>
         <v>67.525</v>
       </c>
@@ -2714,35 +2694,35 @@
       <c r="D20" s="14">
         <v>260</v>
       </c>
-      <c r="E20" s="21" t="s">
+      <c r="E20" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="F20" s="23">
+      <c r="F20" s="21">
         <f t="shared" si="5"/>
         <v>8.84</v>
       </c>
-      <c r="G20" s="23">
+      <c r="G20" s="21">
         <v>0.82</v>
       </c>
-      <c r="H20" s="23">
+      <c r="H20" s="21">
         <v>0.2</v>
       </c>
-      <c r="I20" s="29">
+      <c r="I20" s="27">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>9.86</v>
       </c>
-      <c r="J20" s="23">
+      <c r="J20" s="21">
         <v>24</v>
       </c>
-      <c r="K20" s="30">
+      <c r="K20" s="28">
         <f t="shared" si="0"/>
         <v>14.14</v>
       </c>
-      <c r="L20" s="30">
+      <c r="L20" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>143.407707910751</v>
       </c>
-      <c r="M20" s="30">
+      <c r="M20" s="28">
         <f t="shared" si="1"/>
         <v>58.9166666666667</v>
       </c>
@@ -2760,35 +2740,35 @@
       <c r="D21" s="14">
         <v>100</v>
       </c>
-      <c r="E21" s="21" t="s">
+      <c r="E21" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="F21" s="23">
+      <c r="F21" s="21">
         <f t="shared" si="5"/>
         <v>4.5</v>
       </c>
-      <c r="G21" s="23">
+      <c r="G21" s="21">
         <v>0.685</v>
       </c>
-      <c r="H21" s="23">
+      <c r="H21" s="21">
         <v>0.2</v>
       </c>
-      <c r="I21" s="29">
+      <c r="I21" s="27">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.385</v>
       </c>
-      <c r="J21" s="23">
+      <c r="J21" s="21">
         <v>18</v>
       </c>
-      <c r="K21" s="30">
+      <c r="K21" s="28">
         <f t="shared" si="0"/>
         <v>12.615</v>
       </c>
-      <c r="L21" s="30">
+      <c r="L21" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>234.261838440111</v>
       </c>
-      <c r="M21" s="30">
+      <c r="M21" s="28">
         <f t="shared" si="1"/>
         <v>70.0833333333333</v>
       </c>
@@ -2806,17 +2786,17 @@
       <c r="D22" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="21" t="s">
+      <c r="E22" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="23"/>
-      <c r="K22" s="30"/>
-      <c r="L22" s="30"/>
-      <c r="M22" s="30"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="27"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="28"/>
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:13">
       <c r="A23" s="15" t="s">
@@ -2831,33 +2811,33 @@
       <c r="D23" s="14">
         <v>90</v>
       </c>
-      <c r="E23" s="21" t="s">
+      <c r="E23" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="21">
         <f t="shared" si="5"/>
         <v>3.42</v>
       </c>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23">
+      <c r="G23" s="21"/>
+      <c r="H23" s="21">
         <v>2.5</v>
       </c>
-      <c r="I23" s="29">
+      <c r="I23" s="27">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.92</v>
       </c>
-      <c r="J23" s="23">
+      <c r="J23" s="21">
         <v>16</v>
       </c>
-      <c r="K23" s="30">
+      <c r="K23" s="28">
         <f t="shared" si="0"/>
         <v>10.08</v>
       </c>
-      <c r="L23" s="30">
+      <c r="L23" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>170.27027027027</v>
       </c>
-      <c r="M23" s="30">
+      <c r="M23" s="28">
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
@@ -2875,33 +2855,33 @@
       <c r="D24" s="14">
         <v>70</v>
       </c>
-      <c r="E24" s="21" t="s">
+      <c r="E24" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="F24" s="23">
+      <c r="F24" s="21">
         <f t="shared" si="5"/>
         <v>2.66</v>
       </c>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23">
+      <c r="G24" s="21"/>
+      <c r="H24" s="21">
         <v>2.5</v>
       </c>
-      <c r="I24" s="29">
+      <c r="I24" s="27">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.16</v>
       </c>
-      <c r="J24" s="23">
+      <c r="J24" s="21">
         <v>16</v>
       </c>
-      <c r="K24" s="30">
+      <c r="K24" s="28">
         <f t="shared" si="0"/>
         <v>10.84</v>
       </c>
-      <c r="L24" s="30">
+      <c r="L24" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>210.077519379845</v>
       </c>
-      <c r="M24" s="30">
+      <c r="M24" s="28">
         <f t="shared" si="1"/>
         <v>67.75</v>
       </c>
@@ -2919,35 +2899,35 @@
       <c r="D25" s="14">
         <v>300</v>
       </c>
-      <c r="E25" s="21" t="s">
+      <c r="E25" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F25" s="23">
+      <c r="F25" s="21">
         <f t="shared" si="5"/>
         <v>5.454</v>
       </c>
-      <c r="G25" s="23">
+      <c r="G25" s="21">
         <v>0.82</v>
       </c>
-      <c r="H25" s="24">
+      <c r="H25" s="22">
         <v>0.5</v>
       </c>
-      <c r="I25" s="31">
+      <c r="I25" s="29">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>6.774</v>
       </c>
-      <c r="J25" s="23">
+      <c r="J25" s="21">
         <v>16</v>
       </c>
-      <c r="K25" s="30">
+      <c r="K25" s="28">
         <f t="shared" si="0"/>
         <v>9.226</v>
       </c>
-      <c r="L25" s="30">
+      <c r="L25" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>136.19722468261</v>
       </c>
-      <c r="M25" s="30">
+      <c r="M25" s="28">
         <f t="shared" si="1"/>
         <v>57.6625</v>
       </c>
@@ -2965,35 +2945,35 @@
       <c r="D26" s="14">
         <v>165</v>
       </c>
-      <c r="E26" s="21" t="s">
+      <c r="E26" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F26" s="23">
+      <c r="F26" s="21">
         <f t="shared" si="5"/>
         <v>2.9997</v>
       </c>
-      <c r="G26" s="23">
+      <c r="G26" s="21">
         <v>0.685</v>
       </c>
-      <c r="H26" s="24">
+      <c r="H26" s="22">
         <v>1.5</v>
       </c>
-      <c r="I26" s="31">
+      <c r="I26" s="29">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.1847</v>
       </c>
-      <c r="J26" s="23">
+      <c r="J26" s="21">
         <v>14</v>
       </c>
-      <c r="K26" s="30">
+      <c r="K26" s="28">
         <f t="shared" si="0"/>
         <v>8.8153</v>
       </c>
-      <c r="L26" s="30">
+      <c r="L26" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>170.025266649951</v>
       </c>
-      <c r="M26" s="30">
+      <c r="M26" s="28">
         <f t="shared" si="1"/>
         <v>62.9664285714286</v>
       </c>
@@ -3011,35 +2991,35 @@
       <c r="D27" s="14">
         <v>260</v>
       </c>
-      <c r="E27" s="21" t="s">
+      <c r="E27" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F27" s="23">
+      <c r="F27" s="21">
         <f t="shared" si="5"/>
         <v>4.7268</v>
       </c>
-      <c r="G27" s="23">
+      <c r="G27" s="21">
         <v>0.82</v>
       </c>
-      <c r="H27" s="24">
+      <c r="H27" s="22">
         <v>1.5</v>
       </c>
-      <c r="I27" s="31">
+      <c r="I27" s="29">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>7.0468</v>
       </c>
-      <c r="J27" s="23">
+      <c r="J27" s="21">
         <v>18</v>
       </c>
-      <c r="K27" s="30">
+      <c r="K27" s="28">
         <f t="shared" si="0"/>
         <v>10.9532</v>
       </c>
-      <c r="L27" s="30">
+      <c r="L27" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>155.435091105182</v>
       </c>
-      <c r="M27" s="30">
+      <c r="M27" s="28">
         <f t="shared" si="1"/>
         <v>60.8511111111111</v>
       </c>
@@ -3058,28 +3038,28 @@
         <v>35</v>
       </c>
       <c r="E28" s="14"/>
-      <c r="F28" s="23">
+      <c r="F28" s="21">
         <f t="shared" si="5"/>
         <v>0.8225</v>
       </c>
-      <c r="G28" s="23" t="s">
+      <c r="G28" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="H28" s="24" t="s">
+      <c r="H28" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="I28" s="31">
+      <c r="I28" s="29">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>0.8225</v>
       </c>
-      <c r="J28" s="23" t="s">
+      <c r="J28" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="K28" s="30" t="s">
+      <c r="K28" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="L28" s="30"/>
-      <c r="M28" s="30" t="s">
+      <c r="L28" s="28"/>
+      <c r="M28" s="28" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3096,35 +3076,35 @@
       <c r="D29" s="14">
         <v>165</v>
       </c>
-      <c r="E29" s="21" t="s">
+      <c r="E29" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="F29" s="23">
+      <c r="F29" s="21">
         <f t="shared" si="5"/>
         <v>2.64</v>
       </c>
-      <c r="G29" s="23">
+      <c r="G29" s="21">
         <v>0.685</v>
       </c>
-      <c r="H29" s="24">
+      <c r="H29" s="22">
         <v>1.2</v>
       </c>
-      <c r="I29" s="31">
+      <c r="I29" s="29">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>4.525</v>
       </c>
-      <c r="J29" s="23">
+      <c r="J29" s="21">
         <v>14</v>
       </c>
-      <c r="K29" s="30">
+      <c r="K29" s="28">
         <f t="shared" si="0"/>
         <v>9.475</v>
       </c>
-      <c r="L29" s="30">
+      <c r="L29" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>209.39226519337</v>
       </c>
-      <c r="M29" s="30">
+      <c r="M29" s="28">
         <f t="shared" si="1"/>
         <v>67.6785714285714</v>
       </c>
@@ -3142,41 +3122,41 @@
       <c r="D30" s="14">
         <v>260</v>
       </c>
-      <c r="E30" s="21" t="s">
+      <c r="E30" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="F30" s="23">
+      <c r="F30" s="21">
         <f t="shared" si="5"/>
         <v>4.16</v>
       </c>
-      <c r="G30" s="23">
+      <c r="G30" s="21">
         <v>0.82</v>
       </c>
-      <c r="H30" s="24">
+      <c r="H30" s="22">
         <v>1.2</v>
       </c>
-      <c r="I30" s="31">
+      <c r="I30" s="29">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>6.18</v>
       </c>
-      <c r="J30" s="23">
+      <c r="J30" s="21">
         <v>18</v>
       </c>
-      <c r="K30" s="30">
+      <c r="K30" s="28">
         <f t="shared" si="0"/>
         <v>11.82</v>
       </c>
-      <c r="L30" s="30">
+      <c r="L30" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>191.26213592233</v>
       </c>
-      <c r="M30" s="30">
+      <c r="M30" s="28">
         <f t="shared" si="1"/>
         <v>65.6666666666667</v>
       </c>
     </row>
     <row r="31" ht="18.75" customHeight="1" spans="1:13">
-      <c r="A31" s="16" t="s">
+      <c r="A31" s="12" t="s">
         <v>59</v>
       </c>
       <c r="B31" s="13">
@@ -3185,38 +3165,38 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="17">
+      <c r="D31" s="16">
         <v>140</v>
       </c>
-      <c r="E31" s="21" t="s">
+      <c r="E31" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="F31" s="23">
+      <c r="F31" s="21">
         <f t="shared" si="5"/>
         <v>0.805</v>
       </c>
-      <c r="G31" s="23">
+      <c r="G31" s="21">
         <v>0.82</v>
       </c>
-      <c r="H31" s="23">
+      <c r="H31" s="21">
         <v>4.1</v>
       </c>
-      <c r="I31" s="29">
+      <c r="I31" s="27">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.725</v>
       </c>
-      <c r="J31" s="23">
+      <c r="J31" s="21">
         <v>16</v>
       </c>
-      <c r="K31" s="30">
+      <c r="K31" s="28">
         <f t="shared" si="0"/>
         <v>10.275</v>
       </c>
-      <c r="L31" s="30">
+      <c r="L31" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>179.475982532751</v>
       </c>
-      <c r="M31" s="30">
+      <c r="M31" s="28">
         <f t="shared" si="1"/>
         <v>64.21875</v>
       </c>
@@ -3230,34 +3210,34 @@
         <v>0.5</v>
       </c>
       <c r="D32" s="14"/>
-      <c r="E32" s="21" t="s">
+      <c r="E32" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="F32" s="23">
+      <c r="F32" s="21">
         <v>3.88</v>
       </c>
-      <c r="G32" s="23">
+      <c r="G32" s="21">
         <v>0.685</v>
       </c>
-      <c r="H32" s="23">
+      <c r="H32" s="21">
         <v>0.2</v>
       </c>
-      <c r="I32" s="29">
+      <c r="I32" s="27">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>4.765</v>
       </c>
-      <c r="J32" s="23">
+      <c r="J32" s="21">
         <v>14</v>
       </c>
-      <c r="K32" s="30">
+      <c r="K32" s="28">
         <f t="shared" si="0"/>
         <v>9.235</v>
       </c>
-      <c r="L32" s="30">
+      <c r="L32" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>193.809024134313</v>
       </c>
-      <c r="M32" s="30">
+      <c r="M32" s="28">
         <f t="shared" si="1"/>
         <v>65.9642857142857</v>
       </c>
@@ -3271,34 +3251,34 @@
         <v>0.5</v>
       </c>
       <c r="D33" s="14"/>
-      <c r="E33" s="21" t="s">
+      <c r="E33" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="F33" s="23">
+      <c r="F33" s="21">
         <v>5.28</v>
       </c>
-      <c r="G33" s="23">
+      <c r="G33" s="21">
         <v>0.685</v>
       </c>
-      <c r="H33" s="23">
+      <c r="H33" s="21">
         <v>0.2</v>
       </c>
-      <c r="I33" s="29">
+      <c r="I33" s="27">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>6.165</v>
       </c>
-      <c r="J33" s="23">
+      <c r="J33" s="21">
         <v>15</v>
       </c>
-      <c r="K33" s="30">
+      <c r="K33" s="28">
         <f t="shared" si="0"/>
         <v>8.835</v>
       </c>
-      <c r="L33" s="30">
+      <c r="L33" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>143.30900243309</v>
       </c>
-      <c r="M33" s="30">
+      <c r="M33" s="28">
         <f t="shared" si="1"/>
         <v>58.9</v>
       </c>
@@ -3314,43 +3294,43 @@
       <c r="D34" s="14">
         <v>370</v>
       </c>
-      <c r="E34" s="21" t="s">
+      <c r="E34" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="F34" s="23">
+      <c r="F34" s="21">
         <v>6.64</v>
       </c>
-      <c r="G34" s="23">
+      <c r="G34" s="21">
         <v>0.82</v>
       </c>
-      <c r="H34" s="23">
+      <c r="H34" s="21">
         <v>0.2</v>
       </c>
-      <c r="I34" s="29">
+      <c r="I34" s="27">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>7.66</v>
       </c>
-      <c r="J34" s="23">
+      <c r="J34" s="21">
         <v>24</v>
       </c>
-      <c r="K34" s="30">
+      <c r="K34" s="28">
         <f t="shared" si="0"/>
         <v>16.34</v>
       </c>
-      <c r="L34" s="30">
+      <c r="L34" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>213.31592689295</v>
       </c>
-      <c r="M34" s="30">
+      <c r="M34" s="28">
         <f t="shared" si="1"/>
         <v>68.0833333333333</v>
       </c>
     </row>
     <row r="35" ht="18.75" customHeight="1" spans="1:13">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="B35" s="18">
+      <c r="B35" s="17">
         <v>4.5</v>
       </c>
       <c r="C35" s="13">
@@ -3359,41 +3339,41 @@
       <c r="D35" s="14">
         <v>200</v>
       </c>
-      <c r="E35" s="21" t="s">
+      <c r="E35" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="F35" s="23">
+      <c r="F35" s="21">
         <f t="shared" si="5"/>
         <v>1.8</v>
       </c>
-      <c r="G35" s="23">
+      <c r="G35" s="21">
         <v>0.82</v>
       </c>
-      <c r="H35" s="23">
+      <c r="H35" s="21">
         <v>4</v>
       </c>
-      <c r="I35" s="29">
+      <c r="I35" s="27">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>6.62</v>
       </c>
-      <c r="J35" s="23">
+      <c r="J35" s="21">
         <v>16</v>
       </c>
-      <c r="K35" s="30">
+      <c r="K35" s="28">
         <f t="shared" si="0"/>
         <v>9.38</v>
       </c>
-      <c r="L35" s="30">
+      <c r="L35" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>141.691842900302</v>
       </c>
-      <c r="M35" s="30">
+      <c r="M35" s="28">
         <f t="shared" si="1"/>
         <v>58.625</v>
       </c>
     </row>
     <row r="36" ht="18.75" customHeight="1" spans="1:13">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="12" t="s">
         <v>69</v>
       </c>
       <c r="B36" s="13"/>
@@ -3403,34 +3383,34 @@
       <c r="D36" s="14">
         <v>185</v>
       </c>
-      <c r="E36" s="21" t="s">
+      <c r="E36" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="F36" s="23">
+      <c r="F36" s="21">
         <v>2.5</v>
       </c>
-      <c r="G36" s="23">
+      <c r="G36" s="21">
         <v>0.685</v>
       </c>
-      <c r="H36" s="23">
+      <c r="H36" s="21">
         <v>1.4</v>
       </c>
-      <c r="I36" s="29">
+      <c r="I36" s="27">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>4.585</v>
       </c>
-      <c r="J36" s="23">
+      <c r="J36" s="21">
         <v>15</v>
       </c>
-      <c r="K36" s="30">
+      <c r="K36" s="28">
         <f t="shared" si="0"/>
         <v>10.415</v>
       </c>
-      <c r="L36" s="30">
+      <c r="L36" s="28">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>227.153762268266</v>
       </c>
-      <c r="M36" s="30">
+      <c r="M36" s="28">
         <f t="shared" si="1"/>
         <v>69.4333333333333</v>
       </c>
@@ -3448,7 +3428,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{419032ec-fb80-43c0-9c6b-7e01a062ea6d}</x14:id>
+          <x14:id>{375805dd-d7fb-4574-bbcf-97c86080575e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3463,7 +3443,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{419032ec-fb80-43c0-9c6b-7e01a062ea6d}">
+          <x14:cfRule type="dataBar" id="{375805dd-d7fb-4574-bbcf-97c86080575e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -3488,7 +3468,9 @@
   <sheetFormatPr defaultColWidth="20.6923076923077" defaultRowHeight="20" customHeight="1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="31.8942307692308" customWidth="1"/>
-    <col min="2" max="16383" width="20.6923076923077" customWidth="1"/>
+    <col min="2" max="3" width="20.6923076923077" customWidth="1"/>
+    <col min="4" max="4" width="28.3173076923077" customWidth="1"/>
+    <col min="5" max="16383" width="20.6923076923077" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:4">

--- a/财务与流水/馋唻买-听涛路店商品表.xlsx
+++ b/财务与流水/馋唻买-听涛路店商品表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15860" activeTab="1"/>
+    <workbookView windowHeight="15820" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="堂食利润" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="118">
   <si>
     <t>SKU</t>
   </si>
@@ -366,6 +366,9 @@
   </si>
   <si>
     <t>1根</t>
+  </si>
+  <si>
+    <t>4元</t>
   </si>
 </sst>
 </file>
@@ -373,13 +376,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
-    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="0.000_);\(0.000\)"/>
+    <numFmt numFmtId="176" formatCode="0.000_);\(0.000\)"/>
+    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="30">
     <font>
@@ -457,7 +460,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -471,23 +474,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -495,53 +506,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -557,20 +521,28 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
@@ -585,6 +557,37 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
@@ -592,9 +595,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -651,13 +654,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -669,67 +702,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -747,7 +726,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -759,13 +750,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -777,7 +792,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -795,43 +816,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -944,46 +947,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1003,11 +967,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1029,6 +999,39 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -1040,148 +1043,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1214,7 +1217,7 @@
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1253,31 +1256,31 @@
     <xf numFmtId="4" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="177" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="4" fontId="5" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="10" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="10" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1529,7 +1532,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="3" tint="0.799920651875362"/>
@@ -3547,7 +3550,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2a9fc2a7-303c-467d-af27-5f80d6238363}</x14:id>
+          <x14:id>{cdee42ab-e25b-4484-9437-4e8766d2857d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3562,7 +3565,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2a9fc2a7-303c-467d-af27-5f80d6238363}">
+          <x14:cfRule type="dataBar" id="{cdee42ab-e25b-4484-9437-4e8766d2857d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -3993,7 +3996,7 @@
         <v>116</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>108</v>

--- a/财务与流水/馋唻买-听涛路店商品表.xlsx
+++ b/财务与流水/馋唻买-听涛路店商品表.xlsx
@@ -299,13 +299,13 @@
     <t>约300克</t>
   </si>
   <si>
-    <t>豪华多拼</t>
+    <t>自由搭配</t>
   </si>
   <si>
     <t>豪华三拼(经典+牛肉羹+肉燕)</t>
   </si>
   <si>
-    <t>特色素面</t>
+    <t>手工素面</t>
   </si>
   <si>
     <t>约180克</t>
@@ -317,13 +317,13 @@
     <t>特色口味</t>
   </si>
   <si>
-    <t>特色素面+瘦肉丸</t>
+    <t>手工素面+瘦肉丸</t>
   </si>
   <si>
     <t>月240克</t>
   </si>
   <si>
-    <t>火鸡面拌瘦肉丸</t>
+    <t>火鸡面拌瘦肉丸(辣)</t>
   </si>
   <si>
     <t>13元</t>
@@ -3550,7 +3550,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cdee42ab-e25b-4484-9437-4e8766d2857d}</x14:id>
+          <x14:id>{a0682db1-efc2-4096-96bd-2da5e228320c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3565,7 +3565,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cdee42ab-e25b-4484-9437-4e8766d2857d}">
+          <x14:cfRule type="dataBar" id="{a0682db1-efc2-4096-96bd-2da5e228320c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -3589,7 +3589,8 @@
   <dimension ref="A1:D31"/>
   <sheetFormatPr defaultColWidth="30.6923076923077" defaultRowHeight="20" customHeight="1" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="16384" width="30.6923076923077" customWidth="1"/>
+    <col min="1" max="1" width="36.2211538461538" customWidth="1"/>
+    <col min="2" max="16384" width="30.6923076923077" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:4">

--- a/财务与流水/馋唻买-听涛路店商品表.xlsx
+++ b/财务与流水/馋唻买-听涛路店商品表.xlsx
@@ -3550,7 +3550,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a0682db1-efc2-4096-96bd-2da5e228320c}</x14:id>
+          <x14:id>{a1444e99-d32f-4757-91fa-0e5fa5b7213d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3565,7 +3565,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a0682db1-efc2-4096-96bd-2da5e228320c}">
+          <x14:cfRule type="dataBar" id="{a1444e99-d32f-4757-91fa-0e5fa5b7213d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/财务与流水/馋唻买-听涛路店商品表.xlsx
+++ b/财务与流水/馋唻买-听涛路店商品表.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="120">
   <si>
     <t>SKU</t>
   </si>
@@ -293,7 +293,7 @@
     <t>金汤酸菜瘦肉丸</t>
   </si>
   <si>
-    <t>自由双拼(经典/牛肉羹/肉燕)</t>
+    <t>随心双拼(经典/牛肉羹/肉燕)</t>
   </si>
   <si>
     <t>约300克</t>
@@ -311,7 +311,7 @@
     <t>约180克</t>
   </si>
   <si>
-    <t>7元</t>
+    <t>8元</t>
   </si>
   <si>
     <t>特色口味</t>
@@ -335,6 +335,9 @@
     <t>金汤酸菜弹粉+瘦肉丸</t>
   </si>
   <si>
+    <t>沙县蒸饺(10只)</t>
+  </si>
+  <si>
     <t>10只</t>
   </si>
   <si>
@@ -344,19 +347,22 @@
     <t>特色小吃</t>
   </si>
   <si>
-    <t>福州鱼丸</t>
+    <t>拇指小笼包(10只)</t>
+  </si>
+  <si>
+    <t>福州鱼丸(8颗)</t>
   </si>
   <si>
     <t>8颗</t>
   </si>
   <si>
-    <t>8元</t>
-  </si>
-  <si>
-    <t>纸皮烧卖</t>
-  </si>
-  <si>
-    <t>3个(蛋黄/肉松)</t>
+    <t>潮汕牛肉丸(8颗)</t>
+  </si>
+  <si>
+    <t>纸皮烧卖(3只)</t>
+  </si>
+  <si>
+    <t>3只(蛋黄/肉松)</t>
   </si>
   <si>
     <t>1个</t>
@@ -3550,7 +3556,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a1444e99-d32f-4757-91fa-0e5fa5b7213d}</x14:id>
+          <x14:id>{dc02932e-9f36-474d-85db-39fee7c6df24}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3565,7 +3571,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a1444e99-d32f-4757-91fa-0e5fa5b7213d}">
+          <x14:cfRule type="dataBar" id="{dc02932e-9f36-474d-85db-39fee7c6df24}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -3809,7 +3815,7 @@
         <v>101</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>99</v>
@@ -3893,72 +3899,72 @@
     </row>
     <row r="24" customHeight="1" spans="1:4">
       <c r="A24" s="7" t="s">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:4">
       <c r="A25" s="5" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:4">
       <c r="A26" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>109</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:4">
       <c r="A27" s="5" t="s">
-        <v>28</v>
+        <v>113</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:4">
       <c r="A28" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:4">
@@ -3966,13 +3972,13 @@
         <v>22</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:4">
@@ -3980,13 +3986,13 @@
         <v>19</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:4">
@@ -3994,13 +4000,13 @@
         <v>17</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/财务与流水/馋唻买-听涛路店商品表.xlsx
+++ b/财务与流水/馋唻买-听涛路店商品表.xlsx
@@ -305,7 +305,7 @@
     <t>豪华三拼(经典+牛肉羹+肉燕)</t>
   </si>
   <si>
-    <t>手工素面</t>
+    <t>手工挂面</t>
   </si>
   <si>
     <t>约180克</t>
@@ -317,7 +317,7 @@
     <t>特色口味</t>
   </si>
   <si>
-    <t>手工素面+瘦肉丸</t>
+    <t>手工挂面+瘦肉丸</t>
   </si>
   <si>
     <t>月240克</t>
@@ -384,11 +384,11 @@
   <numFmts count="7">
     <numFmt numFmtId="176" formatCode="0.000_);\(0.000\)"/>
     <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
   <fonts count="30">
     <font>
@@ -466,7 +466,22 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -480,10 +495,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -495,8 +527,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -511,15 +552,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -533,17 +580,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -556,54 +601,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -660,31 +660,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -696,37 +678,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -744,7 +702,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -756,7 +732,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -768,13 +798,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -786,61 +834,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -949,30 +949,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -988,17 +964,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1027,6 +997,36 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -1049,148 +1049,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3556,7 +3556,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dc02932e-9f36-474d-85db-39fee7c6df24}</x14:id>
+          <x14:id>{62f3e13b-edf7-459e-b452-b43e4eff0520}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3571,7 +3571,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dc02932e-9f36-474d-85db-39fee7c6df24}">
+          <x14:cfRule type="dataBar" id="{62f3e13b-edf7-459e-b452-b43e4eff0520}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/财务与流水/馋唻买-听涛路店商品表.xlsx
+++ b/财务与流水/馋唻买-听涛路店商品表.xlsx
@@ -275,7 +275,7 @@
     <t>20元</t>
   </si>
   <si>
-    <t>福鼎肉燕</t>
+    <t>福鼎手工肉燕</t>
   </si>
   <si>
     <t>大份(180克)</t>
@@ -383,12 +383,12 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
     <numFmt numFmtId="176" formatCode="0.000_);\(0.000\)"/>
-    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="30">
     <font>
@@ -466,22 +466,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -503,9 +488,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -521,7 +512,30 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -545,6 +559,29 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -552,7 +589,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -567,43 +604,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -660,7 +660,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -672,7 +750,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -684,7 +768,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -696,55 +792,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -756,79 +822,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -840,7 +840,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -949,17 +949,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -983,6 +977,36 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -993,6 +1017,17 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1011,186 +1046,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1211,70 +1211,70 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="177" fontId="4" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="178" fontId="4" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="4" fontId="9" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="5" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1360,7 +1360,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="0" tint="-0.149937437055574"/>
@@ -1385,7 +1385,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="0" tint="-0.149937437055574"/>
@@ -1538,7 +1538,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+      <numFmt numFmtId="178" formatCode="#,##0.00_ "/>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="3" tint="0.799920651875362"/>
@@ -3556,7 +3556,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{62f3e13b-edf7-459e-b452-b43e4eff0520}</x14:id>
+          <x14:id>{5396a1cd-92a2-440a-9026-16e0b90631db}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3571,7 +3571,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{62f3e13b-edf7-459e-b452-b43e4eff0520}">
+          <x14:cfRule type="dataBar" id="{5396a1cd-92a2-440a-9026-16e0b90631db}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/财务与流水/馋唻买-听涛路店商品表.xlsx
+++ b/财务与流水/馋唻买-听涛路店商品表.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="121">
   <si>
     <t>SKU</t>
   </si>
@@ -323,10 +323,13 @@
     <t>月240克</t>
   </si>
   <si>
-    <t>火鸡面拌瘦肉丸(辣)</t>
+    <t>火鸡面干拌瘦肉丸(辣)</t>
   </si>
   <si>
     <t>13元</t>
+  </si>
+  <si>
+    <t>燕面干拌瘦肉丸</t>
   </si>
   <si>
     <t>金汤酸菜泡面+瘦肉丸</t>
@@ -3556,7 +3559,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5396a1cd-92a2-440a-9026-16e0b90631db}</x14:id>
+          <x14:id>{af0a25a9-cce8-45bd-9b18-cd879bcdfcbd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3571,7 +3574,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5396a1cd-92a2-440a-9026-16e0b90631db}">
+          <x14:cfRule type="dataBar" id="{af0a25a9-cce8-45bd-9b18-cd879bcdfcbd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -3837,7 +3840,7 @@
     </row>
     <row r="19" customHeight="1" spans="1:4">
       <c r="A19" s="5" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>90</v>
@@ -3865,7 +3868,7 @@
     </row>
     <row r="21" customHeight="1" spans="1:4">
       <c r="A21" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>90</v>
@@ -3879,7 +3882,7 @@
     </row>
     <row r="22" customHeight="1" spans="1:4">
       <c r="A22" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>90</v>
@@ -3899,72 +3902,72 @@
     </row>
     <row r="24" customHeight="1" spans="1:4">
       <c r="A24" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:4">
       <c r="A25" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D25" s="6" t="s">
         <v>110</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:4">
       <c r="A26" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>98</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:4">
       <c r="A27" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>112</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:4">
       <c r="A28" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>98</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:4">
@@ -3972,13 +3975,13 @@
         <v>22</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:4">
@@ -3986,13 +3989,13 @@
         <v>19</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:4">
@@ -4000,13 +4003,13 @@
         <v>17</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/财务与流水/馋唻买-听涛路店商品表.xlsx
+++ b/财务与流水/馋唻买-听涛路店商品表.xlsx
@@ -1,16 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github localpath\ChanWeiMai\财务与流水\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC175AB-8153-494D-A11F-9837BFB48805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="15820" activeTab="1"/>
+    <workbookView xWindow="8745" yWindow="1320" windowWidth="35070" windowHeight="19335" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="堂食利润" sheetId="1" r:id="rId1"/>
     <sheet name="菜单" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -296,9 +302,6 @@
     <t>随心双拼(经典/牛肉羹/肉燕)</t>
   </si>
   <si>
-    <t>约300克</t>
-  </si>
-  <si>
     <t>自由搭配</t>
   </si>
   <si>
@@ -378,22 +381,22 @@
   </si>
   <si>
     <t>4元</t>
+  </si>
+  <si>
+    <t>约370克</t>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0.000_);\(0.000\)"/>
     <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -435,7 +438,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -446,7 +449,7 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -459,34 +462,18 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -494,125 +481,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="40">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -627,14 +501,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor theme="4" tint="0.59999389629810485"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.79995117038483843"/>
+        <bgColor theme="4" tint="0.79995117038483843"/>
       </patternFill>
     </fill>
     <fill>
@@ -645,13 +519,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.149937437055574"/>
+        <fgColor theme="0" tint="-0.14990691854609822"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.799920651875362"/>
+        <fgColor theme="3" tint="0.79989013336588644"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -661,194 +535,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="16">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -951,263 +639,21 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1292,269 +738,13 @@
     <xf numFmtId="176" fontId="10" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
-    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
-    <cellStyle name="输入" xfId="4" builtinId="20"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
-    <cellStyle name="货币" xfId="7" builtinId="4"/>
-    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
-    <cellStyle name="百分比" xfId="9" builtinId="5"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
-    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
-    <cellStyle name="计算" xfId="15" builtinId="22"/>
-    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
-    <cellStyle name="适中" xfId="17" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
-    <cellStyle name="好" xfId="19" builtinId="26"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="差" xfId="22" builtinId="27"/>
-    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
-    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
-    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
-    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
-    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
-    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
-    <cellStyle name="标题" xfId="33" builtinId="15"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
-    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="注释" xfId="37" builtinId="10"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
-    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
-    <cellStyle name="超链接" xfId="41" builtinId="8"/>
-    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
-    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
-    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
   </cellStyles>
   <dxfs count="13">
-    <dxf>
-      <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="1"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="center" vertical="center"/>
-      <border>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-0.149937437055574"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center"/>
-      <border>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-0.149937437055574"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-0.149937437055574"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-0.149937437055574"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="3" tint="0.799920651875362"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="3" tint="0.799920651875362"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="3" tint="0.799920651875362"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="1"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="3" tint="0.799920651875362"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="178" formatCode="#,##0.00_ "/>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="3" tint="0.799920651875362"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center"/>
-      <border>
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-      </border>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1566,22 +756,19 @@
         <left style="thin">
           <color rgb="FF000000"/>
         </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
       </border>
     </dxf>
     <dxf>
       <font>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-        <family val="2"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
       <fill>
@@ -1616,6 +803,219 @@
         <left style="thin">
           <color rgb="FF000000"/>
         </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="178" formatCode="#,##0.00_ "/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="3" tint="0.79989013336588644"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center"/>
+      <border>
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="3" tint="0.79989013336588644"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="3" tint="0.79989013336588644"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center"/>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="3" tint="0.79989013336588644"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center"/>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="3" tint="0.79989013336588644"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center"/>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0" tint="-0.14990691854609822"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0" tint="-0.14990691854609822"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center"/>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0" tint="-0.14990691854609822"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0" tint="-0.14990691854609822"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center"/>
+      <border>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+      <border>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
       </border>
     </dxf>
   </dxfs>
@@ -1624,27 +1024,38 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SKUTable" displayName="SKUTable" ref="A1:M36" totalsRowShown="0">
-  <autoFilter ref="A1:M36"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SKUTable" displayName="SKUTable" ref="A1:M36" totalsRowShown="0">
+  <autoFilter ref="A1:M36" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="13">
-    <tableColumn id="1" name="SKU" dataDxfId="0"/>
-    <tableColumn id="2" name="进货价格(元/500g)" dataDxfId="1"/>
-    <tableColumn id="11" name="运费(元/500g)" dataDxfId="2"/>
-    <tableColumn id="3" name="每份制作重量(g)" dataDxfId="3"/>
-    <tableColumn id="10" name="成份说明" dataDxfId="4"/>
-    <tableColumn id="4" name="食材成本(元/份)" dataDxfId="5"/>
-    <tableColumn id="5" name="打包成本(元/份)" dataDxfId="6"/>
-    <tableColumn id="6" name="调味成本(元/份)" dataDxfId="7"/>
-    <tableColumn id="12" name="总成本(元/份)" dataDxfId="8"/>
-    <tableColumn id="7" name="堂食价(元/份)" dataDxfId="9"/>
-    <tableColumn id="8" name="毛利(元/份)" dataDxfId="10"/>
-    <tableColumn id="13" name="利润率(%)" dataDxfId="11"/>
-    <tableColumn id="9" name="毛利率(%)" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="SKU" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="进货价格(元/500g)" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="运费(元/500g)" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="每份制作重量(g)" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="成份说明" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="食材成本(元/份)" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="打包成本(元/份)" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="调味成本(元/份)" dataDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="总成本(元/份)" dataDxfId="4">
+      <calculatedColumnFormula>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="堂食价(元/份)" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="毛利(元/份)" dataDxfId="2">
+      <calculatedColumnFormula>J2-(F2+G2+H2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="利润率(%)" dataDxfId="1">
+      <calculatedColumnFormula>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="毛利率(%)" dataDxfId="0">
+      <calculatedColumnFormula>(J2-(F2+G2+H2))/J2*100</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1929,16 +1340,17 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:M40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="30.5" style="11" customWidth="1"/>
     <col min="2" max="2" width="14" style="12" customWidth="1"/>
@@ -1955,7 +1367,7 @@
     <col min="13" max="13" width="14.75" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="10" customFormat="1" ht="29.25" customHeight="1" spans="1:13">
+    <row r="1" spans="1:13" s="10" customFormat="1" ht="29.25" customHeight="1">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1996,7 +1408,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="20.25" customHeight="1" spans="1:13">
+    <row r="2" spans="1:13" ht="20.25" customHeight="1">
       <c r="A2" s="20" t="s">
         <v>13</v>
       </c>
@@ -2031,18 +1443,18 @@
       </c>
       <c r="K2" s="34">
         <f>J2-(F2+G2+H2)</f>
-        <v>4.89</v>
+        <v>4.8900000000000006</v>
       </c>
       <c r="L2" s="34">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>157.234726688103</v>
+        <v>157.23472668810291</v>
       </c>
       <c r="M2" s="34">
         <f>(J2-(F2+G2+H2))/J2*100</f>
-        <v>61.125</v>
-      </c>
-    </row>
-    <row r="3" ht="20.25" customHeight="1" spans="1:13">
+        <v>61.125000000000007</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="20.25" customHeight="1">
       <c r="A3" s="20" t="s">
         <v>15</v>
       </c>
@@ -2055,7 +1467,7 @@
         <v>16</v>
       </c>
       <c r="F3" s="28">
-        <v>2.45</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="G3" s="28">
         <v>0.2</v>
@@ -2065,30 +1477,30 @@
       </c>
       <c r="I3" s="32">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>2.8</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="J3" s="33">
         <v>8</v>
       </c>
       <c r="K3" s="34">
         <f>J3-(F3+G3+H3)</f>
-        <v>5.2</v>
+        <v>5.1999999999999993</v>
       </c>
       <c r="L3" s="34">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>185.714285714286</v>
+        <v>185.71428571428567</v>
       </c>
       <c r="M3" s="34">
         <f>(J3-(F3+G3+H3))/J3*100</f>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" ht="20.25" customHeight="1" spans="1:13">
+        <v>64.999999999999986</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="20.25" customHeight="1">
       <c r="A4" s="20" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="21">
-        <v>8.8</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="C4" s="21">
         <v>0</v>
@@ -2122,14 +1534,14 @@
       </c>
       <c r="L4" s="34">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>212.01248049922</v>
+        <v>212.01248049921998</v>
       </c>
       <c r="M4" s="34">
         <f t="shared" ref="M4:M36" si="1">(J4-(F4+G4+H4))/J4*100</f>
         <v>67.95</v>
       </c>
     </row>
-    <row r="5" ht="20.25" customHeight="1" spans="1:13">
+    <row r="5" spans="1:13" ht="20.25" customHeight="1">
       <c r="A5" s="20" t="s">
         <v>19</v>
       </c>
@@ -2156,7 +1568,7 @@
       </c>
       <c r="I5" s="32">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>2.05</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="J5" s="33">
         <v>5</v>
@@ -2167,14 +1579,14 @@
       </c>
       <c r="L5" s="34">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>143.90243902439</v>
+        <v>143.90243902439025</v>
       </c>
       <c r="M5" s="34">
         <f t="shared" si="1"/>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" ht="20.25" customHeight="1" spans="1:13">
+        <v>59.000000000000007</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="20.25" customHeight="1">
       <c r="A6" s="20" t="s">
         <v>22</v>
       </c>
@@ -2201,25 +1613,25 @@
       </c>
       <c r="I6" s="32">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>2.85</v>
+        <v>2.8499999999999996</v>
       </c>
       <c r="J6" s="33">
         <v>6</v>
       </c>
       <c r="K6" s="34">
         <f t="shared" si="0"/>
-        <v>3.15</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="L6" s="34">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>110.526315789474</v>
+        <v>110.52631578947371</v>
       </c>
       <c r="M6" s="34">
         <f t="shared" si="1"/>
         <v>52.5</v>
       </c>
     </row>
-    <row r="7" ht="20.25" customHeight="1" spans="1:13">
+    <row r="7" spans="1:13" ht="20.25" customHeight="1">
       <c r="A7" s="23" t="s">
         <v>24</v>
       </c>
@@ -2246,25 +1658,25 @@
       </c>
       <c r="I7" s="35">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>3.44</v>
+        <v>3.4400000000000004</v>
       </c>
       <c r="J7" s="29">
         <v>8</v>
       </c>
       <c r="K7" s="36">
         <f t="shared" si="0"/>
-        <v>4.56</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="L7" s="36">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>132.558139534884</v>
+        <v>132.55813953488368</v>
       </c>
       <c r="M7" s="36">
         <f t="shared" si="1"/>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" ht="20.25" customHeight="1" spans="1:13">
+        <v>56.999999999999993</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="20.25" customHeight="1">
       <c r="A8" s="23" t="s">
         <v>26</v>
       </c>
@@ -2309,7 +1721,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" ht="20.25" customHeight="1" spans="1:13">
+    <row r="9" spans="1:13" ht="20.25" customHeight="1">
       <c r="A9" s="20" t="s">
         <v>28</v>
       </c>
@@ -2347,14 +1759,14 @@
       </c>
       <c r="L9" s="36">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>177.777777777778</v>
+        <v>177.7777777777778</v>
       </c>
       <c r="M9" s="36">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
     </row>
-    <row r="10" ht="20.25" customHeight="1" spans="1:13">
+    <row r="10" spans="1:13" ht="20.25" customHeight="1">
       <c r="A10" s="20" t="s">
         <v>30</v>
       </c>
@@ -2388,18 +1800,18 @@
       </c>
       <c r="K10" s="36">
         <f t="shared" si="0"/>
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="L10" s="36">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>82.4817518248175</v>
+        <v>82.481751824817508</v>
       </c>
       <c r="M10" s="36">
         <f t="shared" si="1"/>
-        <v>45.2</v>
-      </c>
-    </row>
-    <row r="11" ht="20.25" customHeight="1" spans="1:13">
+        <v>45.199999999999996</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="20.25" customHeight="1">
       <c r="A11" s="20" t="s">
         <v>31</v>
       </c>
@@ -2433,18 +1845,18 @@
       </c>
       <c r="K11" s="36">
         <f t="shared" si="0"/>
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="L11" s="36">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>82.4817518248175</v>
+        <v>82.481751824817508</v>
       </c>
       <c r="M11" s="36">
         <f t="shared" si="1"/>
-        <v>45.2</v>
-      </c>
-    </row>
-    <row r="12" ht="20.25" customHeight="1" spans="1:13">
+        <v>45.199999999999996</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="20.25" customHeight="1">
       <c r="A12" s="20" t="s">
         <v>32</v>
       </c>
@@ -2462,35 +1874,35 @@
       </c>
       <c r="F12" s="29">
         <f>(B12+SKUTable[[#This Row],[运费(元/500g)]])*D12/500</f>
-        <v>2.805</v>
+        <v>2.8050000000000002</v>
       </c>
       <c r="G12" s="29">
-        <v>0.685</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="H12" s="29">
         <v>0.2</v>
       </c>
       <c r="I12" s="35">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>3.69</v>
+        <v>3.6900000000000004</v>
       </c>
       <c r="J12" s="29">
         <v>12</v>
       </c>
       <c r="K12" s="36">
         <f t="shared" si="0"/>
-        <v>8.31</v>
+        <v>8.3099999999999987</v>
       </c>
       <c r="L12" s="36">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>225.20325203252</v>
+        <v>225.20325203252028</v>
       </c>
       <c r="M12" s="36">
         <f t="shared" si="1"/>
-        <v>69.25</v>
-      </c>
-    </row>
-    <row r="13" ht="20.25" customHeight="1" spans="1:13">
+        <v>69.249999999999986</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="20.25" customHeight="1">
       <c r="A13" s="20" t="s">
         <v>34</v>
       </c>
@@ -2525,18 +1937,18 @@
       </c>
       <c r="K13" s="36">
         <f t="shared" si="0"/>
-        <v>10.56</v>
+        <v>10.559999999999999</v>
       </c>
       <c r="L13" s="36">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>194.117647058823</v>
+        <v>194.11764705882348</v>
       </c>
       <c r="M13" s="36">
         <f t="shared" si="1"/>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" ht="18.75" customHeight="1" spans="1:13">
+        <v>65.999999999999986</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="18.75" customHeight="1">
       <c r="A14" s="20" t="s">
         <v>35</v>
       </c>
@@ -2557,32 +1969,32 @@
         <v>3.3</v>
       </c>
       <c r="G14" s="29">
-        <v>0.685</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="H14" s="29">
         <v>0.2</v>
       </c>
       <c r="I14" s="35">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>4.185</v>
+        <v>4.1849999999999996</v>
       </c>
       <c r="J14" s="29">
         <v>14</v>
       </c>
       <c r="K14" s="36">
         <f t="shared" si="0"/>
-        <v>9.815</v>
+        <v>9.8150000000000013</v>
       </c>
       <c r="L14" s="36">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>234.52807646356</v>
+        <v>234.52807646356041</v>
       </c>
       <c r="M14" s="36">
         <f t="shared" si="1"/>
-        <v>70.1071428571429</v>
-      </c>
-    </row>
-    <row r="15" ht="18.75" customHeight="1" spans="1:13">
+        <v>70.107142857142861</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="18.75" customHeight="1">
       <c r="A15" s="20" t="s">
         <v>37</v>
       </c>
@@ -2610,7 +2022,7 @@
       </c>
       <c r="I15" s="35">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>6.22</v>
+        <v>6.2200000000000006</v>
       </c>
       <c r="J15" s="29">
         <v>18</v>
@@ -2621,14 +2033,14 @@
       </c>
       <c r="L15" s="36">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>189.389067524116</v>
+        <v>189.38906752411572</v>
       </c>
       <c r="M15" s="36">
         <f t="shared" si="1"/>
-        <v>65.4444444444444</v>
-      </c>
-    </row>
-    <row r="16" ht="18.75" customHeight="1" spans="1:13">
+        <v>65.444444444444443</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="18.75" customHeight="1">
       <c r="A16" s="20" t="s">
         <v>38</v>
       </c>
@@ -2649,32 +2061,32 @@
         <v>4.125</v>
       </c>
       <c r="G16" s="29">
-        <v>0.685</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="H16" s="29">
         <v>0.2</v>
       </c>
       <c r="I16" s="35">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>5.01</v>
+        <v>5.0100000000000007</v>
       </c>
       <c r="J16" s="29">
         <v>15</v>
       </c>
       <c r="K16" s="36">
         <f t="shared" si="0"/>
-        <v>9.99</v>
+        <v>9.9899999999999984</v>
       </c>
       <c r="L16" s="36">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>199.40119760479</v>
+        <v>199.40119760479035</v>
       </c>
       <c r="M16" s="36">
         <f t="shared" si="1"/>
-        <v>66.6</v>
-      </c>
-    </row>
-    <row r="17" ht="18.75" customHeight="1" spans="1:13">
+        <v>66.599999999999994</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="18.75" customHeight="1">
       <c r="A17" s="20" t="s">
         <v>40</v>
       </c>
@@ -2702,7 +2114,7 @@
       </c>
       <c r="I17" s="35">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>7.52</v>
+        <v>7.5200000000000005</v>
       </c>
       <c r="J17" s="29">
         <v>20</v>
@@ -2713,14 +2125,14 @@
       </c>
       <c r="L17" s="36">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>165.957446808511</v>
+        <v>165.95744680851064</v>
       </c>
       <c r="M17" s="36">
         <f t="shared" si="1"/>
         <v>62.4</v>
       </c>
     </row>
-    <row r="18" ht="18.75" customHeight="1" spans="1:13">
+    <row r="18" spans="1:13" ht="18.75" customHeight="1">
       <c r="A18" s="23" t="s">
         <v>41</v>
       </c>
@@ -2741,21 +2153,21 @@
         <v>4.59</v>
       </c>
       <c r="G18" s="29">
-        <v>0.685</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="H18" s="29">
         <v>0.2</v>
       </c>
       <c r="I18" s="35">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>5.475</v>
+        <v>5.4750000000000005</v>
       </c>
       <c r="J18" s="29">
         <v>15</v>
       </c>
       <c r="K18" s="36">
         <f t="shared" ref="K18" si="3">J18-(F18+G18+H18)</f>
-        <v>9.525</v>
+        <v>9.5249999999999986</v>
       </c>
       <c r="L18" s="36">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
@@ -2763,10 +2175,10 @@
       </c>
       <c r="M18" s="36">
         <f t="shared" ref="M18" si="4">(J18-(F18+G18+H18))/J18*100</f>
-        <v>63.5</v>
-      </c>
-    </row>
-    <row r="19" ht="18.75" customHeight="1" spans="1:13">
+        <v>63.499999999999993</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="18.75" customHeight="1">
       <c r="A19" s="23" t="s">
         <v>43</v>
       </c>
@@ -2787,32 +2199,32 @@
         <v>5.61</v>
       </c>
       <c r="G19" s="29">
-        <v>0.685</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="H19" s="29">
         <v>0.2</v>
       </c>
       <c r="I19" s="35">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>6.495</v>
+        <v>6.4950000000000001</v>
       </c>
       <c r="J19" s="29">
         <v>20</v>
       </c>
       <c r="K19" s="36">
         <f t="shared" si="0"/>
-        <v>13.505</v>
+        <v>13.504999999999999</v>
       </c>
       <c r="L19" s="36">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>207.929176289453</v>
+        <v>207.92917628945341</v>
       </c>
       <c r="M19" s="36">
         <f t="shared" si="1"/>
-        <v>67.525</v>
-      </c>
-    </row>
-    <row r="20" ht="18.75" customHeight="1" spans="1:13">
+        <v>67.524999999999991</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="18.75" customHeight="1">
       <c r="A20" s="23" t="s">
         <v>44</v>
       </c>
@@ -2851,14 +2263,14 @@
       </c>
       <c r="L20" s="36">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>143.407707910751</v>
+        <v>143.40770791075053</v>
       </c>
       <c r="M20" s="36">
         <f t="shared" si="1"/>
-        <v>58.9166666666667</v>
-      </c>
-    </row>
-    <row r="21" ht="18.75" customHeight="1" spans="1:13">
+        <v>58.916666666666671</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="18.75" customHeight="1">
       <c r="A21" s="23" t="s">
         <v>45</v>
       </c>
@@ -2879,32 +2291,32 @@
         <v>4.5</v>
       </c>
       <c r="G21" s="29">
-        <v>0.685</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="H21" s="29">
         <v>0.2</v>
       </c>
       <c r="I21" s="35">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>5.385</v>
+        <v>5.3850000000000007</v>
       </c>
       <c r="J21" s="29">
         <v>18</v>
       </c>
       <c r="K21" s="36">
         <f t="shared" si="0"/>
-        <v>12.615</v>
+        <v>12.614999999999998</v>
       </c>
       <c r="L21" s="36">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>234.261838440111</v>
+        <v>234.26183844011135</v>
       </c>
       <c r="M21" s="36">
         <f t="shared" si="1"/>
-        <v>70.0833333333333</v>
-      </c>
-    </row>
-    <row r="22" ht="18.75" customHeight="1" spans="1:13">
+        <v>70.083333333333314</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="18.75" customHeight="1">
       <c r="A22" s="23" t="s">
         <v>47</v>
       </c>
@@ -2929,7 +2341,7 @@
       <c r="L22" s="36"/>
       <c r="M22" s="36"/>
     </row>
-    <row r="23" ht="18.75" customHeight="1" spans="1:13">
+    <row r="23" spans="1:13" ht="18.75" customHeight="1">
       <c r="A23" s="23" t="s">
         <v>48</v>
       </c>
@@ -2966,14 +2378,14 @@
       </c>
       <c r="L23" s="36">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>170.27027027027</v>
+        <v>170.27027027027026</v>
       </c>
       <c r="M23" s="36">
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
     </row>
-    <row r="24" ht="18.75" customHeight="1" spans="1:13">
+    <row r="24" spans="1:13" ht="18.75" customHeight="1">
       <c r="A24" s="23" t="s">
         <v>50</v>
       </c>
@@ -3010,14 +2422,14 @@
       </c>
       <c r="L24" s="36">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>210.077519379845</v>
+        <v>210.07751937984494</v>
       </c>
       <c r="M24" s="36">
         <f t="shared" si="1"/>
         <v>67.75</v>
       </c>
     </row>
-    <row r="25" ht="18.75" customHeight="1" spans="1:13">
+    <row r="25" spans="1:13" ht="18.75" customHeight="1">
       <c r="A25" s="23" t="s">
         <v>51</v>
       </c>
@@ -3035,7 +2447,7 @@
       </c>
       <c r="F25" s="29">
         <f t="shared" si="5"/>
-        <v>5.454</v>
+        <v>5.4539999999999997</v>
       </c>
       <c r="G25" s="29">
         <v>0.82</v>
@@ -3052,18 +2464,18 @@
       </c>
       <c r="K25" s="36">
         <f t="shared" si="0"/>
-        <v>9.226</v>
+        <v>9.2259999999999991</v>
       </c>
       <c r="L25" s="36">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>136.19722468261</v>
+        <v>136.19722468260997</v>
       </c>
       <c r="M25" s="36">
         <f t="shared" si="1"/>
-        <v>57.6625</v>
-      </c>
-    </row>
-    <row r="26" ht="18.75" customHeight="1" spans="1:13">
+        <v>57.662499999999994</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="18.75" customHeight="1">
       <c r="A26" s="20" t="s">
         <v>52</v>
       </c>
@@ -3081,35 +2493,35 @@
       </c>
       <c r="F26" s="29">
         <f t="shared" si="5"/>
-        <v>2.9997</v>
+        <v>2.9996999999999998</v>
       </c>
       <c r="G26" s="29">
-        <v>0.685</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="H26" s="30">
         <v>1.5</v>
       </c>
       <c r="I26" s="37">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>5.1847</v>
+        <v>5.1846999999999994</v>
       </c>
       <c r="J26" s="29">
         <v>14</v>
       </c>
       <c r="K26" s="36">
         <f t="shared" si="0"/>
-        <v>8.8153</v>
+        <v>8.8153000000000006</v>
       </c>
       <c r="L26" s="36">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>170.025266649951</v>
+        <v>170.02526664995085</v>
       </c>
       <c r="M26" s="36">
         <f t="shared" si="1"/>
-        <v>62.9664285714286</v>
-      </c>
-    </row>
-    <row r="27" ht="18.75" customHeight="1" spans="1:13">
+        <v>62.96642857142858</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="18.75" customHeight="1">
       <c r="A27" s="20" t="s">
         <v>54</v>
       </c>
@@ -3127,7 +2539,7 @@
       </c>
       <c r="F27" s="29">
         <f t="shared" si="5"/>
-        <v>4.7268</v>
+        <v>4.7267999999999999</v>
       </c>
       <c r="G27" s="29">
         <v>0.82</v>
@@ -3137,25 +2549,25 @@
       </c>
       <c r="I27" s="37">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>7.0468</v>
+        <v>7.0468000000000002</v>
       </c>
       <c r="J27" s="29">
         <v>18</v>
       </c>
       <c r="K27" s="36">
         <f t="shared" si="0"/>
-        <v>10.9532</v>
+        <v>10.953199999999999</v>
       </c>
       <c r="L27" s="36">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>155.435091105182</v>
+        <v>155.43509110518247</v>
       </c>
       <c r="M27" s="36">
         <f t="shared" si="1"/>
-        <v>60.8511111111111</v>
-      </c>
-    </row>
-    <row r="28" ht="18.75" customHeight="1" spans="1:13">
+        <v>60.851111111111102</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="18.75" customHeight="1">
       <c r="A28" s="20" t="s">
         <v>55</v>
       </c>
@@ -3171,7 +2583,7 @@
       <c r="E28" s="22"/>
       <c r="F28" s="29">
         <f t="shared" si="5"/>
-        <v>0.8225</v>
+        <v>0.82250000000000001</v>
       </c>
       <c r="G28" s="29" t="s">
         <v>20</v>
@@ -3181,7 +2593,7 @@
       </c>
       <c r="I28" s="37">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>0.8225</v>
+        <v>0.82250000000000001</v>
       </c>
       <c r="J28" s="29" t="s">
         <v>20</v>
@@ -3194,7 +2606,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" ht="18.75" customHeight="1" spans="1:13">
+    <row r="29" spans="1:13" ht="18.75" customHeight="1">
       <c r="A29" s="20" t="s">
         <v>56</v>
       </c>
@@ -3215,32 +2627,32 @@
         <v>2.64</v>
       </c>
       <c r="G29" s="29">
-        <v>0.685</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="H29" s="30">
         <v>1.2</v>
       </c>
       <c r="I29" s="37">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>4.525</v>
+        <v>4.5250000000000004</v>
       </c>
       <c r="J29" s="29">
         <v>14</v>
       </c>
       <c r="K29" s="36">
         <f t="shared" si="0"/>
-        <v>9.475</v>
+        <v>9.4749999999999996</v>
       </c>
       <c r="L29" s="36">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>209.39226519337</v>
+        <v>209.39226519337012</v>
       </c>
       <c r="M29" s="36">
         <f t="shared" si="1"/>
-        <v>67.6785714285714</v>
-      </c>
-    </row>
-    <row r="30" ht="18.75" customHeight="1" spans="1:13">
+        <v>67.678571428571416</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="18.75" customHeight="1">
       <c r="A30" s="20" t="s">
         <v>58</v>
       </c>
@@ -3268,7 +2680,7 @@
       </c>
       <c r="I30" s="37">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>6.18</v>
+        <v>6.1800000000000006</v>
       </c>
       <c r="J30" s="29">
         <v>18</v>
@@ -3279,14 +2691,14 @@
       </c>
       <c r="L30" s="36">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>191.26213592233</v>
+        <v>191.26213592233009</v>
       </c>
       <c r="M30" s="36">
         <f t="shared" si="1"/>
-        <v>65.6666666666667</v>
-      </c>
-    </row>
-    <row r="31" ht="18.75" customHeight="1" spans="1:13">
+        <v>65.666666666666671</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="18.75" customHeight="1">
       <c r="A31" s="20" t="s">
         <v>59</v>
       </c>
@@ -3304,17 +2716,17 @@
       </c>
       <c r="F31" s="29">
         <f t="shared" si="5"/>
-        <v>0.805</v>
+        <v>0.80500000000000005</v>
       </c>
       <c r="G31" s="29">
         <v>0.82</v>
       </c>
       <c r="H31" s="29">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I31" s="35">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>5.725</v>
+        <v>5.7249999999999996</v>
       </c>
       <c r="J31" s="29">
         <v>16</v>
@@ -3325,14 +2737,14 @@
       </c>
       <c r="L31" s="36">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>179.475982532751</v>
+        <v>179.47598253275109</v>
       </c>
       <c r="M31" s="36">
         <f t="shared" si="1"/>
         <v>64.21875</v>
       </c>
     </row>
-    <row r="32" ht="18.75" customHeight="1" spans="1:13">
+    <row r="32" spans="1:13" ht="18.75" customHeight="1">
       <c r="A32" s="20" t="s">
         <v>61</v>
       </c>
@@ -3348,32 +2760,32 @@
         <v>3.88</v>
       </c>
       <c r="G32" s="29">
-        <v>0.685</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="H32" s="29">
         <v>0.2</v>
       </c>
       <c r="I32" s="35">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
-        <v>4.765</v>
+        <v>4.7649999999999997</v>
       </c>
       <c r="J32" s="29">
         <v>14</v>
       </c>
       <c r="K32" s="36">
         <f t="shared" si="0"/>
-        <v>9.235</v>
+        <v>9.2349999999999994</v>
       </c>
       <c r="L32" s="36">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>193.809024134313</v>
+        <v>193.80902413431269</v>
       </c>
       <c r="M32" s="36">
         <f t="shared" si="1"/>
-        <v>65.9642857142857</v>
-      </c>
-    </row>
-    <row r="33" ht="18.75" customHeight="1" spans="1:13">
+        <v>65.964285714285708</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="18.75" customHeight="1">
       <c r="A33" s="20" t="s">
         <v>63</v>
       </c>
@@ -3389,7 +2801,7 @@
         <v>5.28</v>
       </c>
       <c r="G33" s="29">
-        <v>0.685</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="H33" s="29">
         <v>0.2</v>
@@ -3403,18 +2815,18 @@
       </c>
       <c r="K33" s="36">
         <f t="shared" si="0"/>
-        <v>8.835</v>
+        <v>8.8350000000000009</v>
       </c>
       <c r="L33" s="36">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>143.30900243309</v>
+        <v>143.30900243309003</v>
       </c>
       <c r="M33" s="36">
         <f t="shared" si="1"/>
-        <v>58.9</v>
-      </c>
-    </row>
-    <row r="34" ht="18.75" customHeight="1" spans="1:13">
+        <v>58.900000000000006</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="18.75" customHeight="1">
       <c r="A34" s="20" t="s">
         <v>65</v>
       </c>
@@ -3450,14 +2862,14 @@
       </c>
       <c r="L34" s="36">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>213.31592689295</v>
+        <v>213.31592689295042</v>
       </c>
       <c r="M34" s="36">
         <f t="shared" si="1"/>
-        <v>68.0833333333333</v>
-      </c>
-    </row>
-    <row r="35" ht="18.75" customHeight="1" spans="1:13">
+        <v>68.083333333333329</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="18.75" customHeight="1">
       <c r="A35" s="20" t="s">
         <v>67</v>
       </c>
@@ -3492,18 +2904,18 @@
       </c>
       <c r="K35" s="36">
         <f t="shared" si="0"/>
-        <v>9.38</v>
+        <v>9.379999999999999</v>
       </c>
       <c r="L35" s="36">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>141.691842900302</v>
+        <v>141.69184290030211</v>
       </c>
       <c r="M35" s="36">
         <f t="shared" si="1"/>
-        <v>58.625</v>
-      </c>
-    </row>
-    <row r="36" ht="18.75" customHeight="1" spans="1:13">
+        <v>58.624999999999993</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="18.75" customHeight="1">
       <c r="A36" s="20" t="s">
         <v>69</v>
       </c>
@@ -3521,7 +2933,7 @@
         <v>2.5</v>
       </c>
       <c r="G36" s="29">
-        <v>0.685</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="H36" s="29">
         <v>1.4</v>
@@ -3535,22 +2947,23 @@
       </c>
       <c r="K36" s="36">
         <f t="shared" si="0"/>
-        <v>10.415</v>
+        <v>10.414999999999999</v>
       </c>
       <c r="L36" s="36">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>227.153762268266</v>
+        <v>227.15376226826604</v>
       </c>
       <c r="M36" s="36">
         <f t="shared" si="1"/>
-        <v>69.4333333333333</v>
-      </c>
-    </row>
-    <row r="40" spans="5:5">
+        <v>69.433333333333323</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="E40" s="16"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="M$1:M$1048576">
+  <phoneticPr fontId="11" type="noConversion"/>
+  <conditionalFormatting sqref="M1:M1048576">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -3559,14 +2972,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{af0a25a9-cce8-45bd-9b18-cd879bcdfcbd}</x14:id>
+          <x14:id>{AF0A25A9-CCE8-45BD-9B18-CD879BCDFCBD}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -3574,7 +2986,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{af0a25a9-cce8-45bd-9b18-cd879bcdfcbd}">
+          <x14:cfRule type="dataBar" id="{AF0A25A9-CCE8-45BD-9B18-CD879BCDFCBD}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -3584,7 +2996,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>M$1:M$1048576</xm:sqref>
+          <xm:sqref>M1:M1048576</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -3593,16 +3005,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D31"/>
-  <sheetFormatPr defaultColWidth="30.6923076923077" defaultRowHeight="20" customHeight="1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="30.75" defaultRowHeight="20.100000000000001" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="36.2211538461538" customWidth="1"/>
-    <col min="2" max="16384" width="30.6923076923077" customWidth="1"/>
+    <col min="1" max="1" width="36.25" customWidth="1"/>
+    <col min="2" max="2" width="30.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:4">
+    <row r="1" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>71</v>
       </c>
@@ -3616,7 +3027,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:4">
+    <row r="2" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>75</v>
       </c>
@@ -3630,7 +3041,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:4">
+    <row r="3" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>75</v>
       </c>
@@ -3644,7 +3055,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:4">
+    <row r="4" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>81</v>
       </c>
@@ -3658,7 +3069,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:4">
+    <row r="5" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>81</v>
       </c>
@@ -3672,7 +3083,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:4">
+    <row r="6" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="7" t="s">
         <v>84</v>
       </c>
@@ -3686,7 +3097,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:4">
+    <row r="7" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="5" t="s">
         <v>84</v>
       </c>
@@ -3700,7 +3111,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:4">
+    <row r="8" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="7" t="s">
         <v>86</v>
       </c>
@@ -3714,7 +3125,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:4">
+    <row r="9" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>86</v>
       </c>
@@ -3728,7 +3139,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:4">
+    <row r="10" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="7" t="s">
         <v>89</v>
       </c>
@@ -3742,7 +3153,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:4">
+    <row r="11" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="5" t="s">
         <v>91</v>
       </c>
@@ -3756,103 +3167,103 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:4">
+    <row r="12" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="7"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
     </row>
-    <row r="13" customHeight="1" spans="1:4">
+    <row r="13" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>93</v>
+      <c r="B13" s="38" t="s">
+        <v>120</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>85</v>
       </c>
       <c r="D13" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="A14" s="7" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:4">
-      <c r="A14" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>93</v>
+      <c r="B14" s="39" t="s">
+        <v>120</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>85</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:4">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="5"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" customHeight="1" spans="1:4">
+    <row r="16" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A16" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="C16" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="D16" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="D16" s="8" t="s">
+    </row>
+    <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="A17" s="5" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:4">
-      <c r="A17" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>101</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:4">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>90</v>
       </c>
       <c r="C18" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="A19" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="1:4">
-      <c r="A19" s="5" t="s">
-        <v>104</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>90</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="1:4">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A20" s="7" t="s">
         <v>48</v>
       </c>
@@ -3860,15 +3271,15 @@
         <v>90</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="1:4">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>90</v>
@@ -3877,12 +3288,12 @@
         <v>80</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="1:4">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A22" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>90</v>
@@ -3891,129 +3302,129 @@
         <v>80</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:4">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A23" s="5"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
     </row>
-    <row r="24" customHeight="1" spans="1:4">
+    <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A24" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="C24" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="D24" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="D24" s="8" t="s">
+    </row>
+    <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="A25" s="5" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="25" customHeight="1" spans="1:4">
-      <c r="A25" s="5" t="s">
+      <c r="B25" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="A26" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C25" s="6" t="s">
+      <c r="B26" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="1:4">
-      <c r="A26" s="7" t="s">
+    </row>
+    <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="A27" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B26" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="1:4">
-      <c r="A27" s="5" t="s">
+      <c r="C27" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="A28" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="1:4">
-      <c r="A28" s="7" t="s">
+      <c r="B28" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="B28" s="8" t="s">
-        <v>116</v>
-      </c>
       <c r="C28" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="1:4">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A29" s="5" t="s">
         <v>22</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C29" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D29" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="1:4">
+    </row>
+    <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A30" s="7" t="s">
         <v>19</v>
       </c>
       <c r="B30" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="C30" s="8" t="s">
-        <v>118</v>
-      </c>
       <c r="D30" s="8" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="1:4">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A31" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B31" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C31" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>120</v>
-      </c>
       <c r="D31" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/财务与流水/馋唻买-听涛路店商品表.xlsx
+++ b/财务与流水/馋唻买-听涛路店商品表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github localpath\ChanWeiMai\财务与流水\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC175AB-8153-494D-A11F-9837BFB48805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8657EE04-C477-4311-B326-75FA01E39B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8745" yWindow="1320" windowWidth="35070" windowHeight="19335" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2475" yWindow="885" windowWidth="35070" windowHeight="19335" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="堂食利润" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="123">
   <si>
     <t>SKU</t>
   </si>
@@ -254,9 +254,6 @@
     <t>大份(240克)</t>
   </si>
   <si>
-    <t>10元</t>
-  </si>
-  <si>
     <t>本店招牌</t>
   </si>
   <si>
@@ -272,118 +269,131 @@
     <t>12元</t>
   </si>
   <si>
+    <t>牛肉羹瘦肉丸</t>
+  </si>
+  <si>
+    <t>20元</t>
+  </si>
+  <si>
+    <t>福鼎手工肉燕</t>
+  </si>
+  <si>
+    <t>大份(180克)</t>
+  </si>
+  <si>
+    <t>特大份(240克)</t>
+  </si>
+  <si>
+    <t>剁椒干拌瘦肉丸</t>
+  </si>
+  <si>
+    <t>约240克</t>
+  </si>
+  <si>
+    <t>金汤酸菜瘦肉丸</t>
+  </si>
+  <si>
+    <t>随心双拼(经典/牛肉羹/肉燕)</t>
+  </si>
+  <si>
+    <t>自由搭配</t>
+  </si>
+  <si>
+    <t>豪华三拼(经典+牛肉羹+肉燕)</t>
+  </si>
+  <si>
+    <t>手工挂面</t>
+  </si>
+  <si>
+    <t>约180克</t>
+  </si>
+  <si>
+    <t>8元</t>
+  </si>
+  <si>
+    <t>特色口味</t>
+  </si>
+  <si>
+    <t>手工挂面+瘦肉丸</t>
+  </si>
+  <si>
+    <t>月240克</t>
+  </si>
+  <si>
+    <t>火鸡面干拌瘦肉丸(辣)</t>
+  </si>
+  <si>
+    <t>13元</t>
+  </si>
+  <si>
+    <t>燕面干拌瘦肉丸</t>
+  </si>
+  <si>
+    <t>金汤酸菜泡面+瘦肉丸</t>
+  </si>
+  <si>
+    <t>金汤酸菜弹粉+瘦肉丸</t>
+  </si>
+  <si>
+    <t>沙县蒸饺(10只)</t>
+  </si>
+  <si>
+    <t>10只</t>
+  </si>
+  <si>
+    <t>6元</t>
+  </si>
+  <si>
+    <t>特色小吃</t>
+  </si>
+  <si>
+    <t>拇指小笼包(10只)</t>
+  </si>
+  <si>
+    <t>福州鱼丸(8颗)</t>
+  </si>
+  <si>
+    <t>8颗</t>
+  </si>
+  <si>
+    <t>潮汕牛肉丸(8颗)</t>
+  </si>
+  <si>
+    <t>纸皮烧卖(3只)</t>
+  </si>
+  <si>
+    <t>3只(蛋黄/肉松)</t>
+  </si>
+  <si>
+    <t>1个</t>
+  </si>
+  <si>
+    <t>3元</t>
+  </si>
+  <si>
+    <t>1根</t>
+  </si>
+  <si>
+    <t>4元</t>
+  </si>
+  <si>
+    <t>约370克</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>12元</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
     <t>16元</t>
-  </si>
-  <si>
-    <t>牛肉羹瘦肉丸</t>
-  </si>
-  <si>
-    <t>20元</t>
-  </si>
-  <si>
-    <t>福鼎手工肉燕</t>
-  </si>
-  <si>
-    <t>大份(180克)</t>
-  </si>
-  <si>
-    <t>特大份(240克)</t>
-  </si>
-  <si>
-    <t>剁椒干拌瘦肉丸</t>
-  </si>
-  <si>
-    <t>约240克</t>
-  </si>
-  <si>
-    <t>金汤酸菜瘦肉丸</t>
-  </si>
-  <si>
-    <t>随心双拼(经典/牛肉羹/肉燕)</t>
-  </si>
-  <si>
-    <t>自由搭配</t>
-  </si>
-  <si>
-    <t>豪华三拼(经典+牛肉羹+肉燕)</t>
-  </si>
-  <si>
-    <t>手工挂面</t>
-  </si>
-  <si>
-    <t>约180克</t>
-  </si>
-  <si>
-    <t>8元</t>
-  </si>
-  <si>
-    <t>特色口味</t>
-  </si>
-  <si>
-    <t>手工挂面+瘦肉丸</t>
-  </si>
-  <si>
-    <t>月240克</t>
-  </si>
-  <si>
-    <t>火鸡面干拌瘦肉丸(辣)</t>
-  </si>
-  <si>
-    <t>13元</t>
-  </si>
-  <si>
-    <t>燕面干拌瘦肉丸</t>
-  </si>
-  <si>
-    <t>金汤酸菜泡面+瘦肉丸</t>
-  </si>
-  <si>
-    <t>金汤酸菜弹粉+瘦肉丸</t>
-  </si>
-  <si>
-    <t>沙县蒸饺(10只)</t>
-  </si>
-  <si>
-    <t>10只</t>
-  </si>
-  <si>
-    <t>6元</t>
-  </si>
-  <si>
-    <t>特色小吃</t>
-  </si>
-  <si>
-    <t>拇指小笼包(10只)</t>
-  </si>
-  <si>
-    <t>福州鱼丸(8颗)</t>
-  </si>
-  <si>
-    <t>8颗</t>
-  </si>
-  <si>
-    <t>潮汕牛肉丸(8颗)</t>
-  </si>
-  <si>
-    <t>纸皮烧卖(3只)</t>
-  </si>
-  <si>
-    <t>3只(蛋黄/肉松)</t>
-  </si>
-  <si>
-    <t>1个</t>
-  </si>
-  <si>
-    <t>3元</t>
-  </si>
-  <si>
-    <t>1根</t>
-  </si>
-  <si>
-    <t>4元</t>
-  </si>
-  <si>
-    <t>约370克</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>14元</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>18元</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -643,7 +653,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -653,9 +663,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -740,6 +747,10 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1352,1614 +1363,1614 @@
   <dimension ref="A1:M40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="30.5" style="11" customWidth="1"/>
-    <col min="2" max="2" width="14" style="12" customWidth="1"/>
-    <col min="3" max="3" width="20.25" style="12" customWidth="1"/>
-    <col min="4" max="4" width="23.875" style="13" customWidth="1"/>
-    <col min="5" max="5" width="33.5" style="13" customWidth="1"/>
-    <col min="6" max="6" width="18.625" style="14" customWidth="1"/>
-    <col min="7" max="7" width="19.25" style="14" customWidth="1"/>
-    <col min="8" max="8" width="18.625" style="14" customWidth="1"/>
-    <col min="9" max="9" width="19.125" style="15" customWidth="1"/>
-    <col min="10" max="10" width="18" style="16" customWidth="1"/>
-    <col min="11" max="11" width="16.75" style="14" customWidth="1"/>
-    <col min="12" max="12" width="17.625" style="14" customWidth="1"/>
-    <col min="13" max="13" width="14.75" style="14" customWidth="1"/>
+    <col min="1" max="1" width="30.5" style="10" customWidth="1"/>
+    <col min="2" max="2" width="14" style="11" customWidth="1"/>
+    <col min="3" max="3" width="20.25" style="11" customWidth="1"/>
+    <col min="4" max="4" width="23.875" style="12" customWidth="1"/>
+    <col min="5" max="5" width="33.5" style="12" customWidth="1"/>
+    <col min="6" max="6" width="18.625" style="13" customWidth="1"/>
+    <col min="7" max="7" width="19.25" style="13" customWidth="1"/>
+    <col min="8" max="8" width="18.625" style="13" customWidth="1"/>
+    <col min="9" max="9" width="19.125" style="14" customWidth="1"/>
+    <col min="10" max="10" width="18" style="15" customWidth="1"/>
+    <col min="11" max="11" width="16.75" style="13" customWidth="1"/>
+    <col min="12" max="12" width="17.625" style="13" customWidth="1"/>
+    <col min="13" max="13" width="14.75" style="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="10" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:13" s="9" customFormat="1" ht="29.25" customHeight="1">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="26" t="s">
+      <c r="I1" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="26" t="s">
+      <c r="K1" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="26" t="s">
+      <c r="L1" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="26" t="s">
+      <c r="M1" s="25" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="21">
+      <c r="B2" s="20">
         <v>11</v>
       </c>
-      <c r="C2" s="21">
+      <c r="C2" s="20">
         <v>0.5</v>
       </c>
-      <c r="D2" s="22">
+      <c r="D2" s="21">
         <v>120</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="28">
+      <c r="F2" s="27">
         <f>(B2+SKUTable[[#This Row],[运费(元/500g)]])*D2/500</f>
         <v>2.76</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G2" s="27">
         <v>0.2</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="27">
         <v>0.15</v>
       </c>
-      <c r="I2" s="32">
+      <c r="I2" s="31">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>3.11</v>
       </c>
-      <c r="J2" s="33">
+      <c r="J2" s="32">
         <v>8</v>
       </c>
-      <c r="K2" s="34">
+      <c r="K2" s="33">
         <f>J2-(F2+G2+H2)</f>
         <v>4.8900000000000006</v>
       </c>
-      <c r="L2" s="34">
+      <c r="L2" s="33">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>157.23472668810291</v>
       </c>
-      <c r="M2" s="34">
+      <c r="M2" s="33">
         <f>(J2-(F2+G2+H2))/J2*100</f>
         <v>61.125000000000007</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="22">
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="21">
         <v>220</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="28">
+      <c r="F3" s="27">
         <v>2.4500000000000002</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3" s="27">
         <v>0.2</v>
       </c>
-      <c r="H3" s="28">
+      <c r="H3" s="27">
         <v>0.15</v>
       </c>
-      <c r="I3" s="32">
+      <c r="I3" s="31">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>2.8000000000000003</v>
       </c>
-      <c r="J3" s="33">
+      <c r="J3" s="32">
         <v>8</v>
       </c>
-      <c r="K3" s="34">
+      <c r="K3" s="33">
         <f>J3-(F3+G3+H3)</f>
         <v>5.1999999999999993</v>
       </c>
-      <c r="L3" s="34">
+      <c r="L3" s="33">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>185.71428571428567</v>
       </c>
-      <c r="M3" s="34">
+      <c r="M3" s="33">
         <f>(J3-(F3+G3+H3))/J3*100</f>
         <v>64.999999999999986</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="20">
         <v>8.8000000000000007</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="20">
         <v>0</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="21">
         <v>70</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="27">
         <f>(B4+SKUTable[[#This Row],[运费(元/500g)]])*D4/500</f>
         <v>1.232</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="27">
         <v>0.05</v>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="27">
         <v>0</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="31">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>1.282</v>
       </c>
-      <c r="J4" s="33">
+      <c r="J4" s="32">
         <v>4</v>
       </c>
-      <c r="K4" s="34">
+      <c r="K4" s="33">
         <f t="shared" ref="K4:K36" si="0">J4-(F4+G4+H4)</f>
         <v>2.718</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="33">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>212.01248049921998</v>
       </c>
-      <c r="M4" s="34">
+      <c r="M4" s="33">
         <f t="shared" ref="M4:M36" si="1">(J4-(F4+G4+H4))/J4*100</f>
         <v>67.95</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="27">
         <v>2</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="27">
         <v>0.05</v>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="27">
         <v>0</v>
       </c>
-      <c r="I5" s="32">
+      <c r="I5" s="31">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>2.0499999999999998</v>
       </c>
-      <c r="J5" s="33">
+      <c r="J5" s="32">
         <v>5</v>
       </c>
-      <c r="K5" s="34">
+      <c r="K5" s="33">
         <f t="shared" si="0"/>
         <v>2.95</v>
       </c>
-      <c r="L5" s="34">
+      <c r="L5" s="33">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>143.90243902439025</v>
       </c>
-      <c r="M5" s="34">
+      <c r="M5" s="33">
         <f t="shared" si="1"/>
         <v>59.000000000000007</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="27">
         <v>2.8</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="27">
         <v>0.05</v>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="27">
         <v>0</v>
       </c>
-      <c r="I6" s="32">
+      <c r="I6" s="31">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>2.8499999999999996</v>
       </c>
-      <c r="J6" s="33">
+      <c r="J6" s="32">
         <v>6</v>
       </c>
-      <c r="K6" s="34">
+      <c r="K6" s="33">
         <f t="shared" si="0"/>
         <v>3.1500000000000004</v>
       </c>
-      <c r="L6" s="34">
+      <c r="L6" s="33">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>110.52631578947371</v>
       </c>
-      <c r="M6" s="34">
+      <c r="M6" s="33">
         <f t="shared" si="1"/>
         <v>52.5</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="28">
         <v>3.24</v>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="28">
         <v>0.2</v>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="28">
         <v>0</v>
       </c>
-      <c r="I7" s="35">
+      <c r="I7" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>3.4400000000000004</v>
       </c>
-      <c r="J7" s="29">
+      <c r="J7" s="28">
         <v>8</v>
       </c>
-      <c r="K7" s="36">
+      <c r="K7" s="35">
         <f t="shared" si="0"/>
         <v>4.5599999999999996</v>
       </c>
-      <c r="L7" s="36">
+      <c r="L7" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>132.55813953488368</v>
       </c>
-      <c r="M7" s="36">
+      <c r="M7" s="35">
         <f t="shared" si="1"/>
         <v>56.999999999999993</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="28">
         <v>0.4</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="28">
         <v>0</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="28">
         <v>0</v>
       </c>
-      <c r="I8" s="35">
+      <c r="I8" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>0.4</v>
       </c>
-      <c r="J8" s="29">
+      <c r="J8" s="28">
         <v>1.25</v>
       </c>
-      <c r="K8" s="36">
+      <c r="K8" s="35">
         <f t="shared" si="0"/>
         <v>0.85</v>
       </c>
-      <c r="L8" s="36">
+      <c r="L8" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>212.5</v>
       </c>
-      <c r="M8" s="36">
+      <c r="M8" s="35">
         <f t="shared" si="1"/>
         <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="28">
         <v>0.45</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="28">
         <v>0</v>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="28">
         <v>0</v>
       </c>
-      <c r="I9" s="35">
+      <c r="I9" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>0.45</v>
       </c>
-      <c r="J9" s="29">
+      <c r="J9" s="28">
         <v>1.25</v>
       </c>
-      <c r="K9" s="36">
+      <c r="K9" s="35">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="L9" s="36">
+      <c r="L9" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>177.7777777777778</v>
       </c>
-      <c r="M9" s="36">
+      <c r="M9" s="35">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="28">
         <v>1.37</v>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="28">
         <v>0</v>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="28">
         <v>0</v>
       </c>
-      <c r="I10" s="35">
+      <c r="I10" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>1.37</v>
       </c>
-      <c r="J10" s="29">
+      <c r="J10" s="28">
         <v>2.5</v>
       </c>
-      <c r="K10" s="36">
+      <c r="K10" s="35">
         <f t="shared" si="0"/>
         <v>1.1299999999999999</v>
       </c>
-      <c r="L10" s="36">
+      <c r="L10" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>82.481751824817508</v>
       </c>
-      <c r="M10" s="36">
+      <c r="M10" s="35">
         <f t="shared" si="1"/>
         <v>45.199999999999996</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="28">
         <v>1.37</v>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="28">
         <v>0</v>
       </c>
-      <c r="H11" s="29">
+      <c r="H11" s="28">
         <v>0</v>
       </c>
-      <c r="I11" s="35">
+      <c r="I11" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>1.37</v>
       </c>
-      <c r="J11" s="29">
+      <c r="J11" s="28">
         <v>2.5</v>
       </c>
-      <c r="K11" s="36">
+      <c r="K11" s="35">
         <f t="shared" si="0"/>
         <v>1.1299999999999999</v>
       </c>
-      <c r="L11" s="36">
+      <c r="L11" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>82.481751824817508</v>
       </c>
-      <c r="M11" s="36">
+      <c r="M11" s="35">
         <f t="shared" si="1"/>
         <v>45.199999999999996</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="20">
         <v>8</v>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="20">
         <v>0.5</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="21">
         <v>165</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="E12" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="28">
         <f>(B12+SKUTable[[#This Row],[运费(元/500g)]])*D12/500</f>
         <v>2.8050000000000002</v>
       </c>
-      <c r="G12" s="29">
+      <c r="G12" s="28">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H12" s="29">
+      <c r="H12" s="28">
         <v>0.2</v>
       </c>
-      <c r="I12" s="35">
+      <c r="I12" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>3.6900000000000004</v>
       </c>
-      <c r="J12" s="29">
+      <c r="J12" s="28">
         <v>12</v>
       </c>
-      <c r="K12" s="36">
+      <c r="K12" s="35">
         <f t="shared" si="0"/>
         <v>8.3099999999999987</v>
       </c>
-      <c r="L12" s="36">
+      <c r="L12" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>225.20325203252028</v>
       </c>
-      <c r="M12" s="36">
+      <c r="M12" s="35">
         <f t="shared" si="1"/>
         <v>69.249999999999986</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="20">
         <v>8</v>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="20">
         <v>0.5</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="21">
         <v>260</v>
       </c>
-      <c r="E13" s="27" t="s">
+      <c r="E13" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="28">
         <f>(B13+SKUTable[[#This Row],[运费(元/500g)]])*D13/500</f>
         <v>4.42</v>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="28">
         <v>0.82</v>
       </c>
-      <c r="H13" s="29">
+      <c r="H13" s="28">
         <v>0.2</v>
       </c>
-      <c r="I13" s="35">
+      <c r="I13" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.44</v>
       </c>
-      <c r="J13" s="29">
+      <c r="J13" s="28">
         <v>16</v>
       </c>
-      <c r="K13" s="36">
+      <c r="K13" s="35">
         <f t="shared" si="0"/>
         <v>10.559999999999999</v>
       </c>
-      <c r="L13" s="36">
+      <c r="L13" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>194.11764705882348</v>
       </c>
-      <c r="M13" s="36">
+      <c r="M13" s="35">
         <f t="shared" si="1"/>
         <v>65.999999999999986</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="20">
         <v>10</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="20">
         <v>0.5</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="21">
         <v>165</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="28">
         <f>IF(B14&lt;&gt;"",B14*D14/500,"")</f>
         <v>3.3</v>
       </c>
-      <c r="G14" s="29">
+      <c r="G14" s="28">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H14" s="29">
+      <c r="H14" s="28">
         <v>0.2</v>
       </c>
-      <c r="I14" s="35">
+      <c r="I14" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>4.1849999999999996</v>
       </c>
-      <c r="J14" s="29">
+      <c r="J14" s="28">
         <v>14</v>
       </c>
-      <c r="K14" s="36">
+      <c r="K14" s="35">
         <f t="shared" si="0"/>
         <v>9.8150000000000013</v>
       </c>
-      <c r="L14" s="36">
+      <c r="L14" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>234.52807646356041</v>
       </c>
-      <c r="M14" s="36">
+      <c r="M14" s="35">
         <f t="shared" si="1"/>
         <v>70.107142857142861</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="20">
         <v>10</v>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="20">
         <v>0.5</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="21">
         <v>260</v>
       </c>
-      <c r="E15" s="27" t="s">
+      <c r="E15" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="28">
         <f>IF(B15&lt;&gt;"",B15*D15/500,"")</f>
         <v>5.2</v>
       </c>
-      <c r="G15" s="29">
+      <c r="G15" s="28">
         <v>0.82</v>
       </c>
-      <c r="H15" s="29">
+      <c r="H15" s="28">
         <v>0.2</v>
       </c>
-      <c r="I15" s="35">
+      <c r="I15" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>6.2200000000000006</v>
       </c>
-      <c r="J15" s="29">
+      <c r="J15" s="28">
         <v>18</v>
       </c>
-      <c r="K15" s="36">
+      <c r="K15" s="35">
         <f t="shared" si="0"/>
         <v>11.78</v>
       </c>
-      <c r="L15" s="36">
+      <c r="L15" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>189.38906752411572</v>
       </c>
-      <c r="M15" s="36">
+      <c r="M15" s="35">
         <f t="shared" si="1"/>
         <v>65.444444444444443</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="20">
         <v>12.5</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="20">
         <v>0.5</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="21">
         <v>165</v>
       </c>
-      <c r="E16" s="27" t="s">
+      <c r="E16" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="28">
         <f>IF(B16&lt;&gt;"",B16*D16/500,"")</f>
         <v>4.125</v>
       </c>
-      <c r="G16" s="29">
+      <c r="G16" s="28">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H16" s="29">
+      <c r="H16" s="28">
         <v>0.2</v>
       </c>
-      <c r="I16" s="35">
+      <c r="I16" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.0100000000000007</v>
       </c>
-      <c r="J16" s="29">
+      <c r="J16" s="28">
         <v>15</v>
       </c>
-      <c r="K16" s="36">
+      <c r="K16" s="35">
         <f t="shared" si="0"/>
         <v>9.9899999999999984</v>
       </c>
-      <c r="L16" s="36">
+      <c r="L16" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>199.40119760479035</v>
       </c>
-      <c r="M16" s="36">
+      <c r="M16" s="35">
         <f t="shared" si="1"/>
         <v>66.599999999999994</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="20">
         <v>12.5</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="20">
         <v>0.5</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="21">
         <v>260</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="28">
         <f>IF(B17&lt;&gt;"",B17*D17/500,"")</f>
         <v>6.5</v>
       </c>
-      <c r="G17" s="29">
+      <c r="G17" s="28">
         <v>0.82</v>
       </c>
-      <c r="H17" s="29">
+      <c r="H17" s="28">
         <v>0.2</v>
       </c>
-      <c r="I17" s="35">
+      <c r="I17" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>7.5200000000000005</v>
       </c>
-      <c r="J17" s="29">
+      <c r="J17" s="28">
         <v>20</v>
       </c>
-      <c r="K17" s="36">
+      <c r="K17" s="35">
         <f t="shared" si="0"/>
         <v>12.48</v>
       </c>
-      <c r="L17" s="36">
+      <c r="L17" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>165.95744680851064</v>
       </c>
-      <c r="M17" s="36">
+      <c r="M17" s="35">
         <f t="shared" si="1"/>
         <v>62.4</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="20">
         <v>17</v>
       </c>
-      <c r="C18" s="21">
+      <c r="C18" s="20">
         <v>0.5</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="21">
         <v>135</v>
       </c>
-      <c r="E18" s="27" t="s">
+      <c r="E18" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="28">
         <f t="shared" ref="F18" si="2">IF(B18&lt;&gt;"",B18*D18/500,"")</f>
         <v>4.59</v>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="28">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="28">
         <v>0.2</v>
       </c>
-      <c r="I18" s="35">
+      <c r="I18" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.4750000000000005</v>
       </c>
-      <c r="J18" s="29">
+      <c r="J18" s="28">
         <v>15</v>
       </c>
-      <c r="K18" s="36">
+      <c r="K18" s="35">
         <f t="shared" ref="K18" si="3">J18-(F18+G18+H18)</f>
         <v>9.5249999999999986</v>
       </c>
-      <c r="L18" s="36">
+      <c r="L18" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>173.972602739726</v>
       </c>
-      <c r="M18" s="36">
+      <c r="M18" s="35">
         <f t="shared" ref="M18" si="4">(J18-(F18+G18+H18))/J18*100</f>
         <v>63.499999999999993</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="21">
+      <c r="B19" s="20">
         <v>17</v>
       </c>
-      <c r="C19" s="21">
+      <c r="C19" s="20">
         <v>0.5</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="21">
         <v>165</v>
       </c>
-      <c r="E19" s="27" t="s">
+      <c r="E19" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="28">
         <f t="shared" ref="F19:F35" si="5">IF(B19&lt;&gt;"",B19*D19/500,"")</f>
         <v>5.61</v>
       </c>
-      <c r="G19" s="29">
+      <c r="G19" s="28">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H19" s="29">
+      <c r="H19" s="28">
         <v>0.2</v>
       </c>
-      <c r="I19" s="35">
+      <c r="I19" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>6.4950000000000001</v>
       </c>
-      <c r="J19" s="29">
+      <c r="J19" s="28">
         <v>20</v>
       </c>
-      <c r="K19" s="36">
+      <c r="K19" s="35">
         <f t="shared" si="0"/>
         <v>13.504999999999999</v>
       </c>
-      <c r="L19" s="36">
+      <c r="L19" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>207.92917628945341</v>
       </c>
-      <c r="M19" s="36">
+      <c r="M19" s="35">
         <f t="shared" si="1"/>
         <v>67.524999999999991</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="21">
+      <c r="B20" s="20">
         <v>17</v>
       </c>
-      <c r="C20" s="21">
+      <c r="C20" s="20">
         <v>0.5</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="21">
         <v>260</v>
       </c>
-      <c r="E20" s="27" t="s">
+      <c r="E20" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="28">
         <f t="shared" si="5"/>
         <v>8.84</v>
       </c>
-      <c r="G20" s="29">
+      <c r="G20" s="28">
         <v>0.82</v>
       </c>
-      <c r="H20" s="29">
+      <c r="H20" s="28">
         <v>0.2</v>
       </c>
-      <c r="I20" s="35">
+      <c r="I20" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>9.86</v>
       </c>
-      <c r="J20" s="29">
+      <c r="J20" s="28">
         <v>24</v>
       </c>
-      <c r="K20" s="36">
+      <c r="K20" s="35">
         <f t="shared" si="0"/>
         <v>14.14</v>
       </c>
-      <c r="L20" s="36">
+      <c r="L20" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>143.40770791075053</v>
       </c>
-      <c r="M20" s="36">
+      <c r="M20" s="35">
         <f t="shared" si="1"/>
         <v>58.916666666666671</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="21">
+      <c r="B21" s="20">
         <v>22.5</v>
       </c>
-      <c r="C21" s="21">
+      <c r="C21" s="20">
         <v>0.5</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="21">
         <v>100</v>
       </c>
-      <c r="E21" s="27" t="s">
+      <c r="E21" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="28">
         <f t="shared" si="5"/>
         <v>4.5</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="28">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="28">
         <v>0.2</v>
       </c>
-      <c r="I21" s="35">
+      <c r="I21" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.3850000000000007</v>
       </c>
-      <c r="J21" s="29">
+      <c r="J21" s="28">
         <v>18</v>
       </c>
-      <c r="K21" s="36">
+      <c r="K21" s="35">
         <f t="shared" si="0"/>
         <v>12.614999999999998</v>
       </c>
-      <c r="L21" s="36">
+      <c r="L21" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>234.26183844011135</v>
       </c>
-      <c r="M21" s="36">
+      <c r="M21" s="35">
         <f t="shared" si="1"/>
         <v>70.083333333333314</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="21">
+      <c r="B22" s="20">
         <v>19</v>
       </c>
-      <c r="C22" s="21">
+      <c r="C22" s="20">
         <v>0.5</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="E22" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="29"/>
-      <c r="K22" s="36"/>
-      <c r="L22" s="36"/>
-      <c r="M22" s="36"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="35"/>
     </row>
     <row r="23" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="21">
+      <c r="B23" s="20">
         <v>19</v>
       </c>
-      <c r="C23" s="21">
+      <c r="C23" s="20">
         <v>0.5</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="21">
         <v>90</v>
       </c>
-      <c r="E23" s="27" t="s">
+      <c r="E23" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="28">
         <f t="shared" si="5"/>
         <v>3.42</v>
       </c>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29">
+      <c r="G23" s="28"/>
+      <c r="H23" s="28">
         <v>2.5</v>
       </c>
-      <c r="I23" s="35">
+      <c r="I23" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.92</v>
       </c>
-      <c r="J23" s="29">
+      <c r="J23" s="28">
         <v>16</v>
       </c>
-      <c r="K23" s="36">
+      <c r="K23" s="35">
         <f t="shared" si="0"/>
         <v>10.08</v>
       </c>
-      <c r="L23" s="36">
+      <c r="L23" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>170.27027027027026</v>
       </c>
-      <c r="M23" s="36">
+      <c r="M23" s="35">
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A24" s="23" t="s">
+      <c r="A24" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="21">
+      <c r="B24" s="20">
         <v>19</v>
       </c>
-      <c r="C24" s="21">
+      <c r="C24" s="20">
         <v>0.5</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="21">
         <v>70</v>
       </c>
-      <c r="E24" s="27" t="s">
+      <c r="E24" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="28">
         <f t="shared" si="5"/>
         <v>2.66</v>
       </c>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29">
+      <c r="G24" s="28"/>
+      <c r="H24" s="28">
         <v>2.5</v>
       </c>
-      <c r="I24" s="35">
+      <c r="I24" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.16</v>
       </c>
-      <c r="J24" s="29">
+      <c r="J24" s="28">
         <v>16</v>
       </c>
-      <c r="K24" s="36">
+      <c r="K24" s="35">
         <f t="shared" si="0"/>
         <v>10.84</v>
       </c>
-      <c r="L24" s="36">
+      <c r="L24" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>210.07751937984494</v>
       </c>
-      <c r="M24" s="36">
+      <c r="M24" s="35">
         <f t="shared" si="1"/>
         <v>67.75</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="21">
+      <c r="B25" s="20">
         <v>9.09</v>
       </c>
-      <c r="C25" s="21">
+      <c r="C25" s="20">
         <v>0.5</v>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="21">
         <v>300</v>
       </c>
-      <c r="E25" s="27" t="s">
+      <c r="E25" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="28">
         <f t="shared" si="5"/>
         <v>5.4539999999999997</v>
       </c>
-      <c r="G25" s="29">
+      <c r="G25" s="28">
         <v>0.82</v>
       </c>
-      <c r="H25" s="30">
+      <c r="H25" s="29">
         <v>0.5</v>
       </c>
-      <c r="I25" s="37">
+      <c r="I25" s="36">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>6.774</v>
       </c>
-      <c r="J25" s="29">
+      <c r="J25" s="28">
         <v>16</v>
       </c>
-      <c r="K25" s="36">
+      <c r="K25" s="35">
         <f t="shared" si="0"/>
         <v>9.2259999999999991</v>
       </c>
-      <c r="L25" s="36">
+      <c r="L25" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>136.19722468260997</v>
       </c>
-      <c r="M25" s="36">
+      <c r="M25" s="35">
         <f t="shared" si="1"/>
         <v>57.662499999999994</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="21">
+      <c r="B26" s="20">
         <v>9.09</v>
       </c>
-      <c r="C26" s="21">
+      <c r="C26" s="20">
         <v>0.5</v>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="21">
         <v>165</v>
       </c>
-      <c r="E26" s="27" t="s">
+      <c r="E26" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="F26" s="29">
+      <c r="F26" s="28">
         <f t="shared" si="5"/>
         <v>2.9996999999999998</v>
       </c>
-      <c r="G26" s="29">
+      <c r="G26" s="28">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H26" s="30">
+      <c r="H26" s="29">
         <v>1.5</v>
       </c>
-      <c r="I26" s="37">
+      <c r="I26" s="36">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.1846999999999994</v>
       </c>
-      <c r="J26" s="29">
+      <c r="J26" s="28">
         <v>14</v>
       </c>
-      <c r="K26" s="36">
+      <c r="K26" s="35">
         <f t="shared" si="0"/>
         <v>8.8153000000000006</v>
       </c>
-      <c r="L26" s="36">
+      <c r="L26" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>170.02526664995085</v>
       </c>
-      <c r="M26" s="36">
+      <c r="M26" s="35">
         <f t="shared" si="1"/>
         <v>62.96642857142858</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="21">
+      <c r="B27" s="20">
         <v>9.09</v>
       </c>
-      <c r="C27" s="21">
+      <c r="C27" s="20">
         <v>0.5</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="21">
         <v>260</v>
       </c>
-      <c r="E27" s="27" t="s">
+      <c r="E27" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="F27" s="29">
+      <c r="F27" s="28">
         <f t="shared" si="5"/>
         <v>4.7267999999999999</v>
       </c>
-      <c r="G27" s="29">
+      <c r="G27" s="28">
         <v>0.82</v>
       </c>
-      <c r="H27" s="30">
+      <c r="H27" s="29">
         <v>1.5</v>
       </c>
-      <c r="I27" s="37">
+      <c r="I27" s="36">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>7.0468000000000002</v>
       </c>
-      <c r="J27" s="29">
+      <c r="J27" s="28">
         <v>18</v>
       </c>
-      <c r="K27" s="36">
+      <c r="K27" s="35">
         <f t="shared" si="0"/>
         <v>10.953199999999999</v>
       </c>
-      <c r="L27" s="36">
+      <c r="L27" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>155.43509110518247</v>
       </c>
-      <c r="M27" s="36">
+      <c r="M27" s="35">
         <f t="shared" si="1"/>
         <v>60.851111111111102</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A28" s="20" t="s">
+      <c r="A28" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="21">
+      <c r="B28" s="20">
         <v>11.75</v>
       </c>
-      <c r="C28" s="21" t="s">
+      <c r="C28" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="21">
         <v>35</v>
       </c>
-      <c r="E28" s="22"/>
-      <c r="F28" s="29">
+      <c r="E28" s="21"/>
+      <c r="F28" s="28">
         <f t="shared" si="5"/>
         <v>0.82250000000000001</v>
       </c>
-      <c r="G28" s="29" t="s">
+      <c r="G28" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="H28" s="30" t="s">
+      <c r="H28" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="I28" s="37">
+      <c r="I28" s="36">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>0.82250000000000001</v>
       </c>
-      <c r="J28" s="29" t="s">
+      <c r="J28" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="K28" s="36" t="s">
+      <c r="K28" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="L28" s="36"/>
-      <c r="M28" s="36" t="s">
+      <c r="L28" s="35"/>
+      <c r="M28" s="35" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="21">
+      <c r="B29" s="20">
         <v>8</v>
       </c>
-      <c r="C29" s="21">
+      <c r="C29" s="20">
         <v>0.5</v>
       </c>
-      <c r="D29" s="22">
+      <c r="D29" s="21">
         <v>165</v>
       </c>
-      <c r="E29" s="27" t="s">
+      <c r="E29" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="F29" s="29">
+      <c r="F29" s="28">
         <f t="shared" si="5"/>
         <v>2.64</v>
       </c>
-      <c r="G29" s="29">
+      <c r="G29" s="28">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H29" s="30">
+      <c r="H29" s="29">
         <v>1.2</v>
       </c>
-      <c r="I29" s="37">
+      <c r="I29" s="36">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>4.5250000000000004</v>
       </c>
-      <c r="J29" s="29">
+      <c r="J29" s="28">
         <v>14</v>
       </c>
-      <c r="K29" s="36">
+      <c r="K29" s="35">
         <f t="shared" si="0"/>
         <v>9.4749999999999996</v>
       </c>
-      <c r="L29" s="36">
+      <c r="L29" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>209.39226519337012</v>
       </c>
-      <c r="M29" s="36">
+      <c r="M29" s="35">
         <f t="shared" si="1"/>
         <v>67.678571428571416</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="21">
+      <c r="B30" s="20">
         <v>8</v>
       </c>
-      <c r="C30" s="21">
+      <c r="C30" s="20">
         <v>0.5</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="21">
         <v>260</v>
       </c>
-      <c r="E30" s="27" t="s">
+      <c r="E30" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="F30" s="29">
+      <c r="F30" s="28">
         <f t="shared" si="5"/>
         <v>4.16</v>
       </c>
-      <c r="G30" s="29">
+      <c r="G30" s="28">
         <v>0.82</v>
       </c>
-      <c r="H30" s="30">
+      <c r="H30" s="29">
         <v>1.2</v>
       </c>
-      <c r="I30" s="37">
+      <c r="I30" s="36">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>6.1800000000000006</v>
       </c>
-      <c r="J30" s="29">
+      <c r="J30" s="28">
         <v>18</v>
       </c>
-      <c r="K30" s="36">
+      <c r="K30" s="35">
         <f t="shared" si="0"/>
         <v>11.82</v>
       </c>
-      <c r="L30" s="36">
+      <c r="L30" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>191.26213592233009</v>
       </c>
-      <c r="M30" s="36">
+      <c r="M30" s="35">
         <f t="shared" si="1"/>
         <v>65.666666666666671</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="B31" s="21">
+      <c r="B31" s="20">
         <v>2.875</v>
       </c>
-      <c r="C31" s="21" t="s">
+      <c r="C31" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="24">
+      <c r="D31" s="23">
         <v>140</v>
       </c>
-      <c r="E31" s="27" t="s">
+      <c r="E31" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="F31" s="29">
+      <c r="F31" s="28">
         <f t="shared" si="5"/>
         <v>0.80500000000000005</v>
       </c>
-      <c r="G31" s="29">
+      <c r="G31" s="28">
         <v>0.82</v>
       </c>
-      <c r="H31" s="29">
+      <c r="H31" s="28">
         <v>4.0999999999999996</v>
       </c>
-      <c r="I31" s="35">
+      <c r="I31" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.7249999999999996</v>
       </c>
-      <c r="J31" s="29">
+      <c r="J31" s="28">
         <v>16</v>
       </c>
-      <c r="K31" s="36">
+      <c r="K31" s="35">
         <f t="shared" si="0"/>
         <v>10.275</v>
       </c>
-      <c r="L31" s="36">
+      <c r="L31" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>179.47598253275109</v>
       </c>
-      <c r="M31" s="36">
+      <c r="M31" s="35">
         <f t="shared" si="1"/>
         <v>64.21875</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A32" s="20" t="s">
+      <c r="A32" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B32" s="21"/>
-      <c r="C32" s="21">
+      <c r="B32" s="20"/>
+      <c r="C32" s="20">
         <v>0.5</v>
       </c>
-      <c r="D32" s="22"/>
-      <c r="E32" s="27" t="s">
+      <c r="D32" s="21"/>
+      <c r="E32" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="F32" s="29">
+      <c r="F32" s="28">
         <v>3.88</v>
       </c>
-      <c r="G32" s="29">
+      <c r="G32" s="28">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H32" s="29">
+      <c r="H32" s="28">
         <v>0.2</v>
       </c>
-      <c r="I32" s="35">
+      <c r="I32" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>4.7649999999999997</v>
       </c>
-      <c r="J32" s="29">
+      <c r="J32" s="28">
         <v>14</v>
       </c>
-      <c r="K32" s="36">
+      <c r="K32" s="35">
         <f t="shared" si="0"/>
         <v>9.2349999999999994</v>
       </c>
-      <c r="L32" s="36">
+      <c r="L32" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>193.80902413431269</v>
       </c>
-      <c r="M32" s="36">
+      <c r="M32" s="35">
         <f t="shared" si="1"/>
         <v>65.964285714285708</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A33" s="20" t="s">
+      <c r="A33" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21">
+      <c r="B33" s="20"/>
+      <c r="C33" s="20">
         <v>0.5</v>
       </c>
-      <c r="D33" s="22"/>
-      <c r="E33" s="27" t="s">
+      <c r="D33" s="21"/>
+      <c r="E33" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="F33" s="29">
+      <c r="F33" s="28">
         <v>5.28</v>
       </c>
-      <c r="G33" s="29">
+      <c r="G33" s="28">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H33" s="29">
+      <c r="H33" s="28">
         <v>0.2</v>
       </c>
-      <c r="I33" s="35">
+      <c r="I33" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>6.165</v>
       </c>
-      <c r="J33" s="29">
+      <c r="J33" s="28">
         <v>15</v>
       </c>
-      <c r="K33" s="36">
+      <c r="K33" s="35">
         <f t="shared" si="0"/>
         <v>8.8350000000000009</v>
       </c>
-      <c r="L33" s="36">
+      <c r="L33" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>143.30900243309003</v>
       </c>
-      <c r="M33" s="36">
+      <c r="M33" s="35">
         <f t="shared" si="1"/>
         <v>58.900000000000006</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A34" s="20" t="s">
+      <c r="A34" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="B34" s="21"/>
-      <c r="C34" s="21">
+      <c r="B34" s="20"/>
+      <c r="C34" s="20">
         <v>0.5</v>
       </c>
-      <c r="D34" s="22">
+      <c r="D34" s="21">
         <v>370</v>
       </c>
-      <c r="E34" s="27" t="s">
+      <c r="E34" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="F34" s="29">
+      <c r="F34" s="28">
         <v>6.64</v>
       </c>
-      <c r="G34" s="29">
+      <c r="G34" s="28">
         <v>0.82</v>
       </c>
-      <c r="H34" s="29">
+      <c r="H34" s="28">
         <v>0.2</v>
       </c>
-      <c r="I34" s="35">
+      <c r="I34" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>7.66</v>
       </c>
-      <c r="J34" s="29">
+      <c r="J34" s="28">
         <v>24</v>
       </c>
-      <c r="K34" s="36">
+      <c r="K34" s="35">
         <f t="shared" si="0"/>
         <v>16.34</v>
       </c>
-      <c r="L34" s="36">
+      <c r="L34" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>213.31592689295042</v>
       </c>
-      <c r="M34" s="36">
+      <c r="M34" s="35">
         <f t="shared" si="1"/>
         <v>68.083333333333329</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A35" s="20" t="s">
+      <c r="A35" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="B35" s="25">
+      <c r="B35" s="24">
         <v>4.5</v>
       </c>
-      <c r="C35" s="21">
+      <c r="C35" s="20">
         <v>0.5</v>
       </c>
-      <c r="D35" s="22">
+      <c r="D35" s="21">
         <v>200</v>
       </c>
-      <c r="E35" s="27" t="s">
+      <c r="E35" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="F35" s="29">
+      <c r="F35" s="28">
         <f t="shared" si="5"/>
         <v>1.8</v>
       </c>
-      <c r="G35" s="29">
+      <c r="G35" s="28">
         <v>0.82</v>
       </c>
-      <c r="H35" s="29">
+      <c r="H35" s="28">
         <v>4</v>
       </c>
-      <c r="I35" s="35">
+      <c r="I35" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>6.62</v>
       </c>
-      <c r="J35" s="29">
+      <c r="J35" s="28">
         <v>16</v>
       </c>
-      <c r="K35" s="36">
+      <c r="K35" s="35">
         <f t="shared" si="0"/>
         <v>9.379999999999999</v>
       </c>
-      <c r="L35" s="36">
+      <c r="L35" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>141.69184290030211</v>
       </c>
-      <c r="M35" s="36">
+      <c r="M35" s="35">
         <f t="shared" si="1"/>
         <v>58.624999999999993</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A36" s="20" t="s">
+      <c r="A36" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="B36" s="21"/>
-      <c r="C36" s="21">
+      <c r="B36" s="20"/>
+      <c r="C36" s="20">
         <v>0.5</v>
       </c>
-      <c r="D36" s="22">
+      <c r="D36" s="21">
         <v>185</v>
       </c>
-      <c r="E36" s="27" t="s">
+      <c r="E36" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="F36" s="29">
+      <c r="F36" s="28">
         <v>2.5</v>
       </c>
-      <c r="G36" s="29">
+      <c r="G36" s="28">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H36" s="29">
+      <c r="H36" s="28">
         <v>1.4</v>
       </c>
-      <c r="I36" s="35">
+      <c r="I36" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>4.585</v>
       </c>
-      <c r="J36" s="29">
+      <c r="J36" s="28">
         <v>15</v>
       </c>
-      <c r="K36" s="36">
+      <c r="K36" s="35">
         <f t="shared" si="0"/>
         <v>10.414999999999999</v>
       </c>
-      <c r="L36" s="36">
+      <c r="L36" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>227.15376226826604</v>
       </c>
-      <c r="M36" s="36">
+      <c r="M36" s="35">
         <f t="shared" si="1"/>
         <v>69.433333333333323</v>
       </c>
     </row>
     <row r="40" spans="1:13">
-      <c r="E40" s="16"/>
+      <c r="E40" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
@@ -3034,11 +3045,11 @@
       <c r="B2" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="20.100000000000001" customHeight="1">
@@ -3046,125 +3057,125 @@
         <v>75</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>120</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>82</v>
+      <c r="C4" s="40" t="s">
+        <v>121</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>83</v>
+        <v>78</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>122</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>76</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C8" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>77</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A9" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>80</v>
+      <c r="C9" s="37" t="s">
+        <v>120</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="20.100000000000001" customHeight="1">
@@ -3175,30 +3186,30 @@
     </row>
     <row r="13" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B13" s="38" t="s">
-        <v>120</v>
+        <v>90</v>
+      </c>
+      <c r="B13" s="37" t="s">
+        <v>118</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A14" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B14" s="39" t="s">
-        <v>120</v>
+        <v>92</v>
+      </c>
+      <c r="B14" s="38" t="s">
+        <v>118</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="20.100000000000001" customHeight="1">
@@ -3209,58 +3220,58 @@
     </row>
     <row r="16" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A16" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="D16" s="8" t="s">
         <v>96</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1">
@@ -3268,41 +3279,41 @@
         <v>48</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A22" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1">
@@ -3313,72 +3324,72 @@
     </row>
     <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A24" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="D24" s="8" t="s">
         <v>107</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A25" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" s="6" t="s">
         <v>107</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A26" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A28" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1">
@@ -3386,13 +3397,13 @@
         <v>22</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1">
@@ -3400,13 +3411,13 @@
         <v>19</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="20.100000000000001" customHeight="1">
@@ -3414,13 +3425,13 @@
         <v>17</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
